--- a/database/event/7556/event_7556_evp_summary.xlsx
+++ b/database/event/7556/event_7556_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.0666</v>
+        <v>9.270200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>9.059939999999999</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4.513722494802755</v>
+        <v>3.3236</v>
       </c>
       <c r="E2" t="n">
-        <v>140.4038</v>
+        <v>9.270200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>28.21136970989236</v>
+        <v>2.786</v>
       </c>
       <c r="G2" t="n">
-        <v>112.1924655943281</v>
+        <v>6.4842</v>
       </c>
       <c r="H2" t="n">
-        <v>33.61863666349387</v>
+        <v>2.786</v>
       </c>
       <c r="I2" t="n">
-        <v>32.53416451305858</v>
+        <v>2.786</v>
       </c>
       <c r="J2" t="n">
-        <v>112.1924655943281</v>
+        <v>6.4907</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -541,7 +529,7 @@
         <v>213</v>
       </c>
       <c r="M2" t="n">
-        <v>144.7266</v>
+        <v>9.2767</v>
       </c>
       <c r="N2" t="n">
         <v>318</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.2829</v>
+        <v>6.826</v>
       </c>
       <c r="C3" t="n">
-        <v>7.45461</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.043143483141341</v>
+        <v>2.3362</v>
       </c>
       <c r="E3" t="n">
-        <v>94.66</v>
+        <v>6.826</v>
       </c>
       <c r="F3" t="n">
-        <v>8.874178581810238</v>
+        <v>1.7505</v>
       </c>
       <c r="G3" t="n">
-        <v>85.78583140020787</v>
+        <v>5.0755</v>
       </c>
       <c r="H3" t="n">
-        <v>8.874178581810238</v>
+        <v>1.7505</v>
       </c>
       <c r="I3" t="n">
-        <v>8.587914756590553</v>
+        <v>1.7505</v>
       </c>
       <c r="J3" t="n">
-        <v>85.78583140020787</v>
+        <v>5.0755</v>
       </c>
       <c r="K3" t="n">
         <v>105</v>
@@ -587,7 +575,7 @@
         <v>213</v>
       </c>
       <c r="M3" t="n">
-        <v>94.3737</v>
+        <v>6.826</v>
       </c>
       <c r="N3" t="n">
         <v>318</v>
@@ -596,185 +584,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.171</v>
+        <v>6.0563</v>
       </c>
       <c r="C4" t="n">
-        <v>6.4539</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.332268840690309</v>
+        <v>2.0252</v>
       </c>
       <c r="E4" t="n">
-        <v>72.5475</v>
+        <v>6.0563</v>
       </c>
       <c r="F4" t="n">
-        <v>18.99794562377214</v>
+        <v>4.2368</v>
       </c>
       <c r="G4" t="n">
-        <v>53.54960034753969</v>
+        <v>1.8195</v>
       </c>
       <c r="H4" t="n">
-        <v>19.14935249037913</v>
+        <v>4.4851</v>
       </c>
       <c r="I4" t="n">
-        <v>25.7677922912014</v>
+        <v>3.6353</v>
       </c>
       <c r="J4" t="n">
-        <v>53.54960034753969</v>
+        <v>1.8195</v>
       </c>
       <c r="K4" t="n">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="L4" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="M4" t="n">
-        <v>79.31740000000001</v>
+        <v>5.4548</v>
       </c>
       <c r="N4" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.787</v>
+        <v>5.468</v>
       </c>
       <c r="C5" t="n">
-        <v>6.1083</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2.11698187172116</v>
+        <v>1.7876</v>
       </c>
       <c r="E5" t="n">
-        <v>65.85080000000001</v>
+        <v>5.468</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.907104309535624</v>
+        <v>4.6346</v>
       </c>
       <c r="G5" t="n">
-        <v>74.75793461676008</v>
+        <v>0.8334</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.907104309535624</v>
+        <v>6.0857</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.619778364066732</v>
+        <v>4.9326</v>
       </c>
       <c r="J5" t="n">
-        <v>74.75793461676008</v>
+        <v>0.8334</v>
       </c>
       <c r="K5" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L5" t="n">
-        <v>213</v>
+        <v>72</v>
       </c>
       <c r="M5" t="n">
-        <v>66.1382</v>
+        <v>5.766</v>
       </c>
       <c r="N5" t="n">
-        <v>318</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.1984</v>
+        <v>5.2116</v>
       </c>
       <c r="C6" t="n">
-        <v>5.57856</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.813726480369922</v>
+        <v>1.684</v>
       </c>
       <c r="E6" t="n">
-        <v>56.4178</v>
+        <v>5.2116</v>
       </c>
       <c r="F6" t="n">
-        <v>39.71889246293118</v>
+        <v>0.4346</v>
       </c>
       <c r="G6" t="n">
-        <v>16.69887675748032</v>
+        <v>4.777</v>
       </c>
       <c r="H6" t="n">
-        <v>67.89956799460052</v>
+        <v>0.4346</v>
       </c>
       <c r="I6" t="n">
-        <v>51.31580253969808</v>
+        <v>0.4346</v>
       </c>
       <c r="J6" t="n">
-        <v>16.69887675748032</v>
+        <v>4.777</v>
       </c>
       <c r="K6" t="n">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="L6" t="n">
-        <v>72</v>
+        <v>213</v>
       </c>
       <c r="M6" t="n">
-        <v>68.0147</v>
+        <v>5.2116</v>
       </c>
       <c r="N6" t="n">
-        <v>154</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.679</v>
+        <v>5.0903</v>
       </c>
       <c r="C7" t="n">
-        <v>5.1111</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.570709111026145</v>
+        <v>1.635</v>
       </c>
       <c r="E7" t="n">
-        <v>48.8585</v>
+        <v>5.0903</v>
       </c>
       <c r="F7" t="n">
-        <v>33.88783695352866</v>
+        <v>2.0795</v>
       </c>
       <c r="G7" t="n">
-        <v>14.97063487084308</v>
+        <v>3.0107</v>
       </c>
       <c r="H7" t="n">
-        <v>47.55246038729005</v>
+        <v>2.0795</v>
       </c>
       <c r="I7" t="n">
-        <v>37.25307956607977</v>
+        <v>2.0892</v>
       </c>
       <c r="J7" t="n">
-        <v>14.97063487084308</v>
+        <v>3.0107</v>
       </c>
       <c r="K7" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="L7" t="n">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="M7" t="n">
-        <v>52.2237</v>
+        <v>5.0999</v>
       </c>
       <c r="N7" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8">
@@ -784,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.1914</v>
+        <v>5.0376</v>
       </c>
       <c r="C8" t="n">
-        <v>4.67226</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.361669026896025</v>
+        <v>1.6137</v>
       </c>
       <c r="E8" t="n">
-        <v>42.3561</v>
+        <v>5.0376</v>
       </c>
       <c r="F8" t="n">
-        <v>34.23704759497132</v>
+        <v>4.3223</v>
       </c>
       <c r="G8" t="n">
-        <v>8.119024142115428</v>
+        <v>0.7153</v>
       </c>
       <c r="H8" t="n">
-        <v>48.57774135072433</v>
+        <v>4.829</v>
       </c>
       <c r="I8" t="n">
-        <v>36.71313171206815</v>
+        <v>3.914</v>
       </c>
       <c r="J8" t="n">
-        <v>8.119024142115428</v>
+        <v>0.7153</v>
       </c>
       <c r="K8" t="n">
         <v>82</v>
@@ -817,7 +805,7 @@
         <v>72</v>
       </c>
       <c r="M8" t="n">
-        <v>44.8322</v>
+        <v>4.629300000000001</v>
       </c>
       <c r="N8" t="n">
         <v>154</v>
@@ -826,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.7381</v>
+        <v>4.1825</v>
       </c>
       <c r="C9" t="n">
-        <v>4.26429</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1.182633056243837</v>
+        <v>1.2683</v>
       </c>
       <c r="E9" t="n">
-        <v>36.787</v>
+        <v>4.1825</v>
       </c>
       <c r="F9" t="n">
-        <v>4.759026581163726</v>
+        <v>1.4571</v>
       </c>
       <c r="G9" t="n">
-        <v>32.02795291201013</v>
+        <v>2.7254</v>
       </c>
       <c r="H9" t="n">
-        <v>4.759026581163726</v>
+        <v>1.4571</v>
       </c>
       <c r="I9" t="n">
-        <v>3.728269671879417</v>
+        <v>1.4639</v>
       </c>
       <c r="J9" t="n">
-        <v>32.02795291201013</v>
+        <v>2.7254</v>
       </c>
       <c r="K9" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="L9" t="n">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="M9" t="n">
-        <v>35.7562</v>
+        <v>4.1893</v>
       </c>
       <c r="N9" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -876,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.2789</v>
+        <v>3.6954</v>
       </c>
       <c r="C10" t="n">
-        <v>3.85101</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1.015105768886889</v>
+        <v>1.0715</v>
       </c>
       <c r="E10" t="n">
-        <v>31.5759</v>
+        <v>3.6954</v>
       </c>
       <c r="F10" t="n">
-        <v>27.29347936604759</v>
+        <v>3.4975</v>
       </c>
       <c r="G10" t="n">
-        <v>4.282396943421245</v>
+        <v>0.1979</v>
       </c>
       <c r="H10" t="n">
-        <v>31.78550224151432</v>
+        <v>3.4975</v>
       </c>
       <c r="I10" t="n">
-        <v>24.02222289220437</v>
+        <v>2.8348</v>
       </c>
       <c r="J10" t="n">
-        <v>4.282396943421245</v>
+        <v>0.1979</v>
       </c>
       <c r="K10" t="n">
         <v>82</v>
@@ -909,7 +897,7 @@
         <v>72</v>
       </c>
       <c r="M10" t="n">
-        <v>28.3046</v>
+        <v>3.0327</v>
       </c>
       <c r="N10" t="n">
         <v>154</v>
@@ -918,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8673</v>
+        <v>3.6242</v>
       </c>
       <c r="C11" t="n">
-        <v>3.48057</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8758998821449525</v>
+        <v>1.0427</v>
       </c>
       <c r="E11" t="n">
-        <v>27.2457</v>
+        <v>3.6242</v>
       </c>
       <c r="F11" t="n">
-        <v>26.86643699953189</v>
+        <v>0.8708</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3793015094856216</v>
+        <v>2.7534</v>
       </c>
       <c r="H11" t="n">
-        <v>30.96705664742094</v>
+        <v>0.8708</v>
       </c>
       <c r="I11" t="n">
-        <v>24.25990612931595</v>
+        <v>0.7058</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3793015094856216</v>
+        <v>2.7534</v>
       </c>
       <c r="K11" t="n">
         <v>85</v>
@@ -955,7 +943,7 @@
         <v>152</v>
       </c>
       <c r="M11" t="n">
-        <v>24.6392</v>
+        <v>3.4592</v>
       </c>
       <c r="N11" t="n">
         <v>237</v>
@@ -964,354 +952,354 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6094</v>
+        <v>3.6122</v>
       </c>
       <c r="C12" t="n">
-        <v>3.24846</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7936406966327395</v>
+        <v>1.0379</v>
       </c>
       <c r="E12" t="n">
-        <v>24.687</v>
+        <v>3.6122</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.876700301645091</v>
+        <v>2.7645</v>
       </c>
       <c r="G12" t="n">
-        <v>26.56368488899051</v>
+        <v>0.8477</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.876700301645091</v>
+        <v>2.7645</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.525329438158371</v>
+        <v>2.2407</v>
       </c>
       <c r="J12" t="n">
-        <v>26.56368488899051</v>
+        <v>0.8477</v>
       </c>
       <c r="K12" t="n">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="L12" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="M12" t="n">
-        <v>24.0384</v>
+        <v>3.0884</v>
       </c>
       <c r="N12" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8267</v>
+        <v>3.3086</v>
       </c>
       <c r="C13" t="n">
-        <v>2.54403</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5653819865112045</v>
+        <v>0.9152</v>
       </c>
       <c r="E13" t="n">
-        <v>17.5868</v>
+        <v>3.3086</v>
       </c>
       <c r="F13" t="n">
-        <v>28.25580572508559</v>
+        <v>4.2934</v>
       </c>
       <c r="G13" t="n">
-        <v>-10.66903573435291</v>
+        <v>-0.9848</v>
       </c>
       <c r="H13" t="n">
-        <v>33.71001574766142</v>
+        <v>4.713</v>
       </c>
       <c r="I13" t="n">
-        <v>35.72950977862731</v>
+        <v>3.82</v>
       </c>
       <c r="J13" t="n">
-        <v>-10.66903573435291</v>
+        <v>-0.9848</v>
       </c>
       <c r="K13" t="n">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="L13" t="n">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="M13" t="n">
-        <v>25.0605</v>
+        <v>2.8352</v>
       </c>
       <c r="N13" t="n">
-        <v>150</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6682</v>
+        <v>2.6594</v>
       </c>
       <c r="C14" t="n">
-        <v>2.40138</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5228039319133077</v>
+        <v>0.653</v>
       </c>
       <c r="E14" t="n">
-        <v>16.2623</v>
+        <v>2.6594</v>
       </c>
       <c r="F14" t="n">
-        <v>19.00629757876402</v>
+        <v>2.9919</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.743960397585018</v>
+        <v>-0.3325</v>
       </c>
       <c r="H14" t="n">
-        <v>19.15912475152258</v>
+        <v>2.9919</v>
       </c>
       <c r="I14" t="n">
-        <v>21.36639718833394</v>
+        <v>2.9919</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.743960397585018</v>
+        <v>-0.3325</v>
       </c>
       <c r="K14" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L14" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="M14" t="n">
-        <v>18.6224</v>
+        <v>2.6594</v>
       </c>
       <c r="N14" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.141</v>
+        <v>2.312</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9269</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3893861646092506</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>12.1122</v>
+        <v>2.312</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9540424893820432</v>
+        <v>1.6956</v>
       </c>
       <c r="G15" t="n">
-        <v>13.06628709203309</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9540424893820432</v>
+        <v>1.6956</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.063955218573523</v>
+        <v>1.7035</v>
       </c>
       <c r="J15" t="n">
-        <v>13.06628709203309</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="L15" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="M15" t="n">
-        <v>12.0023</v>
+        <v>2.3199</v>
       </c>
       <c r="N15" t="n">
-        <v>172</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8065</v>
+        <v>2.1173</v>
       </c>
       <c r="C16" t="n">
-        <v>1.62585</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3108779062398793</v>
+        <v>0.434</v>
       </c>
       <c r="E16" t="n">
-        <v>9.670199999999999</v>
+        <v>2.1173</v>
       </c>
       <c r="F16" t="n">
-        <v>11.95780301075093</v>
+        <v>1.9806</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.287636003877312</v>
+        <v>0.1367</v>
       </c>
       <c r="H16" t="n">
-        <v>11.95780301075093</v>
+        <v>1.9806</v>
       </c>
       <c r="I16" t="n">
-        <v>16.09068423566485</v>
+        <v>1.9899</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.287636003877312</v>
+        <v>0.1367</v>
       </c>
       <c r="K16" t="n">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="L16" t="n">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>13.803</v>
+        <v>2.1266</v>
       </c>
       <c r="N16" t="n">
-        <v>243</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7053</v>
+        <v>1.9184</v>
       </c>
       <c r="C17" t="n">
-        <v>1.53477</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2880133518227722</v>
+        <v>0.3536</v>
       </c>
       <c r="E17" t="n">
-        <v>8.9589</v>
+        <v>1.9184</v>
       </c>
       <c r="F17" t="n">
-        <v>30.99092241637733</v>
+        <v>1.4915</v>
       </c>
       <c r="G17" t="n">
-        <v>-22.03198015501705</v>
+        <v>0.4269</v>
       </c>
       <c r="H17" t="n">
-        <v>39.84004124778743</v>
+        <v>1.4915</v>
       </c>
       <c r="I17" t="n">
-        <v>31.21109222176896</v>
+        <v>1.4984</v>
       </c>
       <c r="J17" t="n">
-        <v>-22.03198015501705</v>
+        <v>0.4269</v>
       </c>
       <c r="K17" t="n">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="L17" t="n">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>9.1791</v>
+        <v>1.9253</v>
       </c>
       <c r="N17" t="n">
-        <v>237</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9755</v>
+        <v>1.413</v>
       </c>
       <c r="C18" t="n">
-        <v>0.87795</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1344844525557898</v>
+        <v>0.1495</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1833</v>
+        <v>1.413</v>
       </c>
       <c r="F18" t="n">
-        <v>4.183272886040924</v>
+        <v>1.3462</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0668</v>
       </c>
       <c r="H18" t="n">
-        <v>4.183272886040924</v>
+        <v>1.3462</v>
       </c>
       <c r="I18" t="n">
-        <v>4.857994319273331</v>
+        <v>1.3525</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.0668</v>
       </c>
       <c r="K18" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>4.858</v>
+        <v>1.4193</v>
       </c>
       <c r="N18" t="n">
-        <v>126</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.837</v>
+        <v>0.834</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7533</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1074726434029477</v>
+        <v>-0.0844</v>
       </c>
       <c r="E19" t="n">
-        <v>3.343</v>
+        <v>0.834</v>
       </c>
       <c r="F19" t="n">
-        <v>3.343043649987631</v>
+        <v>0.834</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.343043649987631</v>
+        <v>0.834</v>
       </c>
       <c r="I19" t="n">
-        <v>3.882244238695314</v>
+        <v>0.834</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1323,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8822</v>
+        <v>0.834</v>
       </c>
       <c r="N19" t="n">
         <v>126</v>
@@ -1332,139 +1320,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3237</v>
+        <v>0.7458</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.29133</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1049213583505271</v>
+        <v>-0.1201</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2637</v>
+        <v>0.7458</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2316340249473798</v>
+        <v>0.0803</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.032049361593256</v>
+        <v>0.6655</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2316340249473798</v>
+        <v>0.0803</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2583199725219627</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.032049361593256</v>
+        <v>0.6655</v>
       </c>
       <c r="K20" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.2904</v>
+        <v>0.7462</v>
       </c>
       <c r="N20" t="n">
-        <v>172</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.9596</v>
+        <v>0.2158</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.8636400000000001</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2341231503252796</v>
+        <v>-0.3342</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.2826</v>
+        <v>0.2158</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.282633851998084</v>
+        <v>0.3874</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.1716</v>
       </c>
       <c r="H21" t="n">
-        <v>-7.282633851998084</v>
+        <v>0.3874</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.906652340791073</v>
+        <v>0.3892</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.1716</v>
       </c>
       <c r="K21" t="n">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>-5.9067</v>
+        <v>0.2176</v>
       </c>
       <c r="N21" t="n">
-        <v>88</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.083</v>
+        <v>0.1695</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.9747</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2608925839696288</v>
+        <v>-0.3529</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.1153</v>
+        <v>0.1695</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.115323756376602</v>
+        <v>-0.099</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.2685</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.115323756376602</v>
+        <v>-0.099</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.582013737890701</v>
+        <v>-0.099</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.2685</v>
       </c>
       <c r="K22" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M22" t="n">
-        <v>-6.582</v>
+        <v>0.1695</v>
       </c>
       <c r="N22" t="n">
-        <v>88</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
@@ -1474,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.5364</v>
+        <v>0.0912</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.38276</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3643448550144551</v>
+        <v>-0.3845</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.3333</v>
+        <v>0.0912</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.457161860882194</v>
+        <v>0.3347</v>
       </c>
       <c r="G23" t="n">
-        <v>-8.876147857712958</v>
+        <v>-0.2435</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.457161860882194</v>
+        <v>0.3347</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.604365106004169</v>
+        <v>0.3347</v>
       </c>
       <c r="J23" t="n">
-        <v>-8.876147857712958</v>
+        <v>-0.2435</v>
       </c>
       <c r="K23" t="n">
         <v>115</v>
@@ -1507,7 +1495,7 @@
         <v>35</v>
       </c>
       <c r="M23" t="n">
-        <v>-11.4805</v>
+        <v>0.0912</v>
       </c>
       <c r="N23" t="n">
         <v>150</v>
@@ -1516,78 +1504,78 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.7522</v>
+        <v>0.0256</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.57698</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4165225175944013</v>
+        <v>-0.411</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.9563</v>
+        <v>0.0256</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.125155989800769</v>
+        <v>0.0256</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.831191908892804</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.125155989800769</v>
+        <v>0.0256</v>
       </c>
       <c r="I24" t="n">
-        <v>-9.671824320986991</v>
+        <v>0.0256</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.831191908892804</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="L24" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-13.503</v>
+        <v>0.0256</v>
       </c>
       <c r="N24" t="n">
-        <v>150</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.8166</v>
+        <v>-0.1988</v>
       </c>
       <c r="C25" t="n">
-        <v>-1.63494</v>
+        <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.432484703765268</v>
+        <v>-0.5017</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.4529</v>
+        <v>-0.1988</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.45286760295324</v>
+        <v>-0.1988</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-13.45286760295324</v>
+        <v>-0.1988</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.91108155815562</v>
+        <v>-0.1988</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1599,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-10.9111</v>
+        <v>-0.1988</v>
       </c>
       <c r="N25" t="n">
         <v>88</v>
@@ -1608,231 +1596,231 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.0773</v>
+        <v>-0.2723</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.86957</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.498914837472221</v>
+        <v>-0.5314</v>
       </c>
       <c r="E26" t="n">
-        <v>-15.5192</v>
+        <v>-0.2723</v>
       </c>
       <c r="F26" t="n">
-        <v>-15.51924309745203</v>
+        <v>-0.2723</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.48340353022093</v>
+        <v>-0.2723</v>
       </c>
       <c r="I26" t="n">
-        <v>-17.98072668025657</v>
+        <v>-0.2723</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-17.9807</v>
+        <v>-0.2723</v>
       </c>
       <c r="N26" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.1468</v>
+        <v>-0.4588</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.93212</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5171529532893845</v>
+        <v>-0.6067</v>
       </c>
       <c r="E27" t="n">
-        <v>-16.0866</v>
+        <v>-0.4588</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.152485568766004</v>
+        <v>-0.4588</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.93407229214364</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.152485568766004</v>
+        <v>-0.4588</v>
       </c>
       <c r="I27" t="n">
-        <v>-5.405565130311634</v>
+        <v>-0.4588</v>
       </c>
       <c r="J27" t="n">
-        <v>-8.93407229214364</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L27" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-14.3396</v>
+        <v>-0.4588</v>
       </c>
       <c r="N27" t="n">
-        <v>154</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.2723</v>
+        <v>-0.492</v>
       </c>
       <c r="C28" t="n">
-        <v>-2.04507</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5506195587654802</v>
+        <v>-0.6201</v>
       </c>
       <c r="E28" t="n">
-        <v>-17.1276</v>
+        <v>-0.492</v>
       </c>
       <c r="F28" t="n">
-        <v>-10.2519305227347</v>
+        <v>0.508</v>
       </c>
       <c r="G28" t="n">
-        <v>-6.875639444893388</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>-10.2519305227347</v>
+        <v>0.508</v>
       </c>
       <c r="I28" t="n">
-        <v>-11.43302850922487</v>
+        <v>0.508</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.875639444893388</v>
+        <v>-1</v>
       </c>
       <c r="K28" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L28" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="M28" t="n">
-        <v>-18.3087</v>
+        <v>-0.492</v>
       </c>
       <c r="N28" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.5668</v>
+        <v>-0.6321</v>
       </c>
       <c r="C29" t="n">
-        <v>-2.31012</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6321061875951295</v>
+        <v>-0.6767</v>
       </c>
       <c r="E29" t="n">
-        <v>-19.6623</v>
+        <v>-0.6321</v>
       </c>
       <c r="F29" t="n">
-        <v>-13.7169738426463</v>
+        <v>-0.6321</v>
       </c>
       <c r="G29" t="n">
-        <v>-5.945318901330536</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-13.7169738426463</v>
+        <v>-0.6321</v>
       </c>
       <c r="I29" t="n">
-        <v>-18.45786341959779</v>
+        <v>-0.6321</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.945318901330536</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="L29" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-24.4032</v>
+        <v>-0.6321</v>
       </c>
       <c r="N29" t="n">
-        <v>243</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.6177</v>
+        <v>-0.79</v>
       </c>
       <c r="C30" t="n">
-        <v>-2.35593</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6466207388956683</v>
+        <v>-0.7405</v>
       </c>
       <c r="E30" t="n">
-        <v>-20.1138</v>
+        <v>-0.79</v>
       </c>
       <c r="F30" t="n">
-        <v>-15.21993531964528</v>
+        <v>-0.5616</v>
       </c>
       <c r="G30" t="n">
-        <v>-4.89384700364486</v>
+        <v>-0.2284</v>
       </c>
       <c r="H30" t="n">
-        <v>-15.202884518</v>
+        <v>-0.5616</v>
       </c>
       <c r="I30" t="n">
-        <v>-11.91009386202765</v>
+        <v>-0.4552</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.89384700364486</v>
+        <v>-0.2284</v>
       </c>
       <c r="K30" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L30" t="n">
-        <v>152</v>
+        <v>72</v>
       </c>
       <c r="M30" t="n">
-        <v>-16.8039</v>
+        <v>-0.6836</v>
       </c>
       <c r="N30" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31">
@@ -1842,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.7741</v>
+        <v>-0.8424</v>
       </c>
       <c r="C31" t="n">
-        <v>-2.49669</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6920260035061677</v>
+        <v>-0.7617</v>
       </c>
       <c r="E31" t="n">
-        <v>-21.5262</v>
+        <v>-0.8424</v>
       </c>
       <c r="F31" t="n">
-        <v>-21.5261583170863</v>
+        <v>-0.8424</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-22.347342864143</v>
+        <v>-0.8424</v>
       </c>
       <c r="I31" t="n">
-        <v>-25.95175300352091</v>
+        <v>-0.8424</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1875,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-25.9518</v>
+        <v>-0.8424</v>
       </c>
       <c r="N31" t="n">
         <v>126</v>
@@ -1884,78 +1872,78 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.8493</v>
+        <v>-1.2268</v>
       </c>
       <c r="C32" t="n">
-        <v>-2.56437</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7143210617562284</v>
+        <v>-0.917</v>
       </c>
       <c r="E32" t="n">
-        <v>-22.2197</v>
+        <v>-1.2268</v>
       </c>
       <c r="F32" t="n">
-        <v>-22.21966831692432</v>
+        <v>-1.6245</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.3977</v>
       </c>
       <c r="H32" t="n">
-        <v>-23.3144003904143</v>
+        <v>-1.6245</v>
       </c>
       <c r="I32" t="n">
-        <v>-18.90937543185676</v>
+        <v>-1.3167</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.3977</v>
       </c>
       <c r="K32" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="M32" t="n">
-        <v>-18.9094</v>
+        <v>-0.919</v>
       </c>
       <c r="N32" t="n">
-        <v>88</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-3.2301</v>
+        <v>-1.2779</v>
       </c>
       <c r="C33" t="n">
-        <v>-2.90709</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8316738213386861</v>
+        <v>-0.9376</v>
       </c>
       <c r="E33" t="n">
-        <v>-25.87</v>
+        <v>-1.2779</v>
       </c>
       <c r="F33" t="n">
-        <v>-25.8700428244141</v>
+        <v>-1.2779</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-29.13843716679667</v>
+        <v>-1.2779</v>
       </c>
       <c r="I33" t="n">
-        <v>-23.63301816293186</v>
+        <v>-1.2779</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1967,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-23.633</v>
+        <v>-1.2779</v>
       </c>
       <c r="N33" t="n">
         <v>88</v>
@@ -1980,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-3.3584</v>
+        <v>-1.3855</v>
       </c>
       <c r="C34" t="n">
-        <v>-3.02256</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8730222100866575</v>
+        <v>-0.9811</v>
       </c>
       <c r="E34" t="n">
-        <v>-27.1562</v>
+        <v>-1.3855</v>
       </c>
       <c r="F34" t="n">
-        <v>-27.15622565256751</v>
+        <v>-1.3855</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-31.52011755239166</v>
+        <v>-1.3855</v>
       </c>
       <c r="I34" t="n">
-        <v>-36.60400748019677</v>
+        <v>-1.3855</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2013,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-36.604</v>
+        <v>-1.3855</v>
       </c>
       <c r="N34" t="n">
         <v>126</v>
@@ -2022,277 +2010,277 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-3.6066</v>
+        <v>-1.5448</v>
       </c>
       <c r="C35" t="n">
-        <v>-3.24594</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9556266853159435</v>
+        <v>-1.0454</v>
       </c>
       <c r="E35" t="n">
-        <v>-29.7257</v>
+        <v>-1.5448</v>
       </c>
       <c r="F35" t="n">
-        <v>-21.75478972041759</v>
+        <v>-1.5448</v>
       </c>
       <c r="G35" t="n">
-        <v>-7.97093043448995</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-22.66163973558445</v>
+        <v>-1.5448</v>
       </c>
       <c r="I35" t="n">
-        <v>-30.49400369949613</v>
+        <v>-1.5448</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.97093043448995</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="L35" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-38.4649</v>
+        <v>-1.5448</v>
       </c>
       <c r="N35" t="n">
-        <v>243</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-3.8423</v>
+        <v>-1.9861</v>
       </c>
       <c r="C36" t="n">
-        <v>-3.45807</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.037478180062381</v>
+        <v>-1.2237</v>
       </c>
       <c r="E36" t="n">
-        <v>-32.2718</v>
+        <v>-1.9861</v>
       </c>
       <c r="F36" t="n">
-        <v>-9.283008683309523</v>
+        <v>-1.3933</v>
       </c>
       <c r="G36" t="n">
-        <v>-22.98878376581098</v>
+        <v>-0.5928</v>
       </c>
       <c r="H36" t="n">
-        <v>-9.283008683309523</v>
+        <v>-1.3933</v>
       </c>
       <c r="I36" t="n">
-        <v>-9.839133627470924</v>
+        <v>-1.3998</v>
       </c>
       <c r="J36" t="n">
-        <v>-22.98878376581098</v>
+        <v>-0.5928</v>
       </c>
       <c r="K36" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L36" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="M36" t="n">
-        <v>-32.8279</v>
+        <v>-1.9926</v>
       </c>
       <c r="N36" t="n">
-        <v>150</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-4.0657</v>
+        <v>-2.228</v>
       </c>
       <c r="C37" t="n">
-        <v>-3.65913</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.118183925375773</v>
+        <v>-1.3214</v>
       </c>
       <c r="E37" t="n">
-        <v>-34.7822</v>
+        <v>-2.228</v>
       </c>
       <c r="F37" t="n">
-        <v>-13.22668486092539</v>
+        <v>-1.4315</v>
       </c>
       <c r="G37" t="n">
-        <v>-21.55554020476229</v>
+        <v>-0.7965</v>
       </c>
       <c r="H37" t="n">
-        <v>-13.22668486092539</v>
+        <v>-1.4315</v>
       </c>
       <c r="I37" t="n">
-        <v>-12.80001760734715</v>
+        <v>-1.4315</v>
       </c>
       <c r="J37" t="n">
-        <v>-21.55554020476229</v>
+        <v>-0.7965</v>
       </c>
       <c r="K37" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L37" t="n">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="M37" t="n">
-        <v>-34.3556</v>
+        <v>-2.228</v>
       </c>
       <c r="N37" t="n">
-        <v>318</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-4.7267</v>
+        <v>-2.2338</v>
       </c>
       <c r="C38" t="n">
-        <v>-4.25403</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.376238798972131</v>
+        <v>-1.3238</v>
       </c>
       <c r="E38" t="n">
-        <v>-42.8093</v>
+        <v>-2.2338</v>
       </c>
       <c r="F38" t="n">
-        <v>-26.38849253054629</v>
+        <v>-0.2371</v>
       </c>
       <c r="G38" t="n">
-        <v>-16.42078648309523</v>
+        <v>-1.9967</v>
       </c>
       <c r="H38" t="n">
-        <v>-30.07602105231322</v>
+        <v>-0.2371</v>
       </c>
       <c r="I38" t="n">
-        <v>-31.87781033194489</v>
+        <v>-0.2371</v>
       </c>
       <c r="J38" t="n">
-        <v>-16.42078648309523</v>
+        <v>-1.9967</v>
       </c>
       <c r="K38" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="L38" t="n">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="M38" t="n">
-        <v>-48.2986</v>
+        <v>-2.2338</v>
       </c>
       <c r="N38" t="n">
-        <v>150</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-4.9961</v>
+        <v>-2.5782</v>
       </c>
       <c r="C39" t="n">
-        <v>-4.496490000000001</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.490188931559719</v>
+        <v>-1.4629</v>
       </c>
       <c r="E39" t="n">
-        <v>-46.3538</v>
+        <v>-2.5782</v>
       </c>
       <c r="F39" t="n">
-        <v>-24.87825734799319</v>
+        <v>-1.5782</v>
       </c>
       <c r="G39" t="n">
-        <v>-21.47555407036386</v>
+        <v>-1</v>
       </c>
       <c r="H39" t="n">
-        <v>-27.42551848210934</v>
+        <v>-1.5782</v>
       </c>
       <c r="I39" t="n">
-        <v>-30.58514042705281</v>
+        <v>-1.2792</v>
       </c>
       <c r="J39" t="n">
-        <v>-21.47555407036386</v>
+        <v>-1</v>
       </c>
       <c r="K39" t="n">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="L39" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="M39" t="n">
-        <v>-52.0607</v>
+        <v>-2.2792</v>
       </c>
       <c r="N39" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.6817</v>
+        <v>-2.6916</v>
       </c>
       <c r="C40" t="n">
-        <v>-5.11353</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.805558893001738</v>
+        <v>-1.5087</v>
       </c>
       <c r="E40" t="n">
-        <v>-56.1637</v>
+        <v>-2.6916</v>
       </c>
       <c r="F40" t="n">
-        <v>-22.59823622496948</v>
+        <v>-1.6916</v>
       </c>
       <c r="G40" t="n">
-        <v>-33.56547205283961</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-23.85983329556078</v>
+        <v>-1.6916</v>
       </c>
       <c r="I40" t="n">
-        <v>-18.03231640770492</v>
+        <v>-1.6995</v>
       </c>
       <c r="J40" t="n">
-        <v>-33.56547205283961</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="L40" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="M40" t="n">
-        <v>-51.5978</v>
+        <v>-2.6995</v>
       </c>
       <c r="N40" t="n">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41">
@@ -2302,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-6.0411</v>
+        <v>-4.028</v>
       </c>
       <c r="C41" t="n">
-        <v>-5.436990000000001</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.986525986030119</v>
+        <v>-2.0486</v>
       </c>
       <c r="E41" t="n">
-        <v>-61.7929</v>
+        <v>-4.028</v>
       </c>
       <c r="F41" t="n">
-        <v>-25.87199930418456</v>
+        <v>-1.9542</v>
       </c>
       <c r="G41" t="n">
-        <v>-35.92087070306104</v>
+        <v>-2.0738</v>
       </c>
       <c r="H41" t="n">
-        <v>-29.14191981497406</v>
+        <v>-1.9542</v>
       </c>
       <c r="I41" t="n">
-        <v>-28.20185788545877</v>
+        <v>-1.9542</v>
       </c>
       <c r="J41" t="n">
-        <v>-35.92087070306104</v>
+        <v>-2.0738</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2335,7 +2323,7 @@
         <v>213</v>
       </c>
       <c r="M41" t="n">
-        <v>-64.12269999999999</v>
+        <v>-4.028</v>
       </c>
       <c r="N41" t="n">
         <v>318</v>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9799498235463195</v>
+        <v>1.2195</v>
       </c>
       <c r="J2" t="n">
-        <v>21.55889611801903</v>
+        <v>26.829</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4130853040439423</v>
+        <v>0.59</v>
       </c>
       <c r="J3" t="n">
-        <v>9.08787668896673</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4130853040439423</v>
+        <v>0.59</v>
       </c>
       <c r="J4" t="n">
-        <v>9.08787668896673</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03478584876369557</v>
+        <v>-0.268</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7652886728013024</v>
+        <v>-5.896</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.25449138638106</v>
+        <v>-0.7343</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.59881050038332</v>
+        <v>-16.1546</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6656529488118024</v>
+        <v>0.7118</v>
       </c>
       <c r="J7" t="n">
-        <v>14.64436487385965</v>
+        <v>15.6596</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.37</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5367879660801372</v>
+        <v>0.627</v>
       </c>
       <c r="J8" t="n">
-        <v>11.80933525376302</v>
+        <v>13.794</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4517116964352064</v>
+        <v>-0.4281</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.937657321574541</v>
+        <v>-9.418200000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5087141402240493</v>
+        <v>-0.4833</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.19171108492908</v>
+        <v>-10.6326</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8738505561269654</v>
+        <v>-0.8151</v>
       </c>
       <c r="J11" t="n">
-        <v>-19.22471223479324</v>
+        <v>-17.9322</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.52</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9933678584891749</v>
+        <v>1.3025</v>
       </c>
       <c r="J12" t="n">
-        <v>23.8408286037402</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.45</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8579529149315536</v>
+        <v>1.1616</v>
       </c>
       <c r="J13" t="n">
-        <v>20.59086995835728</v>
+        <v>27.8784</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1988999198508667</v>
+        <v>0.3574</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7735980764208</v>
+        <v>8.5776</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.79</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2942412425976223</v>
+        <v>-0.7326</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.061789822342935</v>
+        <v>-17.5824</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.384724409152525</v>
+        <v>-0.8937</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.233385819660599</v>
+        <v>-21.4488</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2863084626667062</v>
+        <v>0.3809</v>
       </c>
       <c r="J17" t="n">
-        <v>6.871403104000949</v>
+        <v>9.1416</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04167368910416971</v>
+        <v>0.1661</v>
       </c>
       <c r="J18" t="n">
-        <v>1.000168538500073</v>
+        <v>3.9864</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>0.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1346659642083448</v>
+        <v>-0.1312</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.231983141000274</v>
+        <v>-3.1488</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1346659642083448</v>
+        <v>-0.1312</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.231983141000274</v>
+        <v>-3.1488</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.54</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6744839151136497</v>
+        <v>-0.7073</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.18761396272759</v>
+        <v>-16.9752</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.46</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7134710741318389</v>
+        <v>0.7088</v>
       </c>
       <c r="J22" t="n">
-        <v>17.12330577916413</v>
+        <v>17.0112</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.19</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1652346681075116</v>
+        <v>0.36</v>
       </c>
       <c r="J23" t="n">
-        <v>3.965632034580279</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1505913163163179</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.614191591591629</v>
+        <v>-1.9248</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.202571338390827</v>
+        <v>-0.1645</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.861712121379847</v>
+        <v>-3.948</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6916615820352801</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.59987796884672</v>
+        <v>-16.7304</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6709107923524509</v>
+        <v>0.6252</v>
       </c>
       <c r="J27" t="n">
-        <v>16.10185901645882</v>
+        <v>15.0048</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6134833261395396</v>
+        <v>0.5888</v>
       </c>
       <c r="J28" t="n">
-        <v>14.72359982734895</v>
+        <v>14.1312</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.05180389090965745</v>
+        <v>0.1372</v>
       </c>
       <c r="J29" t="n">
-        <v>1.243293381831779</v>
+        <v>3.2928</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1842786048791522</v>
+        <v>-0.2129</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.422686517099652</v>
+        <v>-5.1096</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2563630024232379</v>
+        <v>-0.2946</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.152712058157709</v>
+        <v>-7.0704</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.65</v>
       </c>
       <c r="I32" t="n">
-        <v>1.389975347852328</v>
+        <v>1.5506</v>
       </c>
       <c r="J32" t="n">
-        <v>27.79950695704656</v>
+        <v>31.012</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5448588027678005</v>
+        <v>0.6439</v>
       </c>
       <c r="J33" t="n">
-        <v>10.89717605535601</v>
+        <v>12.878</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.18</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4635702924517839</v>
+        <v>0.5394</v>
       </c>
       <c r="J34" t="n">
-        <v>9.271405849035677</v>
+        <v>10.788</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.06483108921533304</v>
+        <v>-0.4785</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.296621784306661</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.67</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3497800821492767</v>
+        <v>-1.0035</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.995601642985535</v>
+        <v>-20.07</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4436327131201394</v>
+        <v>0.6153</v>
       </c>
       <c r="J37" t="n">
-        <v>8.872654262402788</v>
+        <v>12.306</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.19</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1184510787552886</v>
+        <v>0.3883</v>
       </c>
       <c r="J38" t="n">
-        <v>2.369021575105771</v>
+        <v>7.766</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.07</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.07897997009866352</v>
+        <v>0.196</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.57959940197327</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.61</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7171100820852396</v>
+        <v>-0.6252</v>
       </c>
       <c r="J40" t="n">
-        <v>-14.34220164170479</v>
+        <v>-12.504</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.5</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8643892966582029</v>
+        <v>-0.7573</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.28778593316406</v>
+        <v>-15.146</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3080003992282433</v>
+        <v>0.5522</v>
       </c>
       <c r="J42" t="n">
-        <v>7.084009182249596</v>
+        <v>12.7006</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05305489615501338</v>
+        <v>0.3172</v>
       </c>
       <c r="J43" t="n">
-        <v>1.220262611565308</v>
+        <v>7.2956</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1794844117582529</v>
+        <v>-0.101</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.128141470439817</v>
+        <v>-2.323</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2431550947341235</v>
+        <v>-0.1993</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.592567178884841</v>
+        <v>-4.5839</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4998570865889195</v>
+        <v>-0.4977</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.49671299154515</v>
+        <v>-11.4471</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>1.543064866150516</v>
+        <v>1.2389</v>
       </c>
       <c r="J47" t="n">
-        <v>35.49049192146187</v>
+        <v>28.4947</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.03628467035888858</v>
+        <v>-0.0569</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.8345474182544372</v>
+        <v>-1.3087</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.04627895076833752</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.064415867671763</v>
+        <v>-2.0907</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1387481616136051</v>
+        <v>-0.2626</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.191207717112917</v>
+        <v>-6.0398</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2309693451666665</v>
+        <v>-0.3967</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.312294938833331</v>
+        <v>-9.1241</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.8</v>
       </c>
       <c r="I52" t="n">
-        <v>1.107309180056632</v>
+        <v>1.7898</v>
       </c>
       <c r="J52" t="n">
-        <v>26.57542032135917</v>
+        <v>42.9552</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.05</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0597977086870376</v>
+        <v>0.1497</v>
       </c>
       <c r="J53" t="n">
-        <v>1.435145008488902</v>
+        <v>3.5928</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.146836792453435</v>
+        <v>-0.4627</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.524083018882441</v>
+        <v>-11.1048</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1728177458417495</v>
+        <v>-0.5175</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.147625900201989</v>
+        <v>-12.42</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.79</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.276186990857348</v>
+        <v>-0.7206</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.628487780576354</v>
+        <v>-17.2944</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3253074590606502</v>
+        <v>0.4571</v>
       </c>
       <c r="J57" t="n">
-        <v>7.807379017455604</v>
+        <v>10.9704</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.16</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1655223511927557</v>
+        <v>0.328</v>
       </c>
       <c r="J58" t="n">
-        <v>3.972536428626136</v>
+        <v>7.872</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1126165672246291</v>
+        <v>0.2812</v>
       </c>
       <c r="J59" t="n">
-        <v>2.702797613391099</v>
+        <v>6.7488</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2260931139080582</v>
+        <v>-0.3369</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.426234733793396</v>
+        <v>-8.085599999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.58</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4775905316170377</v>
+        <v>-0.6686</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.46217275880891</v>
+        <v>-16.0464</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>2.11</v>
       </c>
       <c r="I62" t="n">
-        <v>1.42902103980886</v>
+        <v>1.9633</v>
       </c>
       <c r="J62" t="n">
-        <v>21.4353155971329</v>
+        <v>29.4495</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.75</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9562411517284652</v>
+        <v>1.5495</v>
       </c>
       <c r="J63" t="n">
-        <v>14.34361727592698</v>
+        <v>23.2425</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5213144816656161</v>
+        <v>0.8798</v>
       </c>
       <c r="J64" t="n">
-        <v>7.819717224984242</v>
+        <v>13.197</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>1.41</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4924334598988497</v>
+        <v>0.8374</v>
       </c>
       <c r="J65" t="n">
-        <v>7.386501898482746</v>
+        <v>12.561</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.95</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.14502413607531</v>
+        <v>-0.4064</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.175362041129649</v>
+        <v>-6.096</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1103156525376169</v>
+        <v>0.6069</v>
       </c>
       <c r="J67" t="n">
-        <v>1.654734788064253</v>
+        <v>9.1035</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>0.91</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3208811219326514</v>
+        <v>-0.0914</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.813216828989771</v>
+        <v>-1.371</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>0.63</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5808147908651008</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.712221862976511</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.57</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6386597316688758</v>
+        <v>-0.6403</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.579895975033137</v>
+        <v>-9.6045</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.46</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7426019166044466</v>
+        <v>-0.7786</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.1390287490667</v>
+        <v>-11.679</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.471002878090084</v>
+        <v>0.4694</v>
       </c>
       <c r="J72" t="n">
-        <v>10.36206331798185</v>
+        <v>10.3268</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4042456552671824</v>
+        <v>0.4149</v>
       </c>
       <c r="J73" t="n">
-        <v>8.893404415878011</v>
+        <v>9.127800000000001</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>1.22</v>
       </c>
       <c r="I74" t="n">
-        <v>0.370800807762688</v>
+        <v>0.3868</v>
       </c>
       <c r="J74" t="n">
-        <v>8.157617770779135</v>
+        <v>8.509600000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>1.06</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1244330550107213</v>
+        <v>0.1099</v>
       </c>
       <c r="J75" t="n">
-        <v>2.737527210235868</v>
+        <v>2.4178</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4555403466486054</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.02188762626932</v>
+        <v>-15.202</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.72</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9192840642480863</v>
+        <v>0.9858</v>
       </c>
       <c r="J77" t="n">
-        <v>20.2242494134579</v>
+        <v>21.6876</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.33</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3053551243957056</v>
+        <v>0.5405</v>
       </c>
       <c r="J78" t="n">
-        <v>6.717812736705524</v>
+        <v>11.891</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3439169959070165</v>
+        <v>-0.367</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.566173909954363</v>
+        <v>-8.074</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.451523405576133</v>
+        <v>-0.5039</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.933514922674927</v>
+        <v>-11.0858</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4830927425224859</v>
+        <v>-0.5425</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.62804033549469</v>
+        <v>-11.935</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3962081612751303</v>
+        <v>0.6373</v>
       </c>
       <c r="J82" t="n">
-        <v>7.924163225502606</v>
+        <v>12.746</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1486528001557159</v>
+        <v>-0.0014</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.973056003114319</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2359857216959845</v>
+        <v>-0.1658</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.719714433919691</v>
+        <v>-3.316</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5066238214565161</v>
+        <v>-0.5626</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.13247642913032</v>
+        <v>-11.252</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.54</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6261004825071214</v>
+        <v>-0.701</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.52200965014243</v>
+        <v>-14.02</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7750887355656219</v>
+        <v>1.1351</v>
       </c>
       <c r="J87" t="n">
-        <v>15.50177471131244</v>
+        <v>22.702</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5584151120990497</v>
+        <v>0.8546</v>
       </c>
       <c r="J88" t="n">
-        <v>11.16830224198099</v>
+        <v>17.092</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5082534696513739</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>10.16506939302748</v>
+        <v>15.696</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.07035243709925773</v>
+        <v>0.0102</v>
       </c>
       <c r="J90" t="n">
-        <v>1.407048741985155</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.05320091601815453</v>
+        <v>-0.3638</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.064018320363091</v>
+        <v>-7.276</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4420324473540293</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>13.26097342062088</v>
+        <v>18.372</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2147447758527275</v>
+        <v>0.4295</v>
       </c>
       <c r="J93" t="n">
-        <v>6.442343275581825</v>
+        <v>12.885</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>0.83</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2899514499755063</v>
+        <v>-0.3369</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.698543499265188</v>
+        <v>-10.107</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.83</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2899514499755063</v>
+        <v>-0.3369</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.698543499265188</v>
+        <v>-10.107</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.447036933247999</v>
+        <v>-0.5314</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.41110799743997</v>
+        <v>-15.942</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7860503664448253</v>
+        <v>1.3617</v>
       </c>
       <c r="J97" t="n">
-        <v>23.58151099334476</v>
+        <v>40.851</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4220993410202519</v>
+        <v>0.9085</v>
       </c>
       <c r="J98" t="n">
-        <v>12.66298023060756</v>
+        <v>27.255</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.18</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1486728030565372</v>
+        <v>0.4662</v>
       </c>
       <c r="J99" t="n">
-        <v>4.460184091696117</v>
+        <v>13.986</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.06516034811212937</v>
+        <v>0.0165</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.954810443363881</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.85</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2556664083472235</v>
+        <v>-0.6068</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.669992250416707</v>
+        <v>-18.204</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.71</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8885770317580156</v>
+        <v>1.5961</v>
       </c>
       <c r="J102" t="n">
-        <v>16.8829636034023</v>
+        <v>30.3259</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.46</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5766854632654682</v>
+        <v>1.1143</v>
       </c>
       <c r="J103" t="n">
-        <v>10.9570238020439</v>
+        <v>21.1717</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.29</v>
       </c>
       <c r="I104" t="n">
-        <v>0.355765099373559</v>
+        <v>0.7336</v>
       </c>
       <c r="J104" t="n">
-        <v>6.759536888097621</v>
+        <v>13.9384</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.07106386962615616</v>
+        <v>-0.3452</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.350213522896967</v>
+        <v>-6.5588</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.169230487547836</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.215379263408884</v>
+        <v>-11.3297</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.26</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1093562575125971</v>
+        <v>0.4902</v>
       </c>
       <c r="J107" t="n">
-        <v>2.077768892739346</v>
+        <v>9.313800000000001</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1.22</v>
       </c>
       <c r="I108" t="n">
-        <v>0.05933580499263279</v>
+        <v>0.4353</v>
       </c>
       <c r="J108" t="n">
-        <v>1.127380294860023</v>
+        <v>8.2707</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.96</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2449292943504591</v>
+        <v>-0.0696</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.653656592658724</v>
+        <v>-1.3224</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.68</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5476530179684761</v>
+        <v>-0.5336</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.40540734140105</v>
+        <v>-10.1384</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.55</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6874575528683677</v>
+        <v>-0.6965</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.06169350449899</v>
+        <v>-13.2335</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>1.094484834686376</v>
+        <v>1.7831</v>
       </c>
       <c r="J112" t="n">
-        <v>17.51175735498201</v>
+        <v>28.5296</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.5</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6217005089659335</v>
+        <v>1.1037</v>
       </c>
       <c r="J113" t="n">
-        <v>9.947208143454937</v>
+        <v>17.6592</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>1.41</v>
       </c>
       <c r="I114" t="n">
-        <v>0.522039875571225</v>
+        <v>0.8828</v>
       </c>
       <c r="J114" t="n">
-        <v>8.3526380091396</v>
+        <v>14.1248</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>1.32</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4103855010836047</v>
+        <v>0.679</v>
       </c>
       <c r="J115" t="n">
-        <v>6.566168017337676</v>
+        <v>10.864</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>1.07</v>
       </c>
       <c r="I116" t="n">
-        <v>0.08781212163888308</v>
+        <v>0.0694</v>
       </c>
       <c r="J116" t="n">
-        <v>1.404993946222129</v>
+        <v>1.1104</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.3099107627345517</v>
+        <v>-0.1668</v>
       </c>
       <c r="J117" t="n">
-        <v>-4.958572203752827</v>
+        <v>-2.6688</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>0.78</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3759611963558867</v>
+        <v>-0.2629</v>
       </c>
       <c r="J118" t="n">
-        <v>-6.015379141694186</v>
+        <v>-4.2064</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>0.78</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3759611963558867</v>
+        <v>-0.2629</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.015379141694186</v>
+        <v>-4.2064</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.54</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6204431413319995</v>
+        <v>-0.6541</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.927090261311992</v>
+        <v>-10.4656</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.684619796903269</v>
+        <v>-0.7337</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.9539167504523</v>
+        <v>-11.7392</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.37</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5653099930629283</v>
+        <v>1.0027</v>
       </c>
       <c r="J122" t="n">
-        <v>12.43681984738442</v>
+        <v>22.0594</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3181144871028885</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>6.998518716263548</v>
+        <v>13.3166</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2053215420859535</v>
+        <v>0.3805</v>
       </c>
       <c r="J124" t="n">
-        <v>4.517073925890978</v>
+        <v>8.371</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.04801452368650089</v>
+        <v>-0.3851</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.05631952110302</v>
+        <v>-8.472200000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.0684249070791675</v>
+        <v>-0.4432</v>
       </c>
       <c r="J126" t="n">
-        <v>-1.505347955741685</v>
+        <v>-9.750400000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.11</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0435472610436419</v>
+        <v>0.2651</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9580397429601217</v>
+        <v>5.8322</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.06731295186602844</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.480884941052626</v>
+        <v>1.4982</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.138220461771641</v>
+        <v>-0.15</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.040850158976103</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.165964632320819</v>
+        <v>-0.208</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.651221911058018</v>
+        <v>-4.576</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.78</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2847444598927599</v>
+        <v>-0.3991</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.264378117640718</v>
+        <v>-8.780200000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.89</v>
       </c>
       <c r="I132" t="n">
-        <v>1.180470256200527</v>
+        <v>1.8646</v>
       </c>
       <c r="J132" t="n">
-        <v>34.2336374298153</v>
+        <v>54.0734</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.09586137379431059</v>
+        <v>0.2233</v>
       </c>
       <c r="J133" t="n">
-        <v>2.779979840035007</v>
+        <v>6.4757</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0122064444890953</v>
+        <v>-0.0888</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.3539868901837636</v>
+        <v>-2.5752</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.04098839695062601</v>
+        <v>-0.2291</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.188663511568154</v>
+        <v>-6.6439</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3670333253284511</v>
+        <v>-1.0453</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.64396643452508</v>
+        <v>-30.3137</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.55</v>
       </c>
       <c r="I137" t="n">
-        <v>0.666574662402545</v>
+        <v>0.826</v>
       </c>
       <c r="J137" t="n">
-        <v>19.33066520967381</v>
+        <v>23.954</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0003034757718222979</v>
+        <v>0.2168</v>
       </c>
       <c r="J138" t="n">
-        <v>0.008800797382846639</v>
+        <v>6.2872</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1276551772601772</v>
+        <v>-0.1284</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.702000140545139</v>
+        <v>-3.7236</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.89</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1860260173738194</v>
+        <v>-0.2397</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.394754503840763</v>
+        <v>-6.9513</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.44</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6146321434243396</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.82433215930585</v>
+        <v>-24.0729</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5544688057907569</v>
+        <v>1.3806</v>
       </c>
       <c r="J142" t="n">
-        <v>15.52512656214119</v>
+        <v>38.6568</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.46</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4469018128438422</v>
+        <v>1.1624</v>
       </c>
       <c r="J143" t="n">
-        <v>12.51325075962758</v>
+        <v>32.5472</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>1.38</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3659649462629264</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="J144" t="n">
-        <v>10.24701849536194</v>
+        <v>27.846</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.86</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1751342737882962</v>
+        <v>-0.5703</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.903759666072292</v>
+        <v>-15.9684</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5490609439152838</v>
+        <v>-1.3163</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.37370642962795</v>
+        <v>-36.8564</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.66</v>
       </c>
       <c r="I147" t="n">
-        <v>0.656919952222806</v>
+        <v>0.9537</v>
       </c>
       <c r="J147" t="n">
-        <v>18.39375866223857</v>
+        <v>26.7036</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.09111104456474714</v>
+        <v>0.0599</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.55110924781292</v>
+        <v>1.6772</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>0.79</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2878817828977721</v>
+        <v>-0.3893</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.060689921137618</v>
+        <v>-10.9004</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>0.71</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.362491770859367</v>
+        <v>-0.5001</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.14976958406228</v>
+        <v>-14.0028</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4173063952479226</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.68457906694183</v>
+        <v>-16.1868</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.72</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6833047086474073</v>
+        <v>1.692</v>
       </c>
       <c r="J152" t="n">
-        <v>16.39931300753778</v>
+        <v>40.608</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2882267293414094</v>
+        <v>0.8722</v>
       </c>
       <c r="J153" t="n">
-        <v>6.917441504193825</v>
+        <v>20.9328</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>0.88</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1590061861327447</v>
+        <v>-0.4972</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.816148467185873</v>
+        <v>-11.9328</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2525418879774966</v>
+        <v>-0.702</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.061005311459919</v>
+        <v>-16.848</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2756775485593672</v>
+        <v>-0.7499</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.616261165424813</v>
+        <v>-17.9976</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.28</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2653261303478395</v>
+        <v>0.498</v>
       </c>
       <c r="J157" t="n">
-        <v>6.367827128348147</v>
+        <v>11.952</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>1.24</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2148987751565815</v>
+        <v>0.4441</v>
       </c>
       <c r="J158" t="n">
-        <v>5.157570603757956</v>
+        <v>10.6584</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>1.15</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1009490906778675</v>
+        <v>0.3134</v>
       </c>
       <c r="J159" t="n">
-        <v>2.422778176268821</v>
+        <v>7.5216</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.65</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3786619031467328</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.087885675521587</v>
+        <v>-13.9728</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4056593459482015</v>
+        <v>-0.6196</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.735824302756836</v>
+        <v>-14.8704</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7106747633047414</v>
+        <v>0.842</v>
       </c>
       <c r="J162" t="n">
-        <v>11.37079621287586</v>
+        <v>13.472</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.69</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6998771346632938</v>
+        <v>0.8312</v>
       </c>
       <c r="J163" t="n">
-        <v>11.1980341546127</v>
+        <v>13.2992</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.63</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6349021967475199</v>
+        <v>0.7653</v>
       </c>
       <c r="J164" t="n">
-        <v>10.15843514796032</v>
+        <v>12.2448</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>1.52</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5207918338142064</v>
+        <v>0.6319</v>
       </c>
       <c r="J165" t="n">
-        <v>8.332669341027302</v>
+        <v>10.1104</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.01961465994169275</v>
+        <v>-0.0621</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.3138345590670841</v>
+        <v>-0.9936</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>0.85</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.3347438557886573</v>
+        <v>-0.1311</v>
       </c>
       <c r="J167" t="n">
-        <v>-5.355901692618517</v>
+        <v>-2.0976</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>0.78</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.4232721127139097</v>
+        <v>-0.2426</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.772353803422556</v>
+        <v>-3.8816</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4358436847599508</v>
+        <v>-0.2583</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.973498956159213</v>
+        <v>-4.1328</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.45</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.8131420643445648</v>
+        <v>-0.7623</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.01027302951304</v>
+        <v>-12.1968</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.38</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8976798065388862</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.36287690462218</v>
+        <v>-13.6208</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>0.86</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.189716712203514</v>
+        <v>-0.132</v>
       </c>
       <c r="J172" t="n">
-        <v>-3.414900819663253</v>
+        <v>-2.376</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1999423430740944</v>
+        <v>-0.1485</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.598962175333698</v>
+        <v>-2.673</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>0.71</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.339176970893062</v>
+        <v>-0.3744</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.105185476075117</v>
+        <v>-6.7392</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.52</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.515848717525355</v>
+        <v>-0.6798</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.285276915456389</v>
+        <v>-12.2364</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5746844216049489</v>
+        <v>-0.7584</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.34431958888908</v>
+        <v>-13.6512</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.69</v>
       </c>
       <c r="I177" t="n">
-        <v>0.595042603186885</v>
+        <v>1.5198</v>
       </c>
       <c r="J177" t="n">
-        <v>10.71076685736393</v>
+        <v>27.3564</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3715551329086141</v>
+        <v>0.9837</v>
       </c>
       <c r="J178" t="n">
-        <v>6.687992392355054</v>
+        <v>17.7066</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1.27</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2551827574675801</v>
+        <v>0.6073</v>
       </c>
       <c r="J179" t="n">
-        <v>4.593289634416442</v>
+        <v>10.9314</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2467346728613209</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>4.441224111503777</v>
+        <v>10.4976</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>1.07</v>
       </c>
       <c r="I181" t="n">
-        <v>0.08164479695615398</v>
+        <v>0.0953</v>
       </c>
       <c r="J181" t="n">
-        <v>1.469606345210772</v>
+        <v>1.7154</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3584754126741043</v>
+        <v>0.6422</v>
       </c>
       <c r="J182" t="n">
-        <v>8.603409904178504</v>
+        <v>15.4128</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.04450858260262517</v>
+        <v>0.2756</v>
       </c>
       <c r="J183" t="n">
-        <v>1.068205982463004</v>
+        <v>6.6144</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.06003922469170607</v>
+        <v>0.0578</v>
       </c>
       <c r="J184" t="n">
-        <v>-1.440941392600946</v>
+        <v>1.3872</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.83</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2654464195124885</v>
+        <v>-0.3507</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.370714068299724</v>
+        <v>-8.4168</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2654464195124885</v>
+        <v>-0.3507</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.370714068299724</v>
+        <v>-8.4168</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.41</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3405982919390467</v>
+        <v>1.1097</v>
       </c>
       <c r="J187" t="n">
-        <v>8.17435900653712</v>
+        <v>26.6328</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.31</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2533104873959298</v>
+        <v>0.8923</v>
       </c>
       <c r="J188" t="n">
-        <v>6.079451697502316</v>
+        <v>21.4152</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.03778107928656281</v>
+        <v>0.2061</v>
       </c>
       <c r="J189" t="n">
-        <v>0.9067459028775074</v>
+        <v>4.9464</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.9</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1431334768606086</v>
+        <v>-0.4268</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.435203444654606</v>
+        <v>-10.2432</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4930240793592605</v>
+        <v>-1.0752</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.83257790462225</v>
+        <v>-25.8048</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>2.14</v>
       </c>
       <c r="I192" t="n">
-        <v>1.165440948328676</v>
+        <v>2.0593</v>
       </c>
       <c r="J192" t="n">
-        <v>25.63970086323086</v>
+        <v>45.3046</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.27</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2330303469267976</v>
+        <v>0.697</v>
       </c>
       <c r="J193" t="n">
-        <v>5.126667632389546</v>
+        <v>15.334</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.04030258189409126</v>
+        <v>0.2205</v>
       </c>
       <c r="J194" t="n">
-        <v>0.8866568016700076</v>
+        <v>4.851</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.92</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1415760994086789</v>
+        <v>-0.4298</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.114674186990936</v>
+        <v>-9.4556</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.74</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3139374306737737</v>
+        <v>-0.8747</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.906623474823022</v>
+        <v>-19.2434</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.24</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1456663570301502</v>
+        <v>0.4538</v>
       </c>
       <c r="J197" t="n">
-        <v>3.204659854663304</v>
+        <v>9.983599999999999</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.21</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1092071553140993</v>
+        <v>0.4119</v>
       </c>
       <c r="J198" t="n">
-        <v>2.402557416910184</v>
+        <v>9.0618</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.85</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2332991504779248</v>
+        <v>-0.2975</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.132581310514347</v>
+        <v>-6.545</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2420331364747425</v>
+        <v>-0.3132</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.324729002444336</v>
+        <v>-6.8904</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3973535799796344</v>
+        <v>-0.5646</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.741778759551956</v>
+        <v>-12.4212</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.93</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9763994500260398</v>
+        <v>1.9715</v>
       </c>
       <c r="J202" t="n">
-        <v>21.48078790057287</v>
+        <v>43.373</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.34</v>
       </c>
       <c r="I203" t="n">
-        <v>0.324507575063742</v>
+        <v>0.8862</v>
       </c>
       <c r="J203" t="n">
-        <v>7.139166651402324</v>
+        <v>19.4964</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.03667775942505917</v>
+        <v>0.2089</v>
       </c>
       <c r="J204" t="n">
-        <v>0.8069107073513018</v>
+        <v>4.5958</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.98</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.07533633866900419</v>
+        <v>-0.2222</v>
       </c>
       <c r="J205" t="n">
-        <v>-1.657399450718092</v>
+        <v>-4.8884</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4015635591382311</v>
+        <v>-1.0815</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.834398301041084</v>
+        <v>-23.793</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.38</v>
       </c>
       <c r="I207" t="n">
-        <v>0.281101581930595</v>
+        <v>0.6128</v>
       </c>
       <c r="J207" t="n">
-        <v>6.184234802473091</v>
+        <v>13.4816</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.33</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2158647544319579</v>
+        <v>0.5503</v>
       </c>
       <c r="J208" t="n">
-        <v>4.749024597503074</v>
+        <v>12.1066</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1679768884418557</v>
+        <v>-0.1248</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.695491545720825</v>
+        <v>-2.7456</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2911987046255482</v>
+        <v>-0.3605</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.40637150176206</v>
+        <v>-7.931</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.64</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4446288787648134</v>
+        <v>-0.6006</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.781835332825896</v>
+        <v>-13.2132</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.88</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7126447187253984</v>
+        <v>1.1383</v>
       </c>
       <c r="J212" t="n">
-        <v>17.10347324940956</v>
+        <v>27.3192</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.12</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.04195634195832924</v>
+        <v>0.2257</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.006952206999902</v>
+        <v>5.4168</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2586365597141542</v>
+        <v>-0.218</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.207277433139701</v>
+        <v>-5.232</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4173914460619694</v>
+        <v>-0.4293</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.01739470548726</v>
+        <v>-10.3032</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.74</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4614876599801401</v>
+        <v>-0.4829</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.07570383952336</v>
+        <v>-11.5896</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.69</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5104387818718517</v>
+        <v>1.598</v>
       </c>
       <c r="J217" t="n">
-        <v>12.25053076492444</v>
+        <v>38.352</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.37</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2322108228556124</v>
+        <v>0.9644</v>
       </c>
       <c r="J218" t="n">
-        <v>5.573059748534698</v>
+        <v>23.1456</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.27</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1403639274495344</v>
+        <v>0.7357</v>
       </c>
       <c r="J219" t="n">
-        <v>3.368734258788825</v>
+        <v>17.6568</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>1.04</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.07635662933685766</v>
+        <v>0.0611</v>
       </c>
       <c r="J220" t="n">
-        <v>-1.832559104084584</v>
+        <v>1.4664</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.5</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7393566992855014</v>
+        <v>-1.3573</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.74456078285203</v>
+        <v>-32.5752</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.56</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5261613787394998</v>
+        <v>0.7935</v>
       </c>
       <c r="J222" t="n">
-        <v>22.09877790705899</v>
+        <v>33.327</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1097882689415553</v>
+        <v>0.279</v>
       </c>
       <c r="J223" t="n">
-        <v>4.611107295545324</v>
+        <v>11.718</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>1.14</v>
       </c>
       <c r="I224" t="n">
-        <v>0.09003934450521087</v>
+        <v>0.2451</v>
       </c>
       <c r="J224" t="n">
-        <v>3.781652469218856</v>
+        <v>10.2942</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.03656239297274384</v>
+        <v>-0.0174</v>
       </c>
       <c r="J225" t="n">
-        <v>-1.535620504855241</v>
+        <v>-0.7308</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.73</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3530707677909353</v>
+        <v>-0.5008</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.82897224721928</v>
+        <v>-21.0336</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.34</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2196988174774492</v>
+        <v>0.5649</v>
       </c>
       <c r="J227" t="n">
-        <v>9.227350334052867</v>
+        <v>23.7258</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.13</v>
       </c>
       <c r="I228" t="n">
-        <v>0.02919451681308467</v>
+        <v>0.2701</v>
       </c>
       <c r="J228" t="n">
-        <v>1.226169706149556</v>
+        <v>11.3442</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>0.95</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1712480022989706</v>
+        <v>-0.143</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.192416096556764</v>
+        <v>-6.006</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3011420133032436</v>
+        <v>-0.3142</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.64796455873623</v>
+        <v>-13.1964</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3271673736549982</v>
+        <v>-0.3444</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.74102969350992</v>
+        <v>-14.4648</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.14</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.05191675764155924</v>
+        <v>0.3333</v>
       </c>
       <c r="J232" t="n">
-        <v>-0.9864183951896255</v>
+        <v>6.3327</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.13</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.06334044709598542</v>
+        <v>0.3177</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.203468494823723</v>
+        <v>6.0363</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>0.85</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3662788716342772</v>
+        <v>-0.2719</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.959298561051266</v>
+        <v>-5.1661</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>0.72</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5083614629028318</v>
+        <v>-0.4697</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.658867795153805</v>
+        <v>-8.924300000000001</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6171637764134724</v>
+        <v>-0.6026</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.72611175185598</v>
+        <v>-11.4494</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.76</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5802534050775608</v>
+        <v>1.6284</v>
       </c>
       <c r="J237" t="n">
-        <v>11.02481469647366</v>
+        <v>30.9396</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.6</v>
       </c>
       <c r="I238" t="n">
-        <v>0.4444174758410732</v>
+        <v>1.3319</v>
       </c>
       <c r="J238" t="n">
-        <v>8.443932040980391</v>
+        <v>25.3061</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>1.43</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2958354186340984</v>
+        <v>0.9813</v>
       </c>
       <c r="J239" t="n">
-        <v>5.620872954047869</v>
+        <v>18.6447</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>1.38</v>
       </c>
       <c r="I240" t="n">
-        <v>0.2574217386920566</v>
+        <v>0.8514</v>
       </c>
       <c r="J240" t="n">
-        <v>4.891013035149077</v>
+        <v>16.1766</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4107227002433642</v>
+        <v>-0.8794</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.80373130462392</v>
+        <v>-16.7086</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>2.3</v>
       </c>
       <c r="I242" t="n">
-        <v>1.127358685194239</v>
+        <v>1.4155</v>
       </c>
       <c r="J242" t="n">
-        <v>18.03773896310782</v>
+        <v>22.648</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.7</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6012422332050091</v>
+        <v>0.8405</v>
       </c>
       <c r="J243" t="n">
-        <v>9.619875731280146</v>
+        <v>13.448</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>1.65</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5525613037067308</v>
+        <v>0.786</v>
       </c>
       <c r="J244" t="n">
-        <v>8.840980859307694</v>
+        <v>12.576</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0002391785837347371</v>
+        <v>0.0457</v>
       </c>
       <c r="J245" t="n">
-        <v>-0.003826857339755794</v>
+        <v>0.7312</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.86</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2381050200491799</v>
+        <v>-0.3719</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.809680320786879</v>
+        <v>-5.9504</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.08</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1191797597891787</v>
+        <v>0.2881</v>
       </c>
       <c r="J247" t="n">
-        <v>-1.906876156626859</v>
+        <v>4.6096</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>0.9</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.300928996320065</v>
+        <v>-0.1036</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.81486394112104</v>
+        <v>-1.6576</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>0.86</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3409406782285824</v>
+        <v>-0.1721</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.455050851657318</v>
+        <v>-2.7536</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>0.54</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.6413705465638222</v>
+        <v>-0.6762</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.26192874502116</v>
+        <v>-10.8192</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.43</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7457930126981177</v>
+        <v>-0.8127</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.93268820316988</v>
+        <v>-13.0032</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I252" t="n">
-        <v>0.1181434814641129</v>
+        <v>0.3285</v>
       </c>
       <c r="J252" t="n">
-        <v>2.835443555138711</v>
+        <v>7.884</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.02004126849441384</v>
+        <v>0.068</v>
       </c>
       <c r="J253" t="n">
-        <v>-0.4809904438659321</v>
+        <v>1.632</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.135088159030684</v>
+        <v>-0.1527</v>
       </c>
       <c r="J254" t="n">
-        <v>-3.242115816736416</v>
+        <v>-3.6648</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>0.68</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3748694732524926</v>
+        <v>-0.5173</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.996867358059822</v>
+        <v>-12.4152</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.61</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4540396773607709</v>
+        <v>-0.6096</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.8969522566585</v>
+        <v>-14.6304</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.56</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5413619522097683</v>
+        <v>1.3278</v>
       </c>
       <c r="J257" t="n">
-        <v>12.99268685303444</v>
+        <v>31.8672</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>1.52</v>
       </c>
       <c r="I258" t="n">
-        <v>0.497555403124842</v>
+        <v>1.2493</v>
       </c>
       <c r="J258" t="n">
-        <v>11.94132967499621</v>
+        <v>29.9832</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>1.16</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1013449240949314</v>
+        <v>0.39</v>
       </c>
       <c r="J259" t="n">
-        <v>2.432278178278354</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>1.06</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.01369826336818046</v>
+        <v>0.1048</v>
       </c>
       <c r="J260" t="n">
-        <v>-0.3287583208363311</v>
+        <v>2.5152</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.83</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2462236381411815</v>
+        <v>-0.6641</v>
       </c>
       <c r="J261" t="n">
-        <v>-5.909367315388357</v>
+        <v>-15.9384</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.62</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4737809635219524</v>
+        <v>0.8838</v>
       </c>
       <c r="J262" t="n">
-        <v>10.89696216100491</v>
+        <v>20.3274</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.36</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2192666029181769</v>
+        <v>0.5828</v>
       </c>
       <c r="J263" t="n">
-        <v>5.04313186711807</v>
+        <v>13.4044</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3063721790703281</v>
+        <v>-0.2886</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.046560118617546</v>
+        <v>-6.6378</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>0.71</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4904859232776829</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.28117623538671</v>
+        <v>-11.8358</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.65</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5569896035086771</v>
+        <v>-0.5906</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.81076088069957</v>
+        <v>-13.5838</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.44</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4239223075595703</v>
+        <v>1.1171</v>
       </c>
       <c r="J267" t="n">
-        <v>9.750213073870116</v>
+        <v>25.6933</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3663780050774363</v>
+        <v>1.0118</v>
       </c>
       <c r="J268" t="n">
-        <v>8.426694116781034</v>
+        <v>23.2714</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>1.11</v>
       </c>
       <c r="I269" t="n">
-        <v>0.05307385739997991</v>
+        <v>0.2841</v>
       </c>
       <c r="J269" t="n">
-        <v>1.220698720199538</v>
+        <v>6.5343</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.04160856249368204</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.9569969373546869</v>
+        <v>-0.2024</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.87</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1970900228758321</v>
+        <v>-0.5467</v>
       </c>
       <c r="J271" t="n">
-        <v>-4.533070526144138</v>
+        <v>-12.5741</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>2.75</v>
       </c>
       <c r="I272" t="n">
-        <v>1.209693490043822</v>
+        <v>2.0593</v>
       </c>
       <c r="J272" t="n">
-        <v>15.72601537056968</v>
+        <v>26.7709</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>2.27</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8939846786885275</v>
+        <v>2.0593</v>
       </c>
       <c r="J273" t="n">
-        <v>11.62180082295086</v>
+        <v>26.7709</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.65</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4214323769362066</v>
+        <v>1.2161</v>
       </c>
       <c r="J274" t="n">
-        <v>5.478620900170686</v>
+        <v>15.8093</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>1.25</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1024263526552875</v>
+        <v>0.4339</v>
       </c>
       <c r="J275" t="n">
-        <v>1.331542584518737</v>
+        <v>5.6407</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>1.07</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.05032130782091672</v>
+        <v>0.0037</v>
       </c>
       <c r="J276" t="n">
-        <v>-0.6541770016719174</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>0.59</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.4686235610358974</v>
+        <v>-0.4233</v>
       </c>
       <c r="J277" t="n">
-        <v>-6.092106293466666</v>
+        <v>-5.5029</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>0.54</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.5111556409968454</v>
+        <v>-0.5018</v>
       </c>
       <c r="J278" t="n">
-        <v>-6.64502333295899</v>
+        <v>-6.5234</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.44</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5863090682121272</v>
+        <v>-0.6945</v>
       </c>
       <c r="J279" t="n">
-        <v>-7.622017886757654</v>
+        <v>-9.028499999999999</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.39</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.6265527307357647</v>
+        <v>-0.7764</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.14518549956494</v>
+        <v>-10.0932</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.37</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6432289193991094</v>
+        <v>-0.8068</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.361975952188423</v>
+        <v>-10.4884</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>1.93</v>
       </c>
       <c r="I282" t="n">
-        <v>0.7439183763429951</v>
+        <v>1.8915</v>
       </c>
       <c r="J282" t="n">
-        <v>12.64661239783092</v>
+        <v>32.1555</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>1.57</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4570330674746033</v>
+        <v>1.2443</v>
       </c>
       <c r="J283" t="n">
-        <v>7.769562147068255</v>
+        <v>21.1531</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>1.29</v>
       </c>
       <c r="I284" t="n">
-        <v>0.23344235321285</v>
+        <v>0.6086</v>
       </c>
       <c r="J284" t="n">
-        <v>3.968520004618449</v>
+        <v>10.3462</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>1.28</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2248621377613356</v>
+        <v>0.5861</v>
       </c>
       <c r="J285" t="n">
-        <v>3.822656341942706</v>
+        <v>9.963699999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>1.16</v>
       </c>
       <c r="I286" t="n">
-        <v>0.1218148675802477</v>
+        <v>0.3052</v>
       </c>
       <c r="J286" t="n">
-        <v>2.070852748864212</v>
+        <v>5.1884</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>0.74</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.3042113390419635</v>
+        <v>-0.3053</v>
       </c>
       <c r="J287" t="n">
-        <v>-5.171592763713379</v>
+        <v>-5.1901</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>0.7</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3394328260307651</v>
+        <v>-0.3689</v>
       </c>
       <c r="J288" t="n">
-        <v>-5.770358042523006</v>
+        <v>-6.2713</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>0.68</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3563918724519611</v>
+        <v>-0.4019</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.058661831683339</v>
+        <v>-6.8323</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.62</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.401395539040458</v>
+        <v>-0.5187</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.823724163687785</v>
+        <v>-8.8179</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.49</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5140115967361479</v>
+        <v>-0.7093</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.738197144514515</v>
+        <v>-12.0581</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>2.18</v>
       </c>
       <c r="I292" t="n">
-        <v>1.039382457027169</v>
+        <v>2.0593</v>
       </c>
       <c r="J292" t="n">
-        <v>20.78764914054339</v>
+        <v>41.186</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>1.61</v>
       </c>
       <c r="I293" t="n">
-        <v>0.5227490946540736</v>
+        <v>1.3628</v>
       </c>
       <c r="J293" t="n">
-        <v>10.45498189308147</v>
+        <v>27.256</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1314671244335803</v>
+        <v>0.4801</v>
       </c>
       <c r="J294" t="n">
-        <v>2.629342488671607</v>
+        <v>9.602</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.05659151601273749</v>
+        <v>0.3074</v>
       </c>
       <c r="J295" t="n">
-        <v>1.13183032025475</v>
+        <v>6.148</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>0.63</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4952485300735588</v>
+        <v>-1.1267</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.904970601471176</v>
+        <v>-22.534</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>1.37</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2349429632522416</v>
+        <v>0.6422</v>
       </c>
       <c r="J297" t="n">
-        <v>4.698859265044833</v>
+        <v>12.844</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>0.91</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2497239067742464</v>
+        <v>-0.1598</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.994478135484927</v>
+        <v>-3.196</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>0.86</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2918928439007665</v>
+        <v>-0.261</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.83785687801533</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>0.8</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3489241118359507</v>
+        <v>-0.3577</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.978482236719015</v>
+        <v>-7.154</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>0.59</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5489406593644828</v>
+        <v>-0.6431</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.97881318728966</v>
+        <v>-12.862</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>1.09</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.05001181113708268</v>
+        <v>0.2639</v>
       </c>
       <c r="J302" t="n">
-        <v>-0.9502244116045709</v>
+        <v>5.0141</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.243928870900479</v>
+        <v>-0.114</v>
       </c>
       <c r="J303" t="n">
-        <v>-4.634648547109101</v>
+        <v>-2.166</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.265560592758607</v>
+        <v>-0.1516</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.045651262413533</v>
+        <v>-2.8804</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>0.74</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4315003758531534</v>
+        <v>-0.4326</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.198507141209914</v>
+        <v>-8.2194</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.66</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5202789164854335</v>
+        <v>-0.5438</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.885299413223235</v>
+        <v>-10.3322</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>1.61</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6961579836253069</v>
+        <v>0.8031</v>
       </c>
       <c r="J307" t="n">
-        <v>13.22700168888083</v>
+        <v>15.2589</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>1.38</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4291554650322652</v>
+        <v>0.5336</v>
       </c>
       <c r="J308" t="n">
-        <v>8.15395383561304</v>
+        <v>10.1384</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>1.22</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2539061922592215</v>
+        <v>0.2964</v>
       </c>
       <c r="J309" t="n">
-        <v>4.824217652925209</v>
+        <v>5.6316</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>1.11</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1213550992945248</v>
+        <v>0.1316</v>
       </c>
       <c r="J310" t="n">
-        <v>2.305746886595971</v>
+        <v>2.5004</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>1.09</v>
       </c>
       <c r="I311" t="n">
-        <v>0.09693229907532945</v>
+        <v>0.0994</v>
       </c>
       <c r="J311" t="n">
-        <v>1.84171368243126</v>
+        <v>1.8886</v>
       </c>
     </row>
     <row r="312">
@@ -14841,10 +14829,10 @@
         <v>1.42</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4266662088065616</v>
+        <v>1.0765</v>
       </c>
       <c r="J312" t="n">
-        <v>9.386656593744355</v>
+        <v>23.683</v>
       </c>
     </row>
     <row r="313">
@@ -14881,10 +14869,10 @@
         <v>1.21</v>
       </c>
       <c r="I313" t="n">
-        <v>0.2067296021174072</v>
+        <v>0.5906</v>
       </c>
       <c r="J313" t="n">
-        <v>4.548051246582959</v>
+        <v>12.9932</v>
       </c>
     </row>
     <row r="314">
@@ -14921,10 +14909,10 @@
         <v>1.19</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1868157983971131</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J314" t="n">
-        <v>4.109947564736488</v>
+        <v>11.7876</v>
       </c>
     </row>
     <row r="315">
@@ -14961,10 +14949,10 @@
         <v>1.14</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1421529518869113</v>
+        <v>0.3743</v>
       </c>
       <c r="J315" t="n">
-        <v>3.127364941512049</v>
+        <v>8.2346</v>
       </c>
     </row>
     <row r="316">
@@ -15001,10 +14989,10 @@
         <v>0.86</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1597175735476951</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J316" t="n">
-        <v>-3.513786618049291</v>
+        <v>-12.5862</v>
       </c>
     </row>
     <row r="317">
@@ -15041,10 +15029,10 @@
         <v>1.11</v>
       </c>
       <c r="I317" t="n">
-        <v>0.04215230785486362</v>
+        <v>0.2764</v>
       </c>
       <c r="J317" t="n">
-        <v>0.9273507728069996</v>
+        <v>6.0808</v>
       </c>
     </row>
     <row r="318">
@@ -15081,10 +15069,10 @@
         <v>1.01</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.06538163871571377</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.438396051745703</v>
+        <v>1.7842</v>
       </c>
     </row>
     <row r="319">
@@ -15121,10 +15109,10 @@
         <v>0.9</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1658512971641874</v>
+        <v>-0.1928</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.648728537612123</v>
+        <v>-4.2416</v>
       </c>
     </row>
     <row r="320">
@@ -15161,10 +15149,10 @@
         <v>0.82</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2419539157752147</v>
+        <v>-0.3303</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.322986147054724</v>
+        <v>-7.2666</v>
       </c>
     </row>
     <row r="321">
@@ -15201,10 +15189,10 @@
         <v>0.74</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3210017563409374</v>
+        <v>-0.4481</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.062038639500622</v>
+        <v>-9.8582</v>
       </c>
     </row>
     <row r="322">
@@ -15241,10 +15229,10 @@
         <v>1.91</v>
       </c>
       <c r="I322" t="n">
-        <v>0.7223150385774522</v>
+        <v>1.869</v>
       </c>
       <c r="J322" t="n">
-        <v>13.00167069439414</v>
+        <v>33.642</v>
       </c>
     </row>
     <row r="323">
@@ -15281,10 +15269,10 @@
         <v>1.69</v>
       </c>
       <c r="I323" t="n">
-        <v>0.5441406861598514</v>
+        <v>1.4833</v>
       </c>
       <c r="J323" t="n">
-        <v>9.794532350877326</v>
+        <v>26.6994</v>
       </c>
     </row>
     <row r="324">
@@ -15321,10 +15309,10 @@
         <v>1.52</v>
       </c>
       <c r="I324" t="n">
-        <v>0.398406228669784</v>
+        <v>1.1524</v>
       </c>
       <c r="J324" t="n">
-        <v>7.171312116056112</v>
+        <v>20.7432</v>
       </c>
     </row>
     <row r="325">
@@ -15361,10 +15349,10 @@
         <v>1.1</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0394155866963826</v>
+        <v>0.1563</v>
       </c>
       <c r="J325" t="n">
-        <v>0.7094805605348868</v>
+        <v>2.8134</v>
       </c>
     </row>
     <row r="326">
@@ -15401,10 +15389,10 @@
         <v>0.91</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.1793621696828529</v>
+        <v>-0.5026</v>
       </c>
       <c r="J326" t="n">
-        <v>-3.228519054291352</v>
+        <v>-9.046799999999999</v>
       </c>
     </row>
     <row r="327">
@@ -15441,10 +15429,10 @@
         <v>1.08</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.03471073349017575</v>
+        <v>0.2934</v>
       </c>
       <c r="J327" t="n">
-        <v>-0.6247932028231635</v>
+        <v>5.2812</v>
       </c>
     </row>
     <row r="328">
@@ -15481,10 +15469,10 @@
         <v>1.04</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.06912511035187663</v>
+        <v>0.219</v>
       </c>
       <c r="J328" t="n">
-        <v>-1.244251986333779</v>
+        <v>3.942</v>
       </c>
     </row>
     <row r="329">
@@ -15521,10 +15509,10 @@
         <v>0.66</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3822360547883816</v>
+        <v>-0.5092</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.880248986190868</v>
+        <v>-9.1656</v>
       </c>
     </row>
     <row r="330">
@@ -15561,10 +15549,10 @@
         <v>0.54</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4822114456167207</v>
+        <v>-0.6732</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.679806021100973</v>
+        <v>-12.1176</v>
       </c>
     </row>
     <row r="331">
@@ -15601,10 +15589,10 @@
         <v>0.43</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5718286083923668</v>
+        <v>-0.8105</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.2929149510626</v>
+        <v>-14.589</v>
       </c>
     </row>
     <row r="332">
@@ -15641,10 +15629,10 @@
         <v>1.36</v>
       </c>
       <c r="I332" t="n">
-        <v>0.2584168366775194</v>
+        <v>0.9124</v>
       </c>
       <c r="J332" t="n">
-        <v>5.943587243582945</v>
+        <v>20.9852</v>
       </c>
     </row>
     <row r="333">
@@ -15681,10 +15669,10 @@
         <v>1.32</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2226513252767139</v>
+        <v>0.8213</v>
       </c>
       <c r="J333" t="n">
-        <v>5.120980481364419</v>
+        <v>18.8899</v>
       </c>
     </row>
     <row r="334">
@@ -15721,10 +15709,10 @@
         <v>1.32</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2226513252767139</v>
+        <v>0.8213</v>
       </c>
       <c r="J334" t="n">
-        <v>5.120980481364419</v>
+        <v>18.8899</v>
       </c>
     </row>
     <row r="335">
@@ -15761,10 +15749,10 @@
         <v>1.11</v>
       </c>
       <c r="I335" t="n">
-        <v>0.04399720194001223</v>
+        <v>0.2506</v>
       </c>
       <c r="J335" t="n">
-        <v>1.011935644620281</v>
+        <v>5.7638</v>
       </c>
     </row>
     <row r="336">
@@ -15801,10 +15789,10 @@
         <v>1.04</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.02915225802306616</v>
+        <v>0.0383</v>
       </c>
       <c r="J336" t="n">
-        <v>-0.6705019345305218</v>
+        <v>0.8809</v>
       </c>
     </row>
     <row r="337">
@@ -15841,10 +15829,10 @@
         <v>0.92</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1170071632343449</v>
+        <v>-0.1263</v>
       </c>
       <c r="J337" t="n">
-        <v>-2.691164754389932</v>
+        <v>-2.9049</v>
       </c>
     </row>
     <row r="338">
@@ -15881,10 +15869,10 @@
         <v>0.9</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.132902941789797</v>
+        <v>-0.1658</v>
       </c>
       <c r="J338" t="n">
-        <v>-3.056767661165332</v>
+        <v>-3.8134</v>
       </c>
     </row>
     <row r="339">
@@ -15921,10 +15909,10 @@
         <v>0.9</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.132902941789797</v>
+        <v>-0.1658</v>
       </c>
       <c r="J339" t="n">
-        <v>-3.056767661165332</v>
+        <v>-3.8134</v>
       </c>
     </row>
     <row r="340">
@@ -15961,10 +15949,10 @@
         <v>0.88</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.1465232136574625</v>
+        <v>-0.2125</v>
       </c>
       <c r="J340" t="n">
-        <v>-3.370033914121638</v>
+        <v>-4.8875</v>
       </c>
     </row>
     <row r="341">
@@ -16001,10 +15989,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.1864532371124157</v>
+        <v>-0.3029</v>
       </c>
       <c r="J341" t="n">
-        <v>-4.288424453585561</v>
+        <v>-6.9667</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7556/event_7556_evp_summary.xlsx
+++ b/database/event/7556/event_7556_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.270200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.8455</v>
       </c>
       <c r="D2" t="n">
         <v>3.3236</v>
@@ -545,7 +545,7 @@
         <v>6.826</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.8316</v>
       </c>
       <c r="D3" t="n">
         <v>2.3362</v>
@@ -591,7 +591,7 @@
         <v>6.0563</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.5123</v>
       </c>
       <c r="D4" t="n">
         <v>2.0252</v>
@@ -637,7 +637,7 @@
         <v>5.468</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.2682</v>
       </c>
       <c r="D5" t="n">
         <v>1.7876</v>
@@ -683,7 +683,7 @@
         <v>5.2116</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.1619</v>
       </c>
       <c r="D6" t="n">
         <v>1.684</v>
@@ -729,7 +729,7 @@
         <v>5.0903</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.1116</v>
       </c>
       <c r="D7" t="n">
         <v>1.635</v>
@@ -775,7 +775,7 @@
         <v>5.0376</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.0897</v>
       </c>
       <c r="D8" t="n">
         <v>1.6137</v>
@@ -821,7 +821,7 @@
         <v>4.1825</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.735</v>
       </c>
       <c r="D9" t="n">
         <v>1.2683</v>
@@ -867,7 +867,7 @@
         <v>3.6954</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.5329</v>
       </c>
       <c r="D10" t="n">
         <v>1.0715</v>
@@ -913,7 +913,7 @@
         <v>3.6242</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.5034</v>
       </c>
       <c r="D11" t="n">
         <v>1.0427</v>
@@ -959,7 +959,7 @@
         <v>3.6122</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.4984</v>
       </c>
       <c r="D12" t="n">
         <v>1.0379</v>
@@ -1005,7 +1005,7 @@
         <v>3.3086</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.3725</v>
       </c>
       <c r="D13" t="n">
         <v>0.9152</v>
@@ -1051,7 +1051,7 @@
         <v>2.6594</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.1032</v>
       </c>
       <c r="D14" t="n">
         <v>0.653</v>
@@ -1097,7 +1097,7 @@
         <v>2.312</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.9591</v>
       </c>
       <c r="D15" t="n">
         <v>0.5125999999999999</v>
@@ -1143,7 +1143,7 @@
         <v>2.1173</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.8783</v>
       </c>
       <c r="D16" t="n">
         <v>0.434</v>
@@ -1189,7 +1189,7 @@
         <v>1.9184</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.7958</v>
       </c>
       <c r="D17" t="n">
         <v>0.3536</v>
@@ -1235,7 +1235,7 @@
         <v>1.413</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5861</v>
       </c>
       <c r="D18" t="n">
         <v>0.1495</v>
@@ -1281,7 +1281,7 @@
         <v>0.834</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="D19" t="n">
         <v>-0.0844</v>
@@ -1327,7 +1327,7 @@
         <v>0.7458</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.3094</v>
       </c>
       <c r="D20" t="n">
         <v>-0.1201</v>
@@ -1373,7 +1373,7 @@
         <v>0.2158</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.0895</v>
       </c>
       <c r="D21" t="n">
         <v>-0.3342</v>
@@ -1419,7 +1419,7 @@
         <v>0.1695</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.0703</v>
       </c>
       <c r="D22" t="n">
         <v>-0.3529</v>
@@ -1465,7 +1465,7 @@
         <v>0.0912</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.0378</v>
       </c>
       <c r="D23" t="n">
         <v>-0.3845</v>
@@ -1511,7 +1511,7 @@
         <v>0.0256</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.0106</v>
       </c>
       <c r="D24" t="n">
         <v>-0.411</v>
@@ -1557,7 +1557,7 @@
         <v>-0.1988</v>
       </c>
       <c r="C25" t="n">
-        <v>-0</v>
+        <v>-0.0825</v>
       </c>
       <c r="D25" t="n">
         <v>-0.5017</v>
@@ -1603,7 +1603,7 @@
         <v>-0.2723</v>
       </c>
       <c r="C26" t="n">
-        <v>-0</v>
+        <v>-0.113</v>
       </c>
       <c r="D26" t="n">
         <v>-0.5314</v>
@@ -1649,7 +1649,7 @@
         <v>-0.4588</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>-0.1903</v>
       </c>
       <c r="D27" t="n">
         <v>-0.6067</v>
@@ -1695,7 +1695,7 @@
         <v>-0.492</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.2041</v>
       </c>
       <c r="D28" t="n">
         <v>-0.6201</v>
@@ -1741,7 +1741,7 @@
         <v>-0.6321</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.2622</v>
       </c>
       <c r="D29" t="n">
         <v>-0.6767</v>
@@ -1787,7 +1787,7 @@
         <v>-0.79</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.3277</v>
       </c>
       <c r="D30" t="n">
         <v>-0.7405</v>
@@ -1833,7 +1833,7 @@
         <v>-0.8424</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.3494</v>
       </c>
       <c r="D31" t="n">
         <v>-0.7617</v>
@@ -1879,7 +1879,7 @@
         <v>-1.2268</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.5089</v>
       </c>
       <c r="D32" t="n">
         <v>-0.917</v>
@@ -1925,7 +1925,7 @@
         <v>-1.2779</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.5301</v>
       </c>
       <c r="D33" t="n">
         <v>-0.9376</v>
@@ -1971,7 +1971,7 @@
         <v>-1.3855</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.5747</v>
       </c>
       <c r="D34" t="n">
         <v>-0.9811</v>
@@ -2017,7 +2017,7 @@
         <v>-1.5448</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.6408</v>
       </c>
       <c r="D35" t="n">
         <v>-1.0454</v>
@@ -2063,7 +2063,7 @@
         <v>-1.9861</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.8239</v>
       </c>
       <c r="D36" t="n">
         <v>-1.2237</v>
@@ -2109,7 +2109,7 @@
         <v>-2.228</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.9242</v>
       </c>
       <c r="D37" t="n">
         <v>-1.3214</v>
@@ -2155,7 +2155,7 @@
         <v>-2.2338</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.9266</v>
       </c>
       <c r="D38" t="n">
         <v>-1.3238</v>
@@ -2201,7 +2201,7 @@
         <v>-2.5782</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-1.0695</v>
       </c>
       <c r="D39" t="n">
         <v>-1.4629</v>
@@ -2247,7 +2247,7 @@
         <v>-2.6916</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-1.1165</v>
       </c>
       <c r="D40" t="n">
         <v>-1.5087</v>
@@ -2293,7 +2293,7 @@
         <v>-4.028</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-1.6709</v>
       </c>
       <c r="D41" t="n">
         <v>-2.0486</v>

--- a/database/event/7556/event_7556_evp_summary.xlsx
+++ b/database/event/7556/event_7556_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.8455</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3236</v>
+        <v>3.2493</v>
       </c>
       <c r="E2" t="n">
         <v>9.270200000000001</v>
@@ -548,7 +548,7 @@
         <v>2.8316</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3362</v>
+        <v>2.2756</v>
       </c>
       <c r="E3" t="n">
         <v>6.826</v>
@@ -594,7 +594,7 @@
         <v>2.5123</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0252</v>
+        <v>1.9689</v>
       </c>
       <c r="E4" t="n">
         <v>6.0563</v>
@@ -640,7 +640,7 @@
         <v>2.2682</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7876</v>
+        <v>1.7345</v>
       </c>
       <c r="E5" t="n">
         <v>5.468</v>
@@ -686,7 +686,7 @@
         <v>2.1619</v>
       </c>
       <c r="D6" t="n">
-        <v>1.684</v>
+        <v>1.6324</v>
       </c>
       <c r="E6" t="n">
         <v>5.2116</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.0903</v>
+        <v>5.0825</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1116</v>
+        <v>2.1083</v>
       </c>
       <c r="D7" t="n">
-        <v>1.635</v>
+        <v>1.581</v>
       </c>
       <c r="E7" t="n">
-        <v>5.0903</v>
+        <v>5.0825</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0795</v>
+        <v>2.0718</v>
       </c>
       <c r="G7" t="n">
         <v>3.0107</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0795</v>
+        <v>2.0718</v>
       </c>
       <c r="I7" t="n">
         <v>2.0892</v>
@@ -778,7 +778,7 @@
         <v>2.0897</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6137</v>
+        <v>1.5631</v>
       </c>
       <c r="E8" t="n">
         <v>5.0376</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1825</v>
+        <v>4.1771</v>
       </c>
       <c r="C9" t="n">
-        <v>1.735</v>
+        <v>1.7327</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2683</v>
+        <v>1.2202</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1825</v>
+        <v>4.1771</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4571</v>
+        <v>1.4517</v>
       </c>
       <c r="G9" t="n">
         <v>2.7254</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4571</v>
+        <v>1.4517</v>
       </c>
       <c r="I9" t="n">
         <v>1.4639</v>
@@ -870,7 +870,7 @@
         <v>1.5329</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0715</v>
+        <v>1.0283</v>
       </c>
       <c r="E10" t="n">
         <v>3.6954</v>
@@ -916,7 +916,7 @@
         <v>1.5034</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0427</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>3.6242</v>
@@ -962,7 +962,7 @@
         <v>1.4984</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0379</v>
+        <v>0.9952</v>
       </c>
       <c r="E12" t="n">
         <v>3.6122</v>
@@ -1008,7 +1008,7 @@
         <v>1.3725</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9152</v>
+        <v>0.8742</v>
       </c>
       <c r="E13" t="n">
         <v>3.3086</v>
@@ -1054,7 +1054,7 @@
         <v>1.1032</v>
       </c>
       <c r="D14" t="n">
-        <v>0.653</v>
+        <v>0.6156</v>
       </c>
       <c r="E14" t="n">
         <v>2.6594</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.312</v>
+        <v>2.3057</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9591</v>
+        <v>0.9565</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.4747</v>
       </c>
       <c r="E15" t="n">
-        <v>2.312</v>
+        <v>2.3057</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6956</v>
+        <v>1.6893</v>
       </c>
       <c r="G15" t="n">
         <v>0.6163999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6956</v>
+        <v>1.6893</v>
       </c>
       <c r="I15" t="n">
         <v>1.7035</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1173</v>
+        <v>2.1099</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8783</v>
+        <v>0.8752</v>
       </c>
       <c r="D16" t="n">
-        <v>0.434</v>
+        <v>0.3967</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1173</v>
+        <v>2.1099</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9806</v>
+        <v>1.9732</v>
       </c>
       <c r="G16" t="n">
         <v>0.1367</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9806</v>
+        <v>1.9732</v>
       </c>
       <c r="I16" t="n">
         <v>1.9899</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9184</v>
+        <v>1.9128</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7958</v>
+        <v>0.7935</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3536</v>
+        <v>0.3181</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9184</v>
+        <v>1.9128</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4915</v>
+        <v>1.4859</v>
       </c>
       <c r="G17" t="n">
         <v>0.4269</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4915</v>
+        <v>1.4859</v>
       </c>
       <c r="I17" t="n">
         <v>1.4984</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.413</v>
+        <v>1.408</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5861</v>
+        <v>0.5841</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1495</v>
+        <v>0.117</v>
       </c>
       <c r="E18" t="n">
-        <v>1.413</v>
+        <v>1.408</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3462</v>
+        <v>1.3412</v>
       </c>
       <c r="G18" t="n">
         <v>0.0668</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3462</v>
+        <v>1.3412</v>
       </c>
       <c r="I18" t="n">
         <v>1.3525</v>
@@ -1284,7 +1284,7 @@
         <v>0.346</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0844</v>
+        <v>-0.1116</v>
       </c>
       <c r="E19" t="n">
         <v>0.834</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7458</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3094</v>
+        <v>0.3092</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1201</v>
+        <v>-0.1469</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7458</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0803</v>
+        <v>0.08</v>
       </c>
       <c r="G20" t="n">
         <v>0.6655</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0803</v>
+        <v>0.08</v>
       </c>
       <c r="I20" t="n">
         <v>0.08069999999999999</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2158</v>
+        <v>0.2144</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0895</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3342</v>
+        <v>-0.3585</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2158</v>
+        <v>0.2144</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3874</v>
+        <v>0.386</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1716</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3874</v>
+        <v>0.386</v>
       </c>
       <c r="I21" t="n">
         <v>0.3892</v>
@@ -1422,7 +1422,7 @@
         <v>0.0703</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3529</v>
+        <v>-0.3764</v>
       </c>
       <c r="E22" t="n">
         <v>0.1695</v>
@@ -1468,7 +1468,7 @@
         <v>0.0378</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3845</v>
+        <v>-0.4076</v>
       </c>
       <c r="E23" t="n">
         <v>0.0912</v>
@@ -1514,7 +1514,7 @@
         <v>0.0106</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.411</v>
+        <v>-0.4337</v>
       </c>
       <c r="E24" t="n">
         <v>0.0256</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0825</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5017</v>
+        <v>-0.5231</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1988</v>
@@ -1606,7 +1606,7 @@
         <v>-0.113</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5314</v>
+        <v>-0.5524</v>
       </c>
       <c r="E26" t="n">
         <v>-0.2723</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1903</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6067</v>
+        <v>-0.6267</v>
       </c>
       <c r="E27" t="n">
         <v>-0.4588</v>
@@ -1698,7 +1698,7 @@
         <v>-0.2041</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6201</v>
+        <v>-0.6399</v>
       </c>
       <c r="E28" t="n">
         <v>-0.492</v>
@@ -1744,7 +1744,7 @@
         <v>-0.2622</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6767</v>
+        <v>-0.6957</v>
       </c>
       <c r="E29" t="n">
         <v>-0.6321</v>
@@ -1790,7 +1790,7 @@
         <v>-0.3277</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7405</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="E30" t="n">
         <v>-0.79</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3494</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7617</v>
+        <v>-0.7795</v>
       </c>
       <c r="E31" t="n">
         <v>-0.8424</v>
@@ -1882,7 +1882,7 @@
         <v>-0.5089</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.917</v>
+        <v>-0.9327</v>
       </c>
       <c r="E32" t="n">
         <v>-1.2268</v>
@@ -1928,7 +1928,7 @@
         <v>-0.5301</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9376</v>
+        <v>-0.953</v>
       </c>
       <c r="E33" t="n">
         <v>-1.2779</v>
@@ -1974,7 +1974,7 @@
         <v>-0.5747</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9811</v>
+        <v>-0.9959</v>
       </c>
       <c r="E34" t="n">
         <v>-1.3855</v>
@@ -2020,7 +2020,7 @@
         <v>-0.6408</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0454</v>
+        <v>-1.0594</v>
       </c>
       <c r="E35" t="n">
         <v>-1.5448</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.9861</v>
+        <v>-1.9809</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.8239</v>
+        <v>-0.8217</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2237</v>
+        <v>-1.2331</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.9861</v>
+        <v>-1.9809</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3933</v>
+        <v>-1.3881</v>
       </c>
       <c r="G36" t="n">
         <v>-0.5928</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3933</v>
+        <v>-1.3881</v>
       </c>
       <c r="I36" t="n">
         <v>-1.3998</v>
@@ -2112,7 +2112,7 @@
         <v>-0.9242</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.3214</v>
+        <v>-1.3315</v>
       </c>
       <c r="E37" t="n">
         <v>-2.228</v>
@@ -2158,7 +2158,7 @@
         <v>-0.9266</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.3238</v>
+        <v>-1.3339</v>
       </c>
       <c r="E38" t="n">
         <v>-2.2338</v>
@@ -2204,7 +2204,7 @@
         <v>-1.0695</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4629</v>
+        <v>-1.4711</v>
       </c>
       <c r="E39" t="n">
         <v>-2.5782</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.6916</v>
+        <v>-2.6853</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.1165</v>
+        <v>-1.1139</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5087</v>
+        <v>-1.5137</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.6916</v>
+        <v>-2.6853</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6916</v>
+        <v>-1.6853</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6916</v>
+        <v>-1.6853</v>
       </c>
       <c r="I40" t="n">
         <v>-1.6995</v>
@@ -2296,7 +2296,7 @@
         <v>-1.6709</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0486</v>
+        <v>-2.0487</v>
       </c>
       <c r="E41" t="n">
         <v>-4.028</v>

--- a/database/event/7556/event_7556_evp_summary.xlsx
+++ b/database/event/7556/event_7556_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.270200000000001</v>
+        <v>9.0268</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8455</v>
+        <v>3.7445</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2493</v>
+        <v>3.4371</v>
       </c>
       <c r="E2" t="n">
-        <v>9.270200000000001</v>
+        <v>9.0268</v>
       </c>
       <c r="F2" t="n">
-        <v>2.786</v>
+        <v>3.2594</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4842</v>
+        <v>5.7674</v>
       </c>
       <c r="H2" t="n">
-        <v>2.786</v>
+        <v>3.7972</v>
       </c>
       <c r="I2" t="n">
-        <v>2.786</v>
+        <v>3.7972</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4907</v>
+        <v>5.7674</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -529,7 +529,7 @@
         <v>213</v>
       </c>
       <c r="M2" t="n">
-        <v>9.2767</v>
+        <v>9.5646</v>
       </c>
       <c r="N2" t="n">
         <v>318</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.826</v>
+        <v>6.4162</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8316</v>
+        <v>2.6616</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2756</v>
+        <v>2.2586</v>
       </c>
       <c r="E3" t="n">
-        <v>6.826</v>
+        <v>6.4162</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7505</v>
+        <v>2.0569</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0755</v>
+        <v>4.3593</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7505</v>
+        <v>2.0569</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7505</v>
+        <v>2.0569</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0755</v>
+        <v>4.3593</v>
       </c>
       <c r="K3" t="n">
         <v>105</v>
@@ -575,7 +575,7 @@
         <v>213</v>
       </c>
       <c r="M3" t="n">
-        <v>6.826</v>
+        <v>6.4162</v>
       </c>
       <c r="N3" t="n">
         <v>318</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0563</v>
+        <v>5.5349</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5123</v>
+        <v>2.296</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9689</v>
+        <v>1.8607</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0563</v>
+        <v>5.5349</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2368</v>
+        <v>3.6084</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8195</v>
+        <v>1.9264</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4851</v>
+        <v>7.2276</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6353</v>
+        <v>3.758</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8195</v>
+        <v>1.9264</v>
       </c>
       <c r="K4" t="n">
         <v>85</v>
@@ -621,7 +621,7 @@
         <v>152</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4548</v>
+        <v>5.6844</v>
       </c>
       <c r="N4" t="n">
         <v>237</v>
@@ -630,139 +630,139 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.468</v>
+        <v>5.4949</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2682</v>
+        <v>2.2794</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7345</v>
+        <v>1.8427</v>
       </c>
       <c r="E5" t="n">
-        <v>5.468</v>
+        <v>5.4949</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6346</v>
+        <v>3.0806</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8334</v>
+        <v>2.4144</v>
       </c>
       <c r="H5" t="n">
-        <v>6.0857</v>
+        <v>3.4047</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9326</v>
+        <v>3.5447</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8334</v>
+        <v>2.4144</v>
       </c>
       <c r="K5" t="n">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="L5" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="M5" t="n">
-        <v>5.766</v>
+        <v>5.9591</v>
       </c>
       <c r="N5" t="n">
-        <v>154</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2116</v>
+        <v>5.2239</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1619</v>
+        <v>2.167</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6324</v>
+        <v>1.7203</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2116</v>
+        <v>5.2239</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4346</v>
+        <v>4.4518</v>
       </c>
       <c r="G6" t="n">
-        <v>4.777</v>
+        <v>0.7721</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4346</v>
+        <v>10.9854</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4346</v>
+        <v>5.7119</v>
       </c>
       <c r="J6" t="n">
-        <v>4.777</v>
+        <v>0.7721</v>
       </c>
       <c r="K6" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L6" t="n">
-        <v>213</v>
+        <v>72</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2116</v>
+        <v>6.484</v>
       </c>
       <c r="N6" t="n">
-        <v>318</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.0825</v>
+        <v>5.178</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1083</v>
+        <v>2.1479</v>
       </c>
       <c r="D7" t="n">
-        <v>1.581</v>
+        <v>1.6996</v>
       </c>
       <c r="E7" t="n">
-        <v>5.0825</v>
+        <v>5.178</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0718</v>
+        <v>0.9074</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0107</v>
+        <v>4.2706</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0718</v>
+        <v>0.9074</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0892</v>
+        <v>0.9074</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0107</v>
+        <v>4.2706</v>
       </c>
       <c r="K7" t="n">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="L7" t="n">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="M7" t="n">
-        <v>5.0999</v>
+        <v>5.178</v>
       </c>
       <c r="N7" t="n">
-        <v>243</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.0376</v>
+        <v>4.6703</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0897</v>
+        <v>1.9373</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5631</v>
+        <v>1.4704</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0376</v>
+        <v>4.6703</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3223</v>
+        <v>3.9418</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7153</v>
+        <v>0.7285</v>
       </c>
       <c r="H8" t="n">
-        <v>4.829</v>
+        <v>8.402100000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>3.914</v>
+        <v>4.3687</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7153</v>
+        <v>0.7285</v>
       </c>
       <c r="K8" t="n">
         <v>82</v>
@@ -805,7 +805,7 @@
         <v>72</v>
       </c>
       <c r="M8" t="n">
-        <v>4.629300000000001</v>
+        <v>5.0972</v>
       </c>
       <c r="N8" t="n">
         <v>154</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1771</v>
+        <v>4.6542</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7327</v>
+        <v>1.9307</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2202</v>
+        <v>1.4631</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1771</v>
+        <v>4.6542</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4517</v>
+        <v>1.8809</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7254</v>
+        <v>2.7733</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4517</v>
+        <v>1.8809</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4639</v>
+        <v>0.978</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7254</v>
+        <v>2.7733</v>
       </c>
       <c r="K9" t="n">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="L9" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1893</v>
+        <v>3.7513</v>
       </c>
       <c r="N9" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6954</v>
+        <v>3.9336</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5329</v>
+        <v>1.6317</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0283</v>
+        <v>1.1378</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6954</v>
+        <v>3.9336</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4975</v>
+        <v>1.6429</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1979</v>
+        <v>2.2907</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4975</v>
+        <v>1.6429</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8348</v>
+        <v>1.7105</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1979</v>
+        <v>2.2907</v>
       </c>
       <c r="K10" t="n">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="L10" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0327</v>
+        <v>4.0012</v>
       </c>
       <c r="N10" t="n">
-        <v>154</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6242</v>
+        <v>3.6537</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5034</v>
+        <v>1.5156</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.0114</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6242</v>
+        <v>3.6537</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8708</v>
+        <v>3.3241</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7534</v>
+        <v>0.3296</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8708</v>
+        <v>6.2257</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7058</v>
+        <v>3.2371</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7534</v>
+        <v>0.3296</v>
       </c>
       <c r="K11" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L11" t="n">
-        <v>152</v>
+        <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4592</v>
+        <v>3.5667</v>
       </c>
       <c r="N11" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6122</v>
+        <v>3.5449</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4984</v>
+        <v>1.4705</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9952</v>
+        <v>0.9623</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6122</v>
+        <v>3.5449</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7645</v>
+        <v>2.8534</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8477</v>
+        <v>0.6915</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7645</v>
+        <v>4.5671</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2407</v>
+        <v>2.3747</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8477</v>
+        <v>0.6915</v>
       </c>
       <c r="K12" t="n">
         <v>85</v>
@@ -989,7 +989,7 @@
         <v>152</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0884</v>
+        <v>3.0662</v>
       </c>
       <c r="N12" t="n">
         <v>237</v>
@@ -998,139 +998,139 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3086</v>
+        <v>3.1814</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3725</v>
+        <v>1.3197</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8742</v>
+        <v>0.7982</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3086</v>
+        <v>3.1814</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2934</v>
+        <v>2.63</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9848</v>
+        <v>0.5514</v>
       </c>
       <c r="H13" t="n">
-        <v>4.713</v>
+        <v>2.63</v>
       </c>
       <c r="I13" t="n">
-        <v>3.82</v>
+        <v>2.7382</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9848</v>
+        <v>0.5514</v>
       </c>
       <c r="K13" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="L13" t="n">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8352</v>
+        <v>3.2896</v>
       </c>
       <c r="N13" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6594</v>
+        <v>3.143</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1032</v>
+        <v>1.3038</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6156</v>
+        <v>0.7809</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6594</v>
+        <v>3.143</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9919</v>
+        <v>3.7963</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3325</v>
+        <v>-0.6533</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9919</v>
+        <v>7.8894</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9919</v>
+        <v>4.1021</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3325</v>
+        <v>-0.6533</v>
       </c>
       <c r="K14" t="n">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6594</v>
+        <v>3.4488</v>
       </c>
       <c r="N14" t="n">
-        <v>150</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3057</v>
+        <v>2.8465</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9565</v>
+        <v>1.1808</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4747</v>
+        <v>0.647</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3057</v>
+        <v>2.8465</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6893</v>
+        <v>3.1219</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6163999999999999</v>
+        <v>-0.2754</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6893</v>
+        <v>3.4953</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7035</v>
+        <v>3.4953</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6163999999999999</v>
+        <v>-0.2754</v>
       </c>
       <c r="K15" t="n">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="L15" t="n">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3199</v>
+        <v>3.2199</v>
       </c>
       <c r="N15" t="n">
-        <v>243</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1099</v>
+        <v>2.7989</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8752</v>
+        <v>1.161</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3967</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1099</v>
+        <v>2.7989</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9732</v>
+        <v>2.5911</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1367</v>
+        <v>0.2078</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9732</v>
+        <v>2.5911</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9899</v>
+        <v>2.6977</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1367</v>
+        <v>0.2078</v>
       </c>
       <c r="K16" t="n">
         <v>121</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1266</v>
+        <v>2.9055</v>
       </c>
       <c r="N16" t="n">
         <v>172</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9128</v>
+        <v>2.2364</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7935</v>
+        <v>0.9277</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3181</v>
+        <v>0.3716</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9128</v>
+        <v>2.2364</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4859</v>
+        <v>1.7371</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4269</v>
+        <v>0.4993</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4859</v>
+        <v>1.7371</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4984</v>
+        <v>1.8085</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4269</v>
+        <v>0.4993</v>
       </c>
       <c r="K17" t="n">
         <v>121</v>
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9253</v>
+        <v>2.3078</v>
       </c>
       <c r="N17" t="n">
         <v>172</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.408</v>
+        <v>1.8646</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5841</v>
+        <v>0.7735</v>
       </c>
       <c r="D18" t="n">
-        <v>0.117</v>
+        <v>0.2038</v>
       </c>
       <c r="E18" t="n">
-        <v>1.408</v>
+        <v>1.8646</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3412</v>
+        <v>1.7296</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0668</v>
+        <v>0.135</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3412</v>
+        <v>1.7296</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3525</v>
+        <v>1.8007</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0668</v>
+        <v>0.135</v>
       </c>
       <c r="K18" t="n">
         <v>121</v>
@@ -1265,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4193</v>
+        <v>1.9357</v>
       </c>
       <c r="N18" t="n">
         <v>172</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.834</v>
+        <v>1.1927</v>
       </c>
       <c r="C19" t="n">
-        <v>0.346</v>
+        <v>0.4948</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1116</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.834</v>
+        <v>1.1927</v>
       </c>
       <c r="F19" t="n">
-        <v>0.834</v>
+        <v>1.1927</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.834</v>
+        <v>1.1927</v>
       </c>
       <c r="I19" t="n">
-        <v>0.834</v>
+        <v>1.1927</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.834</v>
+        <v>1.1927</v>
       </c>
       <c r="N19" t="n">
         <v>126</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.6863</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3092</v>
+        <v>0.2847</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1469</v>
+        <v>-0.3282</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.6863</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08</v>
+        <v>0.7819</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6655</v>
+        <v>-0.0956</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08</v>
+        <v>0.7819</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.8141</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6655</v>
+        <v>-0.0956</v>
       </c>
       <c r="K20" t="n">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="L20" t="n">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7462</v>
+        <v>0.7185</v>
       </c>
       <c r="N20" t="n">
-        <v>243</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2144</v>
+        <v>0.6207</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.2575</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3585</v>
+        <v>-0.3578</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2144</v>
+        <v>0.6207</v>
       </c>
       <c r="F21" t="n">
-        <v>0.386</v>
+        <v>0.6446</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1716</v>
+        <v>-0.0239</v>
       </c>
       <c r="H21" t="n">
-        <v>0.386</v>
+        <v>0.6446</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3892</v>
+        <v>0.6446</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1716</v>
+        <v>-0.0239</v>
       </c>
       <c r="K21" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2176</v>
+        <v>0.6206999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1695</v>
+        <v>0.4758</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0703</v>
+        <v>0.1974</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3764</v>
+        <v>-0.4232</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1695</v>
+        <v>0.4758</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.099</v>
+        <v>0.197</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2685</v>
+        <v>0.2788</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.099</v>
+        <v>0.197</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.099</v>
+        <v>0.197</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2685</v>
+        <v>0.2788</v>
       </c>
       <c r="K22" t="n">
         <v>115</v>
@@ -1449,7 +1449,7 @@
         <v>35</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1695</v>
+        <v>0.4758</v>
       </c>
       <c r="N22" t="n">
         <v>150</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0912</v>
+        <v>0.3866</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0378</v>
+        <v>0.1604</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4076</v>
+        <v>-0.4635</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0912</v>
+        <v>0.3866</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3347</v>
+        <v>0.111</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2435</v>
+        <v>0.2756</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3347</v>
+        <v>0.111</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3347</v>
+        <v>0.1156</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2435</v>
+        <v>0.2756</v>
       </c>
       <c r="K23" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L23" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0912</v>
+        <v>0.3912</v>
       </c>
       <c r="N23" t="n">
-        <v>150</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0256</v>
+        <v>0.3163</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0106</v>
+        <v>0.1312</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4337</v>
+        <v>-0.4952</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0256</v>
+        <v>0.3163</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0256</v>
+        <v>0.3163</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0256</v>
+        <v>0.3163</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0256</v>
+        <v>0.3163</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0256</v>
+        <v>0.3163</v>
       </c>
       <c r="N24" t="n">
         <v>126</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1988</v>
+        <v>0.151</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0825</v>
+        <v>0.0626</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5231</v>
+        <v>-0.5698</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1988</v>
+        <v>0.151</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1988</v>
+        <v>0.151</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1988</v>
+        <v>0.151</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1988</v>
+        <v>0.151</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1988</v>
+        <v>0.151</v>
       </c>
       <c r="N25" t="n">
         <v>88</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2723</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.113</v>
+        <v>0.0401</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5524</v>
+        <v>-0.5944</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2723</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2723</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2723</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2723</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2723</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>88</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4588</v>
+        <v>-0.1692</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1903</v>
+        <v>-0.0702</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6267</v>
+        <v>-0.7144</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4588</v>
+        <v>-0.1692</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4588</v>
+        <v>0.7412</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.9104</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4588</v>
+        <v>0.7412</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4588</v>
+        <v>0.7412</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.9104</v>
       </c>
       <c r="K27" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4588</v>
+        <v>-0.1692</v>
       </c>
       <c r="N27" t="n">
-        <v>88</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.492</v>
+        <v>-0.2408</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2041</v>
+        <v>-0.0999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6399</v>
+        <v>-0.7467</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.492</v>
+        <v>-0.2408</v>
       </c>
       <c r="F28" t="n">
-        <v>0.508</v>
+        <v>-0.2408</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.508</v>
+        <v>-0.2408</v>
       </c>
       <c r="I28" t="n">
-        <v>0.508</v>
+        <v>-0.2408</v>
       </c>
       <c r="J28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.492</v>
+        <v>-0.2408</v>
       </c>
       <c r="N28" t="n">
-        <v>150</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6321</v>
+        <v>-0.3023</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2622</v>
+        <v>-0.1254</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6957</v>
+        <v>-0.7745</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6321</v>
+        <v>-0.3023</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6321</v>
+        <v>-0.3023</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6321</v>
+        <v>-0.3023</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6321</v>
+        <v>-0.3023</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6321</v>
+        <v>-0.3023</v>
       </c>
       <c r="N29" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.79</v>
+        <v>-0.3511</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3277</v>
+        <v>-0.1456</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.7965</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.79</v>
+        <v>-0.3511</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5616</v>
+        <v>-0.2269</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2284</v>
+        <v>-0.1242</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5616</v>
+        <v>-0.2269</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4552</v>
+        <v>-0.118</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2284</v>
+        <v>-0.1242</v>
       </c>
       <c r="K30" t="n">
         <v>82</v>
@@ -1817,7 +1817,7 @@
         <v>72</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6836</v>
+        <v>-0.2422</v>
       </c>
       <c r="N30" t="n">
         <v>154</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8424</v>
+        <v>-0.4157</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3494</v>
+        <v>-0.1724</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7795</v>
+        <v>-0.8257</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8424</v>
+        <v>-0.4157</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8424</v>
+        <v>-0.4157</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8424</v>
+        <v>-0.4157</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8424</v>
+        <v>-0.4157</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8424</v>
+        <v>-0.4157</v>
       </c>
       <c r="N31" t="n">
         <v>126</v>
@@ -1872,231 +1872,231 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.2268</v>
+        <v>-0.7447</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.5089</v>
+        <v>-0.3089</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9327</v>
+        <v>-0.9742</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.2268</v>
+        <v>-0.7447</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.6245</v>
+        <v>-0.7447</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3977</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.6245</v>
+        <v>-0.7447</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.3167</v>
+        <v>-0.7447</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3977</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L32" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.919</v>
+        <v>-0.7447</v>
       </c>
       <c r="N32" t="n">
-        <v>237</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.2779</v>
+        <v>-0.8288</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.5301</v>
+        <v>-0.3438</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.953</v>
+        <v>-1.0122</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.2779</v>
+        <v>-0.8288</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.2779</v>
+        <v>-0.8288</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.2779</v>
+        <v>-0.8288</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.2779</v>
+        <v>-0.8288</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.2779</v>
+        <v>-0.8288</v>
       </c>
       <c r="N33" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.3855</v>
+        <v>-1.0842</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.5747</v>
+        <v>-0.4497</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9959</v>
+        <v>-1.1275</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.3855</v>
+        <v>-1.0842</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.3855</v>
+        <v>-2.0327</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.9485</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.3855</v>
+        <v>-2.0327</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.3855</v>
+        <v>-1.0569</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.9485</v>
       </c>
       <c r="K34" t="n">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.3855</v>
+        <v>-0.1083999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>126</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.5448</v>
+        <v>-1.1078</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.6408</v>
+        <v>-0.4595</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0594</v>
+        <v>-1.1381</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.5448</v>
+        <v>-1.1078</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.5448</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.2323</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.5448</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.5448</v>
+        <v>-0.9115</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.2323</v>
       </c>
       <c r="K35" t="n">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.5448</v>
+        <v>-1.1438</v>
       </c>
       <c r="N35" t="n">
-        <v>88</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.9809</v>
+        <v>-1.1617</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.8217</v>
+        <v>-0.4819</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2331</v>
+        <v>-1.1625</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.9809</v>
+        <v>-1.1617</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3881</v>
+        <v>-1.1617</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5928</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3881</v>
+        <v>-1.1617</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3998</v>
+        <v>-1.1617</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5928</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="L36" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.9926</v>
+        <v>-1.1617</v>
       </c>
       <c r="N36" t="n">
-        <v>243</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.228</v>
+        <v>-1.3971</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.9242</v>
+        <v>-0.5795</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.3315</v>
+        <v>-1.2687</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.228</v>
+        <v>-1.3971</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4315</v>
+        <v>-0.8323</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7965</v>
+        <v>-0.5648</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4315</v>
+        <v>-0.8323</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.4315</v>
+        <v>-0.8323</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7965</v>
+        <v>-0.5648</v>
       </c>
       <c r="K37" t="n">
         <v>115</v>
@@ -2139,7 +2139,7 @@
         <v>35</v>
       </c>
       <c r="M37" t="n">
-        <v>-2.228</v>
+        <v>-1.3971</v>
       </c>
       <c r="N37" t="n">
         <v>150</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.2338</v>
+        <v>-1.6997</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.9266</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.3339</v>
+        <v>-1.4053</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.2338</v>
+        <v>-1.6997</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2371</v>
+        <v>0.0498</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.9967</v>
+        <v>-1.7495</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2371</v>
+        <v>0.0498</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2371</v>
+        <v>0.0498</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.9967</v>
+        <v>-1.7495</v>
       </c>
       <c r="K38" t="n">
         <v>105</v>
@@ -2185,7 +2185,7 @@
         <v>213</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.2338</v>
+        <v>-1.6997</v>
       </c>
       <c r="N38" t="n">
         <v>318</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.5782</v>
+        <v>-1.8319</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.0695</v>
+        <v>-0.7599</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4711</v>
+        <v>-1.465</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.5782</v>
+        <v>-1.8319</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5782</v>
+        <v>-1.1324</v>
       </c>
       <c r="G39" t="n">
-        <v>-1</v>
+        <v>-0.6995</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5782</v>
+        <v>-1.1324</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2792</v>
+        <v>-1.179</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>-0.6995</v>
       </c>
       <c r="K39" t="n">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="L39" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.2792</v>
+        <v>-1.8785</v>
       </c>
       <c r="N39" t="n">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.6853</v>
+        <v>-2.945</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.1139</v>
+        <v>-1.2216</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5137</v>
+        <v>-1.9675</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.6853</v>
+        <v>-2.945</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6853</v>
+        <v>-1.945</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6853</v>
+        <v>-1.945</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6995</v>
+        <v>-1.0113</v>
       </c>
       <c r="J40" t="n">
         <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="L40" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.6995</v>
+        <v>-2.0113</v>
       </c>
       <c r="N40" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.028</v>
+        <v>-3.1721</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.6709</v>
+        <v>-1.3159</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0487</v>
+        <v>-2.0701</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.028</v>
+        <v>-3.1721</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9542</v>
+        <v>-1.4641</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.0738</v>
+        <v>-1.708</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9542</v>
+        <v>-1.4641</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9542</v>
+        <v>-1.4641</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.0738</v>
+        <v>-1.708</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2323,7 +2323,7 @@
         <v>213</v>
       </c>
       <c r="M41" t="n">
-        <v>-4.028</v>
+        <v>-3.1721</v>
       </c>
       <c r="N41" t="n">
         <v>318</v>
@@ -2429,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2195</v>
+        <v>1.1351</v>
       </c>
       <c r="J2" t="n">
-        <v>26.829</v>
+        <v>24.9722</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.59</v>
+        <v>0.5755</v>
       </c>
       <c r="J3" t="n">
-        <v>12.98</v>
+        <v>12.661</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.59</v>
+        <v>0.5755</v>
       </c>
       <c r="J4" t="n">
-        <v>12.98</v>
+        <v>12.661</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.268</v>
+        <v>-0.1978</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.896</v>
+        <v>-4.3516</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7343</v>
+        <v>-0.6825</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.1546</v>
+        <v>-15.015</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7118</v>
+        <v>0.8806</v>
       </c>
       <c r="J7" t="n">
-        <v>15.6596</v>
+        <v>19.3732</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.37</v>
       </c>
       <c r="I8" t="n">
-        <v>0.627</v>
+        <v>0.7611</v>
       </c>
       <c r="J8" t="n">
-        <v>13.794</v>
+        <v>16.7442</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4281</v>
+        <v>-0.2724</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.418200000000001</v>
+        <v>-5.9928</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4833</v>
+        <v>-0.3111</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.6326</v>
+        <v>-6.8442</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8151</v>
+        <v>-0.5591</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.9322</v>
+        <v>-12.3002</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.52</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3025</v>
+        <v>1.1893</v>
       </c>
       <c r="J12" t="n">
-        <v>31.26</v>
+        <v>28.5432</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.45</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1616</v>
+        <v>1.0972</v>
       </c>
       <c r="J13" t="n">
-        <v>27.8784</v>
+        <v>26.3328</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3574</v>
+        <v>0.3734</v>
       </c>
       <c r="J14" t="n">
-        <v>8.5776</v>
+        <v>8.961600000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.79</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7326</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-17.5824</v>
+        <v>-16.3416</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8937</v>
+        <v>-0.857</v>
       </c>
       <c r="J16" t="n">
-        <v>-21.4488</v>
+        <v>-20.568</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3809</v>
+        <v>0.4276</v>
       </c>
       <c r="J17" t="n">
-        <v>9.1416</v>
+        <v>10.2624</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1661</v>
+        <v>0.1578</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9864</v>
+        <v>3.7872</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1312</v>
+        <v>-0.0935</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.1488</v>
+        <v>-2.244</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1312</v>
+        <v>-0.0935</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.1488</v>
+        <v>-2.244</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.54</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7073</v>
+        <v>-0.476</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.9752</v>
+        <v>-11.424</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.46</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7088</v>
+        <v>0.67</v>
       </c>
       <c r="J22" t="n">
-        <v>17.0112</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.19</v>
       </c>
       <c r="I23" t="n">
-        <v>0.36</v>
+        <v>0.3156</v>
       </c>
       <c r="J23" t="n">
-        <v>8.640000000000001</v>
+        <v>7.5744</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0383</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9248</v>
+        <v>-0.9192</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1645</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.948</v>
+        <v>-2.1792</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.4681</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.7304</v>
+        <v>-11.2344</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6252</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>15.0048</v>
+        <v>13.1256</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5888</v>
+        <v>0.5127</v>
       </c>
       <c r="J28" t="n">
-        <v>14.1312</v>
+        <v>12.3048</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1372</v>
+        <v>0.1445</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2928</v>
+        <v>3.468</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2129</v>
+        <v>-0.115</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.1096</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2946</v>
+        <v>-0.1715</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.0704</v>
+        <v>-4.116</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.65</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5506</v>
+        <v>1.356</v>
       </c>
       <c r="J32" t="n">
-        <v>31.012</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6439</v>
+        <v>0.626</v>
       </c>
       <c r="J33" t="n">
-        <v>12.878</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.18</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5394</v>
+        <v>0.5266</v>
       </c>
       <c r="J34" t="n">
-        <v>10.788</v>
+        <v>10.532</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4785</v>
+        <v>-0.412</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.57</v>
+        <v>-8.24</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.67</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0035</v>
+        <v>-0.9791</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.07</v>
+        <v>-19.582</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6153</v>
+        <v>0.7448</v>
       </c>
       <c r="J37" t="n">
-        <v>12.306</v>
+        <v>14.896</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.19</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3883</v>
+        <v>0.4389</v>
       </c>
       <c r="J38" t="n">
-        <v>7.766</v>
+        <v>8.778</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.07</v>
       </c>
       <c r="I39" t="n">
-        <v>0.196</v>
+        <v>0.1974</v>
       </c>
       <c r="J39" t="n">
-        <v>3.92</v>
+        <v>3.948</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.61</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6252</v>
+        <v>-0.4142</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.504</v>
+        <v>-8.284000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.5</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7573</v>
+        <v>-0.5142</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.146</v>
+        <v>-10.284</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5522</v>
+        <v>0.4353</v>
       </c>
       <c r="J42" t="n">
-        <v>12.7006</v>
+        <v>10.0119</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3172</v>
+        <v>0.2742</v>
       </c>
       <c r="J43" t="n">
-        <v>7.2956</v>
+        <v>6.3066</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.101</v>
+        <v>-0.0519</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.323</v>
+        <v>-1.1937</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1993</v>
+        <v>-0.1138</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.5839</v>
+        <v>-2.6174</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4977</v>
+        <v>-0.3194</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.4471</v>
+        <v>-7.3462</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2389</v>
+        <v>0.8267</v>
       </c>
       <c r="J47" t="n">
-        <v>28.4947</v>
+        <v>19.0141</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0569</v>
+        <v>-0.0128</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.3087</v>
+        <v>-0.2944</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0339</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.0907</v>
+        <v>-0.7796999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2626</v>
+        <v>-0.1493</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.0398</v>
+        <v>-3.4339</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3967</v>
+        <v>-0.2441</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.1241</v>
+        <v>-5.6143</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.8</v>
       </c>
       <c r="I52" t="n">
-        <v>1.7898</v>
+        <v>1.2894</v>
       </c>
       <c r="J52" t="n">
-        <v>42.9552</v>
+        <v>30.9456</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.05</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1497</v>
+        <v>0.1811</v>
       </c>
       <c r="J53" t="n">
-        <v>3.5928</v>
+        <v>4.3464</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4627</v>
+        <v>-0.4005</v>
       </c>
       <c r="J54" t="n">
-        <v>-11.1048</v>
+        <v>-9.612</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5175</v>
+        <v>-0.4568</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.42</v>
+        <v>-10.9632</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.79</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7206</v>
+        <v>-0.6702</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.2944</v>
+        <v>-16.0848</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4571</v>
+        <v>0.4511</v>
       </c>
       <c r="J57" t="n">
-        <v>10.9704</v>
+        <v>10.8264</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.16</v>
       </c>
       <c r="I58" t="n">
-        <v>0.328</v>
+        <v>0.3534</v>
       </c>
       <c r="J58" t="n">
-        <v>7.872</v>
+        <v>8.4816</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2812</v>
+        <v>0.3087</v>
       </c>
       <c r="J59" t="n">
-        <v>6.7488</v>
+        <v>7.4088</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3369</v>
+        <v>-0.2075</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.085599999999999</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.58</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6686</v>
+        <v>-0.4464</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.0464</v>
+        <v>-10.7136</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.11</v>
       </c>
       <c r="I62" t="n">
-        <v>1.9633</v>
+        <v>1.5034</v>
       </c>
       <c r="J62" t="n">
-        <v>29.4495</v>
+        <v>22.551</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.75</v>
       </c>
       <c r="I63" t="n">
-        <v>1.5495</v>
+        <v>1.1036</v>
       </c>
       <c r="J63" t="n">
-        <v>23.2425</v>
+        <v>16.554</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8798</v>
+        <v>0.7343</v>
       </c>
       <c r="J64" t="n">
-        <v>13.197</v>
+        <v>11.0145</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.41</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8374</v>
+        <v>0.7095</v>
       </c>
       <c r="J65" t="n">
-        <v>12.561</v>
+        <v>10.6425</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.95</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4064</v>
+        <v>-0.3211</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.096</v>
+        <v>-4.8165</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6069</v>
+        <v>0.5746</v>
       </c>
       <c r="J67" t="n">
-        <v>9.1035</v>
+        <v>8.619</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.91</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0914</v>
+        <v>-0.0944</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.371</v>
+        <v>-1.416</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.63</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.3728</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.4</v>
+        <v>-5.592</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.57</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6403</v>
+        <v>-0.4289</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.6045</v>
+        <v>-6.4335</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.46</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7786</v>
+        <v>-0.5308</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.679</v>
+        <v>-7.962</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4694</v>
+        <v>0.3712</v>
       </c>
       <c r="J72" t="n">
-        <v>10.3268</v>
+        <v>8.166399999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4149</v>
+        <v>0.341</v>
       </c>
       <c r="J73" t="n">
-        <v>9.127800000000001</v>
+        <v>7.502</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.22</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3868</v>
+        <v>0.3213</v>
       </c>
       <c r="J74" t="n">
-        <v>8.509600000000001</v>
+        <v>7.0686</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.06</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1099</v>
+        <v>0.1073</v>
       </c>
       <c r="J75" t="n">
-        <v>2.4178</v>
+        <v>2.3606</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.4635</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.202</v>
+        <v>-10.197</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.72</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9858</v>
+        <v>0.7108</v>
       </c>
       <c r="J77" t="n">
-        <v>21.6876</v>
+        <v>15.6376</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.33</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5405</v>
+        <v>0.4295</v>
       </c>
       <c r="J78" t="n">
-        <v>11.891</v>
+        <v>9.449</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.367</v>
+        <v>-0.2252</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.074</v>
+        <v>-4.9544</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5039</v>
+        <v>-0.3233</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.0858</v>
+        <v>-7.1126</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5425</v>
+        <v>-0.3517</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.935</v>
+        <v>-7.7374</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6373</v>
+        <v>0.595</v>
       </c>
       <c r="J82" t="n">
-        <v>12.746</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0014</v>
+        <v>-0.024</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.028</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1658</v>
+        <v>-0.1233</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.316</v>
+        <v>-2.466</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5626</v>
+        <v>-0.3696</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.252</v>
+        <v>-7.392</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.54</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.701</v>
+        <v>-0.4715</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.02</v>
+        <v>-9.43</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1351</v>
+        <v>0.8135</v>
       </c>
       <c r="J87" t="n">
-        <v>22.702</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8546</v>
+        <v>0.6431</v>
       </c>
       <c r="J88" t="n">
-        <v>17.092</v>
+        <v>12.862</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="J89" t="n">
-        <v>15.696</v>
+        <v>12.056</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0102</v>
+        <v>0.0815</v>
       </c>
       <c r="J90" t="n">
-        <v>0.204</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3638</v>
+        <v>-0.2857</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.276</v>
+        <v>-5.714</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>18.372</v>
+        <v>17.223</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4295</v>
+        <v>0.4299</v>
       </c>
       <c r="J93" t="n">
-        <v>12.885</v>
+        <v>12.897</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.83</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3369</v>
+        <v>-0.2075</v>
       </c>
       <c r="J94" t="n">
-        <v>-10.107</v>
+        <v>-6.225</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.83</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3369</v>
+        <v>-0.2075</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.107</v>
+        <v>-6.225</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5314</v>
+        <v>-0.3446</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.942</v>
+        <v>-10.338</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3617</v>
+        <v>0.9578</v>
       </c>
       <c r="J97" t="n">
-        <v>40.851</v>
+        <v>28.734</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9085</v>
+        <v>0.6727</v>
       </c>
       <c r="J98" t="n">
-        <v>27.255</v>
+        <v>20.181</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.18</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4662</v>
+        <v>0.4395</v>
       </c>
       <c r="J99" t="n">
-        <v>13.986</v>
+        <v>13.185</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0165</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>0.495</v>
+        <v>2.565</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.85</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6068</v>
+        <v>-0.5422</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.204</v>
+        <v>-16.266</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.71</v>
       </c>
       <c r="I102" t="n">
-        <v>1.5961</v>
+        <v>1.115</v>
       </c>
       <c r="J102" t="n">
-        <v>30.3259</v>
+        <v>21.185</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.46</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1143</v>
+        <v>0.8047</v>
       </c>
       <c r="J103" t="n">
-        <v>21.1717</v>
+        <v>15.2893</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.29</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7336</v>
+        <v>0.5837</v>
       </c>
       <c r="J104" t="n">
-        <v>13.9384</v>
+        <v>11.0903</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3452</v>
+        <v>-0.2637</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.5588</v>
+        <v>-5.0103</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.5288</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.3297</v>
+        <v>-10.0472</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.26</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4902</v>
+        <v>0.475</v>
       </c>
       <c r="J107" t="n">
-        <v>9.313800000000001</v>
+        <v>9.025</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.22</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4353</v>
+        <v>0.4317</v>
       </c>
       <c r="J108" t="n">
-        <v>8.2707</v>
+        <v>8.202299999999999</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.96</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0696</v>
+        <v>-0.058</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.3224</v>
+        <v>-1.102</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.68</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5336</v>
+        <v>-0.3474</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.1384</v>
+        <v>-6.6006</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.55</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6965</v>
+        <v>-0.4678</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.2335</v>
+        <v>-8.888199999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>1.7831</v>
+        <v>1.2799</v>
       </c>
       <c r="J112" t="n">
-        <v>28.5296</v>
+        <v>20.4784</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.5</v>
       </c>
       <c r="I113" t="n">
-        <v>1.1037</v>
+        <v>0.8257</v>
       </c>
       <c r="J113" t="n">
-        <v>17.6592</v>
+        <v>13.2112</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.41</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8828</v>
+        <v>0.7188</v>
       </c>
       <c r="J114" t="n">
-        <v>14.1248</v>
+        <v>11.5008</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.32</v>
       </c>
       <c r="I115" t="n">
-        <v>0.679</v>
+        <v>0.6047</v>
       </c>
       <c r="J115" t="n">
-        <v>10.864</v>
+        <v>9.6752</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.07</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0694</v>
+        <v>0.1606</v>
       </c>
       <c r="J116" t="n">
-        <v>1.1104</v>
+        <v>2.5696</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1668</v>
+        <v>-0.1529</v>
       </c>
       <c r="J117" t="n">
-        <v>-2.6688</v>
+        <v>-2.4464</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.78</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2629</v>
+        <v>-0.2174</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.2064</v>
+        <v>-3.4784</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.78</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2629</v>
+        <v>-0.2174</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.2064</v>
+        <v>-3.4784</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.54</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6541</v>
+        <v>-0.4426</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.4656</v>
+        <v>-7.0816</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7337</v>
+        <v>-0.4989</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.7392</v>
+        <v>-7.9824</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.37</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0027</v>
+        <v>0.7209</v>
       </c>
       <c r="J122" t="n">
-        <v>22.0594</v>
+        <v>15.8598</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.4804</v>
       </c>
       <c r="J123" t="n">
-        <v>13.3166</v>
+        <v>10.5688</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3805</v>
+        <v>0.3589</v>
       </c>
       <c r="J124" t="n">
-        <v>8.371</v>
+        <v>7.8958</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3851</v>
+        <v>-0.3187</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.472200000000001</v>
+        <v>-7.0114</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4432</v>
+        <v>-0.3778</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.750400000000001</v>
+        <v>-8.3116</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.11</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2651</v>
+        <v>0.2822</v>
       </c>
       <c r="J127" t="n">
-        <v>5.8322</v>
+        <v>6.2084</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0479</v>
       </c>
       <c r="J128" t="n">
-        <v>1.4982</v>
+        <v>1.0538</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.15</v>
+        <v>-0.0948</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.3</v>
+        <v>-2.0856</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.208</v>
+        <v>-0.1284</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.576</v>
+        <v>-2.8248</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.78</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3991</v>
+        <v>-0.2525</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.780200000000001</v>
+        <v>-5.555</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.89</v>
       </c>
       <c r="I132" t="n">
-        <v>1.8646</v>
+        <v>1.3841</v>
       </c>
       <c r="J132" t="n">
-        <v>54.0734</v>
+        <v>40.1389</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2233</v>
+        <v>0.2639</v>
       </c>
       <c r="J133" t="n">
-        <v>6.4757</v>
+        <v>7.6531</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0888</v>
+        <v>-0.0276</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.5752</v>
+        <v>-0.8004</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2291</v>
+        <v>-0.1607</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.6439</v>
+        <v>-4.6603</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.0453</v>
+        <v>-1.0261</v>
       </c>
       <c r="J136" t="n">
-        <v>-30.3137</v>
+        <v>-29.7569</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.55</v>
       </c>
       <c r="I137" t="n">
-        <v>0.826</v>
+        <v>0.7518</v>
       </c>
       <c r="J137" t="n">
-        <v>23.954</v>
+        <v>21.8022</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2168</v>
+        <v>0.2298</v>
       </c>
       <c r="J138" t="n">
-        <v>6.2872</v>
+        <v>6.6642</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1284</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.7236</v>
+        <v>-2.1576</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.89</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2397</v>
+        <v>-0.1435</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.9513</v>
+        <v>-4.1615</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.44</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="J141" t="n">
-        <v>-24.0729</v>
+        <v>-16.5619</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3806</v>
+        <v>1.2424</v>
       </c>
       <c r="J142" t="n">
-        <v>38.6568</v>
+        <v>34.7872</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.46</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1624</v>
+        <v>1.1003</v>
       </c>
       <c r="J143" t="n">
-        <v>32.5472</v>
+        <v>30.8084</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.38</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9821</v>
       </c>
       <c r="J144" t="n">
-        <v>27.846</v>
+        <v>27.4988</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.86</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5703</v>
+        <v>-0.5054</v>
       </c>
       <c r="J145" t="n">
-        <v>-15.9684</v>
+        <v>-14.1512</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.3163</v>
+        <v>-1.3371</v>
       </c>
       <c r="J146" t="n">
-        <v>-36.8564</v>
+        <v>-37.4388</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.66</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9537</v>
+        <v>1.1372</v>
       </c>
       <c r="J147" t="n">
-        <v>26.7036</v>
+        <v>31.8416</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0599</v>
+        <v>0.0439</v>
       </c>
       <c r="J148" t="n">
-        <v>1.6772</v>
+        <v>1.2292</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.79</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3893</v>
+        <v>-0.2447</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.9004</v>
+        <v>-6.8516</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.71</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5001</v>
+        <v>-0.3226</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.0028</v>
+        <v>-9.0328</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.3791</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.1868</v>
+        <v>-10.6148</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.72</v>
       </c>
       <c r="I152" t="n">
-        <v>1.692</v>
+        <v>1.4542</v>
       </c>
       <c r="J152" t="n">
-        <v>40.608</v>
+        <v>34.9008</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.8722</v>
+        <v>0.8517</v>
       </c>
       <c r="J153" t="n">
-        <v>20.9328</v>
+        <v>20.4408</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.88</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4972</v>
+        <v>-0.4338</v>
       </c>
       <c r="J154" t="n">
-        <v>-11.9328</v>
+        <v>-10.4112</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.702</v>
+        <v>-0.6492</v>
       </c>
       <c r="J155" t="n">
-        <v>-16.848</v>
+        <v>-15.5808</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7499</v>
+        <v>-0.7007</v>
       </c>
       <c r="J156" t="n">
-        <v>-17.9976</v>
+        <v>-16.8168</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.28</v>
       </c>
       <c r="I157" t="n">
-        <v>0.498</v>
+        <v>0.5867</v>
       </c>
       <c r="J157" t="n">
-        <v>11.952</v>
+        <v>14.0808</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.24</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4441</v>
+        <v>0.5155</v>
       </c>
       <c r="J158" t="n">
-        <v>10.6584</v>
+        <v>12.372</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.15</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3134</v>
+        <v>0.3485</v>
       </c>
       <c r="J159" t="n">
-        <v>7.5216</v>
+        <v>8.364000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.65</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.3818</v>
       </c>
       <c r="J160" t="n">
-        <v>-13.9728</v>
+        <v>-9.1632</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6196</v>
+        <v>-0.4096</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.8704</v>
+        <v>-9.830399999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>0.842</v>
+        <v>0.7788</v>
       </c>
       <c r="J162" t="n">
-        <v>13.472</v>
+        <v>12.4608</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.69</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8312</v>
+        <v>0.769</v>
       </c>
       <c r="J163" t="n">
-        <v>13.2992</v>
+        <v>12.304</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.63</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7653</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>12.2448</v>
+        <v>11.3632</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.52</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6319</v>
+        <v>0.602</v>
       </c>
       <c r="J165" t="n">
-        <v>10.1104</v>
+        <v>9.632</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0621</v>
+        <v>-0.0083</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.9936</v>
+        <v>-0.1328</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.85</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1311</v>
+        <v>-0.1302</v>
       </c>
       <c r="J167" t="n">
-        <v>-2.0976</v>
+        <v>-2.0832</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.78</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2426</v>
+        <v>-0.208</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.8816</v>
+        <v>-3.328</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2583</v>
+        <v>-0.2186</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.1328</v>
+        <v>-3.4976</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.45</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.7623</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="J170" t="n">
-        <v>-12.1968</v>
+        <v>-8.331200000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.38</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.5868</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.6208</v>
+        <v>-9.3888</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.86</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.132</v>
+        <v>-0.1292</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.376</v>
+        <v>-2.3256</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1485</v>
+        <v>-0.1406</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.673</v>
+        <v>-2.5308</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.71</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3744</v>
+        <v>-0.2859</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.7392</v>
+        <v>-5.1462</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.52</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6798</v>
+        <v>-0.4607</v>
       </c>
       <c r="J175" t="n">
-        <v>-12.2364</v>
+        <v>-8.2926</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7584</v>
+        <v>-0.517</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.6512</v>
+        <v>-9.305999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.69</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5198</v>
+        <v>1.3427</v>
       </c>
       <c r="J177" t="n">
-        <v>27.3564</v>
+        <v>24.1686</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9837</v>
+        <v>1.0074</v>
       </c>
       <c r="J178" t="n">
-        <v>17.7066</v>
+        <v>18.1332</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.27</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6073</v>
+        <v>0.699</v>
       </c>
       <c r="J179" t="n">
-        <v>10.9314</v>
+        <v>12.582</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>10.4976</v>
+        <v>12.1662</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.07</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0953</v>
+        <v>0.1814</v>
       </c>
       <c r="J181" t="n">
-        <v>1.7154</v>
+        <v>3.2652</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6422</v>
+        <v>0.7844</v>
       </c>
       <c r="J182" t="n">
-        <v>15.4128</v>
+        <v>18.8256</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2756</v>
+        <v>0.3136</v>
       </c>
       <c r="J183" t="n">
-        <v>6.6144</v>
+        <v>7.5264</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0578</v>
+        <v>0.0857</v>
       </c>
       <c r="J184" t="n">
-        <v>1.3872</v>
+        <v>2.0568</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.83</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3507</v>
+        <v>-0.2141</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.4168</v>
+        <v>-5.1384</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3507</v>
+        <v>-0.2141</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.4168</v>
+        <v>-5.1384</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.41</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1097</v>
+        <v>1.0606</v>
       </c>
       <c r="J187" t="n">
-        <v>26.6328</v>
+        <v>25.4544</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.31</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8923</v>
+        <v>0.8672</v>
       </c>
       <c r="J188" t="n">
-        <v>21.4152</v>
+        <v>20.8128</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2061</v>
+        <v>0.2152</v>
       </c>
       <c r="J189" t="n">
-        <v>4.9464</v>
+        <v>5.1648</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.9</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4268</v>
+        <v>-0.3666</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.2432</v>
+        <v>-8.798400000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.0752</v>
+        <v>-1.0602</v>
       </c>
       <c r="J191" t="n">
-        <v>-25.8048</v>
+        <v>-25.4448</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.14</v>
       </c>
       <c r="I192" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J192" t="n">
-        <v>45.3046</v>
+        <v>40.3436</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.27</v>
       </c>
       <c r="I193" t="n">
-        <v>0.697</v>
+        <v>0.7165</v>
       </c>
       <c r="J193" t="n">
-        <v>15.334</v>
+        <v>15.763</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2205</v>
+        <v>0.2945</v>
       </c>
       <c r="J194" t="n">
-        <v>4.851</v>
+        <v>6.479</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.92</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4298</v>
+        <v>-0.3528</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.4556</v>
+        <v>-7.7616</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.74</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8747</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="J196" t="n">
-        <v>-19.2434</v>
+        <v>-18.3524</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.24</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4538</v>
+        <v>0.5261</v>
       </c>
       <c r="J197" t="n">
-        <v>9.983599999999999</v>
+        <v>11.5742</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.21</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4119</v>
+        <v>0.471</v>
       </c>
       <c r="J198" t="n">
-        <v>9.0618</v>
+        <v>10.362</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.85</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2975</v>
+        <v>-0.1833</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.545</v>
+        <v>-4.0326</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3132</v>
+        <v>-0.1936</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.8904</v>
+        <v>-4.2592</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5646</v>
+        <v>-0.3693</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.4212</v>
+        <v>-8.124599999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.93</v>
       </c>
       <c r="I202" t="n">
-        <v>1.9715</v>
+        <v>1.6735</v>
       </c>
       <c r="J202" t="n">
-        <v>43.373</v>
+        <v>36.817</v>
       </c>
     </row>
     <row r="203">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2089</v>
+        <v>0.2749</v>
       </c>
       <c r="J204" t="n">
-        <v>4.5958</v>
+        <v>6.0478</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.98</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2222</v>
+        <v>-0.1437</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.8884</v>
+        <v>-3.1614</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-1.0815</v>
+        <v>-1.067</v>
       </c>
       <c r="J206" t="n">
-        <v>-23.793</v>
+        <v>-23.474</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.38</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6128</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J207" t="n">
-        <v>13.4816</v>
+        <v>16.3548</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.33</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5503</v>
+        <v>0.659</v>
       </c>
       <c r="J208" t="n">
-        <v>12.1066</v>
+        <v>14.498</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1248</v>
+        <v>-0.0658</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.7456</v>
+        <v>-1.4476</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3605</v>
+        <v>-0.2218</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.931</v>
+        <v>-4.8796</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.64</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6006</v>
+        <v>-0.3952</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.2132</v>
+        <v>-8.6944</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.88</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1383</v>
+        <v>1.2929</v>
       </c>
       <c r="J212" t="n">
-        <v>27.3192</v>
+        <v>31.0296</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.12</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2257</v>
+        <v>0.2677</v>
       </c>
       <c r="J213" t="n">
-        <v>5.4168</v>
+        <v>6.4248</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.218</v>
+        <v>-0.1211</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.232</v>
+        <v>-2.9064</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4293</v>
+        <v>-0.2686</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.3032</v>
+        <v>-6.4464</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.74</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4829</v>
+        <v>-0.3075</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.5896</v>
+        <v>-7.38</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.69</v>
       </c>
       <c r="I217" t="n">
-        <v>1.598</v>
+        <v>1.3886</v>
       </c>
       <c r="J217" t="n">
-        <v>38.352</v>
+        <v>33.3264</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.37</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9644</v>
+        <v>0.9577</v>
       </c>
       <c r="J218" t="n">
-        <v>23.1456</v>
+        <v>22.9848</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.27</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7357</v>
+        <v>0.731</v>
       </c>
       <c r="J219" t="n">
-        <v>17.6568</v>
+        <v>17.544</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.04</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0611</v>
+        <v>0.1257</v>
       </c>
       <c r="J220" t="n">
-        <v>1.4664</v>
+        <v>3.0168</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.5</v>
       </c>
       <c r="I221" t="n">
-        <v>-1.3573</v>
+        <v>-1.3853</v>
       </c>
       <c r="J221" t="n">
-        <v>-32.5752</v>
+        <v>-33.2472</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.56</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7935</v>
+        <v>0.709</v>
       </c>
       <c r="J222" t="n">
-        <v>33.327</v>
+        <v>29.778</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.279</v>
+        <v>0.2396</v>
       </c>
       <c r="J223" t="n">
-        <v>11.718</v>
+        <v>10.0632</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.14</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2451</v>
+        <v>0.2138</v>
       </c>
       <c r="J224" t="n">
-        <v>10.2942</v>
+        <v>8.9796</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0174</v>
+        <v>0.0134</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.7308</v>
+        <v>0.5628</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.73</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5008</v>
+        <v>-0.3203</v>
       </c>
       <c r="J226" t="n">
-        <v>-21.0336</v>
+        <v>-13.4526</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.34</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5649</v>
+        <v>0.519</v>
       </c>
       <c r="J227" t="n">
-        <v>23.7258</v>
+        <v>21.798</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.13</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2701</v>
+        <v>0.2303</v>
       </c>
       <c r="J228" t="n">
-        <v>11.3442</v>
+        <v>9.672599999999999</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.95</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.143</v>
+        <v>-0.0779</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.006</v>
+        <v>-3.2718</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3142</v>
+        <v>-0.1902</v>
       </c>
       <c r="J230" t="n">
-        <v>-13.1964</v>
+        <v>-7.9884</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3444</v>
+        <v>-0.2109</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.4648</v>
+        <v>-8.857799999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.14</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3333</v>
+        <v>0.3629</v>
       </c>
       <c r="J232" t="n">
-        <v>6.3327</v>
+        <v>6.8951</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.13</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3177</v>
+        <v>0.3426</v>
       </c>
       <c r="J233" t="n">
-        <v>6.0363</v>
+        <v>6.5094</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.85</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2719</v>
+        <v>-0.1754</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.1661</v>
+        <v>-3.3326</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.72</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4697</v>
+        <v>-0.304</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.924300000000001</v>
+        <v>-5.776</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6026</v>
+        <v>-0.3985</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.4494</v>
+        <v>-7.5715</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.76</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6284</v>
+        <v>1.416</v>
       </c>
       <c r="J237" t="n">
-        <v>30.9396</v>
+        <v>26.904</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.6</v>
       </c>
       <c r="I238" t="n">
-        <v>1.3319</v>
+        <v>1.2269</v>
       </c>
       <c r="J238" t="n">
-        <v>25.3061</v>
+        <v>23.3111</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.43</v>
       </c>
       <c r="I239" t="n">
-        <v>0.9813</v>
+        <v>1.0165</v>
       </c>
       <c r="J239" t="n">
-        <v>18.6447</v>
+        <v>19.3135</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.38</v>
       </c>
       <c r="I240" t="n">
-        <v>0.8514</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="J240" t="n">
-        <v>16.1766</v>
+        <v>17.6871</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8794</v>
+        <v>-0.8393</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.7086</v>
+        <v>-15.9467</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.3</v>
       </c>
       <c r="I242" t="n">
-        <v>1.4155</v>
+        <v>1.2031</v>
       </c>
       <c r="J242" t="n">
-        <v>22.648</v>
+        <v>19.2496</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.7</v>
       </c>
       <c r="I243" t="n">
-        <v>0.8405</v>
+        <v>0.778</v>
       </c>
       <c r="J243" t="n">
-        <v>13.448</v>
+        <v>12.448</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.65</v>
       </c>
       <c r="I244" t="n">
-        <v>0.786</v>
+        <v>0.7291</v>
       </c>
       <c r="J244" t="n">
-        <v>12.576</v>
+        <v>11.6656</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0457</v>
+        <v>0.0878</v>
       </c>
       <c r="J245" t="n">
-        <v>0.7312</v>
+        <v>1.4048</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.86</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3719</v>
+        <v>-0.2237</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.9504</v>
+        <v>-3.5792</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.08</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2881</v>
+        <v>0.2283</v>
       </c>
       <c r="J247" t="n">
-        <v>4.6096</v>
+        <v>3.6528</v>
       </c>
     </row>
     <row r="248">
@@ -12309,10 +12309,10 @@
         <v>0.86</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1721</v>
+        <v>-0.1488</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.7536</v>
+        <v>-2.3808</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.54</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.6762</v>
+        <v>-0.4551</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.8192</v>
+        <v>-7.2816</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.43</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.8127</v>
+        <v>-0.5568</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.0032</v>
+        <v>-8.908799999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3285</v>
+        <v>0.3546</v>
       </c>
       <c r="J252" t="n">
-        <v>7.884</v>
+        <v>8.510400000000001</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.068</v>
+        <v>0.032</v>
       </c>
       <c r="J253" t="n">
-        <v>1.632</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1527</v>
+        <v>-0.121</v>
       </c>
       <c r="J254" t="n">
-        <v>-3.6648</v>
+        <v>-2.904</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.68</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5173</v>
+        <v>-0.3384</v>
       </c>
       <c r="J255" t="n">
-        <v>-12.4152</v>
+        <v>-8.121600000000001</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.61</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6096</v>
+        <v>-0.4042</v>
       </c>
       <c r="J256" t="n">
-        <v>-14.6304</v>
+        <v>-9.700799999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.56</v>
       </c>
       <c r="I257" t="n">
-        <v>1.3278</v>
+        <v>1.2111</v>
       </c>
       <c r="J257" t="n">
-        <v>31.8672</v>
+        <v>29.0664</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.52</v>
       </c>
       <c r="I258" t="n">
-        <v>1.2493</v>
+        <v>1.1607</v>
       </c>
       <c r="J258" t="n">
-        <v>29.9832</v>
+        <v>27.8568</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.16</v>
       </c>
       <c r="I259" t="n">
-        <v>0.39</v>
+        <v>0.4573</v>
       </c>
       <c r="J259" t="n">
-        <v>9.359999999999999</v>
+        <v>10.9752</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.06</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1048</v>
+        <v>0.1778</v>
       </c>
       <c r="J260" t="n">
-        <v>2.5152</v>
+        <v>4.2672</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.83</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6641</v>
+        <v>-0.6029</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.9384</v>
+        <v>-14.4696</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.62</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8838</v>
+        <v>1.0733</v>
       </c>
       <c r="J262" t="n">
-        <v>20.3274</v>
+        <v>24.6859</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.36</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5828</v>
+        <v>0.7037</v>
       </c>
       <c r="J263" t="n">
-        <v>13.4044</v>
+        <v>16.1851</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2886</v>
+        <v>-0.1716</v>
       </c>
       <c r="J264" t="n">
-        <v>-6.6378</v>
+        <v>-3.9468</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.71</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.3314</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.8358</v>
+        <v>-7.6222</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.65</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5906</v>
+        <v>-0.3876</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.5838</v>
+        <v>-8.9148</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.44</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1171</v>
+        <v>1.072</v>
       </c>
       <c r="J267" t="n">
-        <v>25.6933</v>
+        <v>24.656</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I268" t="n">
-        <v>1.0118</v>
+        <v>0.9977</v>
       </c>
       <c r="J268" t="n">
-        <v>23.2714</v>
+        <v>22.9471</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.11</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2841</v>
+        <v>0.3381</v>
       </c>
       <c r="J269" t="n">
-        <v>6.5343</v>
+        <v>7.7763</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0559</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.2024</v>
+        <v>1.2857</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.87</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5467</v>
+        <v>-0.4799</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.5741</v>
+        <v>-11.0377</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.75</v>
       </c>
       <c r="I272" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J272" t="n">
-        <v>26.7709</v>
+        <v>23.8394</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>2.27</v>
       </c>
       <c r="I273" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J273" t="n">
-        <v>26.7709</v>
+        <v>23.8394</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.65</v>
       </c>
       <c r="I274" t="n">
-        <v>1.2161</v>
+        <v>1.2404</v>
       </c>
       <c r="J274" t="n">
-        <v>15.8093</v>
+        <v>16.1252</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.25</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4339</v>
+        <v>0.5659</v>
       </c>
       <c r="J275" t="n">
-        <v>5.6407</v>
+        <v>7.3567</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.07</v>
       </c>
       <c r="I276" t="n">
-        <v>0.0037</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="J276" t="n">
-        <v>0.0481</v>
+        <v>1.2623</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.59</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.4233</v>
+        <v>-0.3477</v>
       </c>
       <c r="J277" t="n">
-        <v>-5.5029</v>
+        <v>-4.5201</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.54</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.5018</v>
+        <v>-0.4</v>
       </c>
       <c r="J278" t="n">
-        <v>-6.5234</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.44</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.6945</v>
+        <v>-0.4931</v>
       </c>
       <c r="J279" t="n">
-        <v>-9.028499999999999</v>
+        <v>-6.4103</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.39</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.7764</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.0932</v>
+        <v>-7.0304</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.37</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.8068</v>
+        <v>-0.5604</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.4884</v>
+        <v>-7.2852</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.93</v>
       </c>
       <c r="I282" t="n">
-        <v>1.8915</v>
+        <v>1.5971</v>
       </c>
       <c r="J282" t="n">
-        <v>32.1555</v>
+        <v>27.1507</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.57</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2443</v>
+        <v>1.1815</v>
       </c>
       <c r="J283" t="n">
-        <v>21.1531</v>
+        <v>20.0855</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.29</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6086</v>
+        <v>0.7241</v>
       </c>
       <c r="J284" t="n">
-        <v>10.3462</v>
+        <v>12.3097</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.28</v>
       </c>
       <c r="I285" t="n">
-        <v>0.5861</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="J285" t="n">
-        <v>9.963699999999999</v>
+        <v>11.9187</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.16</v>
       </c>
       <c r="I286" t="n">
-        <v>0.3052</v>
+        <v>0.4091</v>
       </c>
       <c r="J286" t="n">
-        <v>5.1884</v>
+        <v>6.9547</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.74</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.3053</v>
+        <v>-0.2497</v>
       </c>
       <c r="J287" t="n">
-        <v>-5.1901</v>
+        <v>-4.2449</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.7</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3689</v>
+        <v>-0.2895</v>
       </c>
       <c r="J288" t="n">
-        <v>-6.2713</v>
+        <v>-4.9215</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.68</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4019</v>
+        <v>-0.3086</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.8323</v>
+        <v>-5.2462</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.62</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.5187</v>
+        <v>-0.3621</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.8179</v>
+        <v>-6.1557</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.49</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7093</v>
+        <v>-0.4829</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.0581</v>
+        <v>-8.209300000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>2.18</v>
       </c>
       <c r="I292" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J292" t="n">
-        <v>41.186</v>
+        <v>36.676</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.61</v>
       </c>
       <c r="I293" t="n">
-        <v>1.3628</v>
+        <v>1.2436</v>
       </c>
       <c r="J293" t="n">
-        <v>27.256</v>
+        <v>24.872</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.4801</v>
+        <v>0.5779</v>
       </c>
       <c r="J294" t="n">
-        <v>9.602</v>
+        <v>11.558</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3074</v>
+        <v>0.402</v>
       </c>
       <c r="J295" t="n">
-        <v>6.148</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.63</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.1267</v>
+        <v>-1.1203</v>
       </c>
       <c r="J296" t="n">
-        <v>-22.534</v>
+        <v>-22.406</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.37</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6422</v>
+        <v>0.7832</v>
       </c>
       <c r="J297" t="n">
-        <v>12.844</v>
+        <v>15.664</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.91</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1598</v>
+        <v>-0.1141</v>
       </c>
       <c r="J298" t="n">
-        <v>-3.196</v>
+        <v>-2.282</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.86</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.261</v>
+        <v>-0.1667</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.22</v>
+        <v>-3.334</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.8</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3577</v>
+        <v>-0.2276</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.154</v>
+        <v>-4.552</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.59</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6431</v>
+        <v>-0.428</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.862</v>
+        <v>-8.56</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.09</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2639</v>
+        <v>0.2072</v>
       </c>
       <c r="J302" t="n">
-        <v>5.0141</v>
+        <v>3.9368</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.114</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.166</v>
+        <v>-1.8639</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1516</v>
+        <v>-0.1207</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.8804</v>
+        <v>-2.2933</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.74</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4326</v>
+        <v>-0.2808</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.2194</v>
+        <v>-5.3352</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.66</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5438</v>
+        <v>-0.3571</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.3322</v>
+        <v>-6.7849</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.61</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8031</v>
+        <v>0.7245</v>
       </c>
       <c r="J307" t="n">
-        <v>15.2589</v>
+        <v>13.7655</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.38</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5336</v>
+        <v>0.4783</v>
       </c>
       <c r="J308" t="n">
-        <v>10.1384</v>
+        <v>9.0877</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.22</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2964</v>
+        <v>0.2986</v>
       </c>
       <c r="J309" t="n">
-        <v>5.6316</v>
+        <v>5.6734</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.11</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1316</v>
+        <v>0.1566</v>
       </c>
       <c r="J310" t="n">
-        <v>2.5004</v>
+        <v>2.9754</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.09</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0994</v>
+        <v>0.128</v>
       </c>
       <c r="J311" t="n">
-        <v>1.8886</v>
+        <v>2.432</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.42</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0765</v>
+        <v>1.0454</v>
       </c>
       <c r="J312" t="n">
-        <v>23.683</v>
+        <v>22.9988</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.21</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5906</v>
+        <v>0.5905</v>
       </c>
       <c r="J313" t="n">
-        <v>12.9932</v>
+        <v>12.991</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.19</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J314" t="n">
-        <v>11.7876</v>
+        <v>11.9196</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.14</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3743</v>
+        <v>0.4184</v>
       </c>
       <c r="J315" t="n">
-        <v>8.2346</v>
+        <v>9.204800000000001</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.86</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.5069</v>
       </c>
       <c r="J316" t="n">
-        <v>-12.5862</v>
+        <v>-11.1518</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.11</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2764</v>
+        <v>0.2923</v>
       </c>
       <c r="J317" t="n">
-        <v>6.0808</v>
+        <v>6.4306</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.01</v>
       </c>
       <c r="I318" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0555</v>
       </c>
       <c r="J318" t="n">
-        <v>1.7842</v>
+        <v>1.221</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.9</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1928</v>
+        <v>-0.1255</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.2416</v>
+        <v>-2.761</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.82</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3303</v>
+        <v>-0.2088</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.2666</v>
+        <v>-4.5936</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.74</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4481</v>
+        <v>-0.2878</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.8582</v>
+        <v>-6.3316</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.91</v>
       </c>
       <c r="I322" t="n">
-        <v>1.869</v>
+        <v>1.5792</v>
       </c>
       <c r="J322" t="n">
-        <v>33.642</v>
+        <v>28.4256</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.69</v>
       </c>
       <c r="I323" t="n">
-        <v>1.4833</v>
+        <v>1.3258</v>
       </c>
       <c r="J323" t="n">
-        <v>26.6994</v>
+        <v>23.8644</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.52</v>
       </c>
       <c r="I324" t="n">
-        <v>1.1524</v>
+        <v>1.1248</v>
       </c>
       <c r="J324" t="n">
-        <v>20.7432</v>
+        <v>20.2464</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.1</v>
       </c>
       <c r="I325" t="n">
-        <v>0.1563</v>
+        <v>0.2511</v>
       </c>
       <c r="J325" t="n">
-        <v>2.8134</v>
+        <v>4.5198</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.91</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5026</v>
+        <v>-0.4244</v>
       </c>
       <c r="J326" t="n">
-        <v>-9.046799999999999</v>
+        <v>-7.6392</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.08</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2934</v>
+        <v>0.3057</v>
       </c>
       <c r="J327" t="n">
-        <v>5.2812</v>
+        <v>5.5026</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.04</v>
       </c>
       <c r="I328" t="n">
-        <v>0.219</v>
+        <v>0.2078</v>
       </c>
       <c r="J328" t="n">
-        <v>3.942</v>
+        <v>3.7404</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.66</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.5092</v>
+        <v>-0.341</v>
       </c>
       <c r="J329" t="n">
-        <v>-9.1656</v>
+        <v>-6.138</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.54</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.6732</v>
+        <v>-0.4533</v>
       </c>
       <c r="J330" t="n">
-        <v>-12.1176</v>
+        <v>-8.1594</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.43</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8105</v>
+        <v>-0.5552</v>
       </c>
       <c r="J331" t="n">
-        <v>-14.589</v>
+        <v>-9.993600000000001</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.36</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9124</v>
+        <v>0.9202</v>
       </c>
       <c r="J332" t="n">
-        <v>20.9852</v>
+        <v>21.1646</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.32</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8213</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J333" t="n">
-        <v>18.8899</v>
+        <v>19.1153</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.32</v>
       </c>
       <c r="I334" t="n">
-        <v>0.8213</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J334" t="n">
-        <v>18.8899</v>
+        <v>19.1153</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.11</v>
       </c>
       <c r="I335" t="n">
-        <v>0.2506</v>
+        <v>0.3235</v>
       </c>
       <c r="J335" t="n">
-        <v>5.7638</v>
+        <v>7.4405</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>1.04</v>
       </c>
       <c r="I336" t="n">
-        <v>0.0383</v>
+        <v>0.1118</v>
       </c>
       <c r="J336" t="n">
-        <v>0.8809</v>
+        <v>2.5714</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.92</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1263</v>
+        <v>-0.1011</v>
       </c>
       <c r="J337" t="n">
-        <v>-2.9049</v>
+        <v>-2.3253</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.9</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1658</v>
+        <v>-0.1233</v>
       </c>
       <c r="J338" t="n">
-        <v>-3.8134</v>
+        <v>-2.8359</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.9</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1658</v>
+        <v>-0.1233</v>
       </c>
       <c r="J339" t="n">
-        <v>-3.8134</v>
+        <v>-2.8359</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.88</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2125</v>
+        <v>-0.144</v>
       </c>
       <c r="J340" t="n">
-        <v>-4.8875</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3029</v>
+        <v>-0.1951</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.9667</v>
+        <v>-4.4873</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7556/event_7556_evp_summary.xlsx
+++ b/database/event/7556/event_7556_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.0268</v>
+        <v>8.9345</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7445</v>
+        <v>3.7062</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4371</v>
+        <v>3.443</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0268</v>
+        <v>8.9345</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2594</v>
+        <v>2.9912</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7674</v>
+        <v>5.9433</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7972</v>
+        <v>3.8218</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7972</v>
+        <v>3.8218</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7674</v>
+        <v>5.9433</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -529,7 +529,7 @@
         <v>213</v>
       </c>
       <c r="M2" t="n">
-        <v>9.5646</v>
+        <v>9.7651</v>
       </c>
       <c r="N2" t="n">
         <v>318</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4162</v>
+        <v>6.6161</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6616</v>
+        <v>2.7445</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2586</v>
+        <v>2.3876</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4162</v>
+        <v>6.6161</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0569</v>
+        <v>1.9924</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3593</v>
+        <v>4.6237</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0569</v>
+        <v>1.9924</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0569</v>
+        <v>1.9924</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3593</v>
+        <v>4.6237</v>
       </c>
       <c r="K3" t="n">
         <v>105</v>
@@ -575,7 +575,7 @@
         <v>213</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4162</v>
+        <v>6.6161</v>
       </c>
       <c r="N3" t="n">
         <v>318</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5349</v>
+        <v>5.6768</v>
       </c>
       <c r="C4" t="n">
-        <v>2.296</v>
+        <v>2.3549</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8607</v>
+        <v>1.96</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5349</v>
+        <v>5.6768</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6084</v>
+        <v>3.6351</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9264</v>
+        <v>2.0417</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2276</v>
+        <v>7.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>3.758</v>
+        <v>3.8336</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9264</v>
+        <v>2.0417</v>
       </c>
       <c r="K4" t="n">
         <v>85</v>
@@ -621,7 +621,7 @@
         <v>152</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6844</v>
+        <v>5.8753</v>
       </c>
       <c r="N4" t="n">
         <v>237</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4949</v>
+        <v>5.5112</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2794</v>
+        <v>2.2862</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8427</v>
+        <v>1.8846</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4949</v>
+        <v>5.5112</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0806</v>
+        <v>2.7725</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4144</v>
+        <v>2.7387</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4047</v>
+        <v>3.3432</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5447</v>
+        <v>3.4294</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4144</v>
+        <v>2.7387</v>
       </c>
       <c r="K5" t="n">
         <v>146</v>
@@ -667,7 +667,7 @@
         <v>97</v>
       </c>
       <c r="M5" t="n">
-        <v>5.9591</v>
+        <v>6.1681</v>
       </c>
       <c r="N5" t="n">
         <v>243</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2239</v>
+        <v>5.4162</v>
       </c>
       <c r="C6" t="n">
-        <v>2.167</v>
+        <v>2.2468</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7203</v>
+        <v>1.8414</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2239</v>
+        <v>5.4162</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7721</v>
+        <v>0.8355</v>
       </c>
       <c r="H6" t="n">
-        <v>10.9854</v>
+        <v>10.5815</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7119</v>
+        <v>5.7139</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7721</v>
+        <v>0.8355</v>
       </c>
       <c r="K6" t="n">
         <v>82</v>
@@ -713,7 +713,7 @@
         <v>72</v>
       </c>
       <c r="M6" t="n">
-        <v>6.484</v>
+        <v>6.549399999999999</v>
       </c>
       <c r="N6" t="n">
         <v>154</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.178</v>
+        <v>5.412</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1479</v>
+        <v>2.245</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6996</v>
+        <v>1.8395</v>
       </c>
       <c r="E7" t="n">
-        <v>5.178</v>
+        <v>5.412</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9074</v>
+        <v>0.8084</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2706</v>
+        <v>4.6036</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9074</v>
+        <v>0.8084</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9074</v>
+        <v>0.8084</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2706</v>
+        <v>4.6036</v>
       </c>
       <c r="K7" t="n">
         <v>105</v>
@@ -759,7 +759,7 @@
         <v>213</v>
       </c>
       <c r="M7" t="n">
-        <v>5.178</v>
+        <v>5.412</v>
       </c>
       <c r="N7" t="n">
         <v>318</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6703</v>
+        <v>4.7122</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9373</v>
+        <v>1.9547</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4704</v>
+        <v>1.5209</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6703</v>
+        <v>4.7122</v>
       </c>
       <c r="F8" t="n">
-        <v>3.9418</v>
+        <v>3.9178</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7285</v>
+        <v>0.7944</v>
       </c>
       <c r="H8" t="n">
-        <v>8.402100000000001</v>
+        <v>8.0322</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3687</v>
+        <v>4.3373</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7285</v>
+        <v>0.7944</v>
       </c>
       <c r="K8" t="n">
         <v>82</v>
@@ -805,7 +805,7 @@
         <v>72</v>
       </c>
       <c r="M8" t="n">
-        <v>5.0972</v>
+        <v>5.1317</v>
       </c>
       <c r="N8" t="n">
         <v>154</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6542</v>
+        <v>4.6743</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9307</v>
+        <v>1.939</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4631</v>
+        <v>1.5036</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6542</v>
+        <v>4.6743</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8809</v>
+        <v>1.821</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7733</v>
+        <v>2.8533</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8809</v>
+        <v>1.821</v>
       </c>
       <c r="I9" t="n">
-        <v>0.978</v>
+        <v>0.9833</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7733</v>
+        <v>2.8533</v>
       </c>
       <c r="K9" t="n">
         <v>85</v>
@@ -851,7 +851,7 @@
         <v>152</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7513</v>
+        <v>3.8366</v>
       </c>
       <c r="N9" t="n">
         <v>237</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9336</v>
+        <v>4.0641</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6317</v>
+        <v>1.6859</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1378</v>
+        <v>1.2259</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9336</v>
+        <v>4.0641</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6429</v>
+        <v>1.5801</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2907</v>
+        <v>2.484</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6429</v>
+        <v>1.5801</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7105</v>
+        <v>1.6208</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2907</v>
+        <v>2.484</v>
       </c>
       <c r="K10" t="n">
         <v>146</v>
@@ -897,7 +897,7 @@
         <v>97</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0012</v>
+        <v>4.1048</v>
       </c>
       <c r="N10" t="n">
         <v>243</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6537</v>
+        <v>3.6968</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5156</v>
+        <v>1.5335</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0114</v>
+        <v>1.0587</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6537</v>
+        <v>3.6968</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3241</v>
+        <v>3.2955</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3296</v>
+        <v>0.4013</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2257</v>
+        <v>5.979</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2371</v>
+        <v>3.2286</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3296</v>
+        <v>0.4013</v>
       </c>
       <c r="K11" t="n">
         <v>82</v>
@@ -943,7 +943,7 @@
         <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5667</v>
+        <v>3.6299</v>
       </c>
       <c r="N11" t="n">
         <v>154</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5449</v>
+        <v>3.6593</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4705</v>
+        <v>1.518</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9623</v>
+        <v>1.0416</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5449</v>
+        <v>3.6593</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8534</v>
+        <v>2.813</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6915</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5671</v>
+        <v>4.3869</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3747</v>
+        <v>2.3689</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6915</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>85</v>
@@ -989,7 +989,7 @@
         <v>152</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0662</v>
+        <v>3.2152</v>
       </c>
       <c r="N12" t="n">
         <v>237</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1814</v>
+        <v>3.1649</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3197</v>
+        <v>1.3129</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7982</v>
+        <v>0.8165</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1814</v>
+        <v>3.1649</v>
       </c>
       <c r="F13" t="n">
-        <v>2.63</v>
+        <v>3.7085</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5514</v>
+        <v>-0.5436</v>
       </c>
       <c r="H13" t="n">
-        <v>2.63</v>
+        <v>7.3414</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7382</v>
+        <v>3.9643</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5514</v>
+        <v>-0.5436</v>
       </c>
       <c r="K13" t="n">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="L13" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2896</v>
+        <v>3.4207</v>
       </c>
       <c r="N13" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.143</v>
+        <v>3.1134</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3038</v>
+        <v>1.2915</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7809</v>
+        <v>0.7931</v>
       </c>
       <c r="E14" t="n">
-        <v>3.143</v>
+        <v>3.1134</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7963</v>
+        <v>2.429</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6533</v>
+        <v>0.6844</v>
       </c>
       <c r="H14" t="n">
-        <v>7.8894</v>
+        <v>2.5914</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1021</v>
+        <v>2.6582</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6533</v>
+        <v>0.6844</v>
       </c>
       <c r="K14" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="L14" t="n">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4488</v>
+        <v>3.3426</v>
       </c>
       <c r="N14" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8465</v>
+        <v>2.6269</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1808</v>
+        <v>1.0897</v>
       </c>
       <c r="D15" t="n">
-        <v>0.647</v>
+        <v>0.5716</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8465</v>
+        <v>2.6269</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1219</v>
+        <v>2.4286</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2754</v>
+        <v>0.1983</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4953</v>
+        <v>2.5905</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4953</v>
+        <v>2.6573</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2754</v>
+        <v>0.1983</v>
       </c>
       <c r="K15" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2199</v>
+        <v>2.8556</v>
       </c>
       <c r="N15" t="n">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7989</v>
+        <v>2.4671</v>
       </c>
       <c r="C16" t="n">
-        <v>1.161</v>
+        <v>1.0234</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.4989</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7989</v>
+        <v>2.4671</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5911</v>
+        <v>2.7757</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2078</v>
+        <v>-0.3086</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5911</v>
+        <v>3.3502</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6977</v>
+        <v>3.3502</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2078</v>
+        <v>-0.3086</v>
       </c>
       <c r="K16" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L16" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9055</v>
+        <v>3.0416</v>
       </c>
       <c r="N16" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2364</v>
+        <v>2.207</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9277</v>
+        <v>0.9155</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3716</v>
+        <v>0.3805</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2364</v>
+        <v>2.207</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7371</v>
+        <v>1.6375</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4993</v>
+        <v>0.5695</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7371</v>
+        <v>1.6375</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8085</v>
+        <v>1.6797</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4993</v>
+        <v>0.5695</v>
       </c>
       <c r="K17" t="n">
         <v>121</v>
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3078</v>
+        <v>2.2492</v>
       </c>
       <c r="N17" t="n">
         <v>172</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8646</v>
+        <v>1.7654</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7735</v>
+        <v>0.7323</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2038</v>
+        <v>0.1794</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8646</v>
+        <v>1.7654</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7296</v>
+        <v>1.6373</v>
       </c>
       <c r="G18" t="n">
-        <v>0.135</v>
+        <v>0.1281</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7296</v>
+        <v>1.6373</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8007</v>
+        <v>1.6795</v>
       </c>
       <c r="J18" t="n">
-        <v>0.135</v>
+        <v>0.1281</v>
       </c>
       <c r="K18" t="n">
         <v>121</v>
@@ -1265,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9357</v>
+        <v>1.8076</v>
       </c>
       <c r="N18" t="n">
         <v>172</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1927</v>
+        <v>1.1555</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4948</v>
+        <v>0.4793</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.0982</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1927</v>
+        <v>1.1555</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1927</v>
+        <v>1.1555</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1927</v>
+        <v>1.1555</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1927</v>
+        <v>1.1555</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1927</v>
+        <v>1.1555</v>
       </c>
       <c r="N19" t="n">
         <v>126</v>
@@ -1320,185 +1320,185 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6863</v>
+        <v>0.629</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2847</v>
+        <v>0.2609</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3282</v>
+        <v>-0.3379</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6863</v>
+        <v>0.629</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7819</v>
+        <v>0.6155</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0956</v>
+        <v>0.0135</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7819</v>
+        <v>0.6155</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8141</v>
+        <v>0.6155</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0956</v>
+        <v>0.0135</v>
       </c>
       <c r="K20" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7185</v>
+        <v>0.629</v>
       </c>
       <c r="N20" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6207</v>
+        <v>0.5984</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2575</v>
+        <v>0.2482</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3578</v>
+        <v>-0.3518</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6207</v>
+        <v>0.5984</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6446</v>
+        <v>0.185</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0239</v>
+        <v>0.4134</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6446</v>
+        <v>0.185</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6446</v>
+        <v>0.1898</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0239</v>
+        <v>0.4134</v>
       </c>
       <c r="K21" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6206999999999999</v>
+        <v>0.6032</v>
       </c>
       <c r="N21" t="n">
-        <v>150</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4758</v>
+        <v>0.5975</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1974</v>
+        <v>0.2479</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4232</v>
+        <v>-0.3522</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4758</v>
+        <v>0.5975</v>
       </c>
       <c r="F22" t="n">
-        <v>0.197</v>
+        <v>0.7037</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2788</v>
+        <v>-0.1062</v>
       </c>
       <c r="H22" t="n">
-        <v>0.197</v>
+        <v>0.7037</v>
       </c>
       <c r="I22" t="n">
-        <v>0.197</v>
+        <v>0.7218</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2788</v>
+        <v>-0.1062</v>
       </c>
       <c r="K22" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="L22" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4758</v>
+        <v>0.6156</v>
       </c>
       <c r="N22" t="n">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3866</v>
+        <v>0.505</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1604</v>
+        <v>0.2095</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4635</v>
+        <v>-0.3943</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3866</v>
+        <v>0.505</v>
       </c>
       <c r="F23" t="n">
-        <v>0.111</v>
+        <v>0.2085</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2756</v>
+        <v>0.2965</v>
       </c>
       <c r="H23" t="n">
-        <v>0.111</v>
+        <v>0.2085</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1156</v>
+        <v>0.2085</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2756</v>
+        <v>0.2965</v>
       </c>
       <c r="K23" t="n">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="L23" t="n">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3912</v>
+        <v>0.505</v>
       </c>
       <c r="N23" t="n">
-        <v>243</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3163</v>
+        <v>0.2684</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1312</v>
+        <v>0.1113</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4952</v>
+        <v>-0.502</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3163</v>
+        <v>0.2684</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3163</v>
+        <v>0.2684</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3163</v>
+        <v>0.2684</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3163</v>
+        <v>0.2684</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3163</v>
+        <v>0.2684</v>
       </c>
       <c r="N24" t="n">
         <v>126</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.151</v>
+        <v>0.0721</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0626</v>
+        <v>0.0299</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5698</v>
+        <v>-0.5914</v>
       </c>
       <c r="E25" t="n">
-        <v>0.151</v>
+        <v>0.0721</v>
       </c>
       <c r="F25" t="n">
-        <v>0.151</v>
+        <v>0.0721</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.151</v>
+        <v>0.0721</v>
       </c>
       <c r="I25" t="n">
-        <v>0.151</v>
+        <v>0.0721</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.151</v>
+        <v>0.0721</v>
       </c>
       <c r="N25" t="n">
         <v>88</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0334</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0401</v>
+        <v>0.0139</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5944</v>
+        <v>-0.609</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0334</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0334</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0334</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0334</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0334</v>
       </c>
       <c r="N26" t="n">
         <v>88</v>
@@ -1642,185 +1642,185 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1692</v>
+        <v>-0.212</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0702</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7144</v>
+        <v>-0.7207</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1692</v>
+        <v>-0.212</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7412</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.9104</v>
+        <v>-0.1342</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7412</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7412</v>
+        <v>-0.042</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9104</v>
+        <v>-0.1342</v>
       </c>
       <c r="K27" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1692</v>
+        <v>-0.1762</v>
       </c>
       <c r="N27" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2408</v>
+        <v>-0.2611</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0999</v>
+        <v>-0.1083</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7467</v>
+        <v>-0.7431</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2408</v>
+        <v>-0.2611</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2408</v>
+        <v>0.6708</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.9319</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2408</v>
+        <v>0.6708</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2408</v>
+        <v>0.6708</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.9319</v>
       </c>
       <c r="K28" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2408</v>
+        <v>-0.2611</v>
       </c>
       <c r="N28" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3023</v>
+        <v>-0.2685</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1254</v>
+        <v>-0.1114</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7745</v>
+        <v>-0.7464</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3023</v>
+        <v>-0.2685</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3023</v>
+        <v>-0.2685</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3023</v>
+        <v>-0.2685</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3023</v>
+        <v>-0.2685</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3023</v>
+        <v>-0.2685</v>
       </c>
       <c r="N29" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3511</v>
+        <v>-0.3411</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1456</v>
+        <v>-0.1415</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7965</v>
+        <v>-0.7795</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3511</v>
+        <v>-0.3411</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2269</v>
+        <v>-0.3411</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1242</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2269</v>
+        <v>-0.3411</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.118</v>
+        <v>-0.3411</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1242</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L30" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2422</v>
+        <v>-0.3411</v>
       </c>
       <c r="N30" t="n">
-        <v>154</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4157</v>
+        <v>-0.4667</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1724</v>
+        <v>-0.1936</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8257</v>
+        <v>-0.8367</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4157</v>
+        <v>-0.4667</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4157</v>
+        <v>-0.4667</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4157</v>
+        <v>-0.4667</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4157</v>
+        <v>-0.4667</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4157</v>
+        <v>-0.4667</v>
       </c>
       <c r="N31" t="n">
         <v>126</v>
@@ -1872,139 +1872,139 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7447</v>
+        <v>-0.6869</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3089</v>
+        <v>-0.2849</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9742</v>
+        <v>-0.9369</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7447</v>
+        <v>-0.6869</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7447</v>
+        <v>-1.6539</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7447</v>
+        <v>-1.6539</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7447</v>
+        <v>-0.8931</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="K32" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7447</v>
+        <v>0.07389999999999997</v>
       </c>
       <c r="N32" t="n">
-        <v>88</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8288</v>
+        <v>-0.8062</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3438</v>
+        <v>-0.3344</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0122</v>
+        <v>-0.9912</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8288</v>
+        <v>-0.8062</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8288</v>
+        <v>-0.8062</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8288</v>
+        <v>-0.8062</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8288</v>
+        <v>-0.8062</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8288</v>
+        <v>-0.8062</v>
       </c>
       <c r="N33" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0842</v>
+        <v>-0.8779</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4497</v>
+        <v>-0.3642</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1275</v>
+        <v>-1.0238</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0842</v>
+        <v>-0.8779</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.0327</v>
+        <v>-0.8779</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9485</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.0327</v>
+        <v>-0.8779</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0569</v>
+        <v>-0.8779</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9485</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="L34" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1083999999999999</v>
+        <v>-0.8779</v>
       </c>
       <c r="N34" t="n">
-        <v>237</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1078</v>
+        <v>-0.948</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4595</v>
+        <v>-0.3933</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1381</v>
+        <v>-1.0558</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1078</v>
+        <v>-0.948</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.803</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2323</v>
+        <v>-0.145</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.803</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9115</v>
+        <v>-0.8237</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2323</v>
+        <v>-0.145</v>
       </c>
       <c r="K35" t="n">
         <v>146</v>
@@ -2047,7 +2047,7 @@
         <v>97</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1438</v>
+        <v>-0.9687</v>
       </c>
       <c r="N35" t="n">
         <v>243</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1617</v>
+        <v>-1.215</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4819</v>
+        <v>-0.504</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1625</v>
+        <v>-1.1773</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1617</v>
+        <v>-1.215</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1617</v>
+        <v>-1.215</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1617</v>
+        <v>-1.215</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1617</v>
+        <v>-1.215</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1617</v>
+        <v>-1.215</v>
       </c>
       <c r="N36" t="n">
         <v>88</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3971</v>
+        <v>-1.4436</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5795</v>
+        <v>-0.5988</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2687</v>
+        <v>-1.2814</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3971</v>
+        <v>-1.4436</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8323</v>
+        <v>-0.8437</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5648</v>
+        <v>-0.5999</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8323</v>
+        <v>-0.8437</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8323</v>
+        <v>-0.8437</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5648</v>
+        <v>-0.5999</v>
       </c>
       <c r="K37" t="n">
         <v>115</v>
@@ -2139,7 +2139,7 @@
         <v>35</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3971</v>
+        <v>-1.4436</v>
       </c>
       <c r="N37" t="n">
         <v>150</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6997</v>
+        <v>-1.6516</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.6851</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.4053</v>
+        <v>-1.376</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6997</v>
+        <v>-1.6516</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0498</v>
+        <v>0.0182</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.7495</v>
+        <v>-1.6698</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0498</v>
+        <v>0.0182</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0498</v>
+        <v>0.0182</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.7495</v>
+        <v>-1.6698</v>
       </c>
       <c r="K38" t="n">
         <v>105</v>
@@ -2185,7 +2185,7 @@
         <v>213</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6997</v>
+        <v>-1.6516</v>
       </c>
       <c r="N38" t="n">
         <v>318</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8319</v>
+        <v>-1.7812</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7599</v>
+        <v>-0.7389</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.465</v>
+        <v>-1.435</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8319</v>
+        <v>-1.7812</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1324</v>
+        <v>-1.0669</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.6995</v>
+        <v>-0.7143</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1324</v>
+        <v>-1.0669</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.179</v>
+        <v>-1.0944</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6995</v>
+        <v>-0.7143</v>
       </c>
       <c r="K39" t="n">
         <v>121</v>
@@ -2231,7 +2231,7 @@
         <v>51</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8785</v>
+        <v>-1.8087</v>
       </c>
       <c r="N39" t="n">
         <v>172</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.945</v>
+        <v>-2.5115</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.2216</v>
+        <v>-1.0418</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.9675</v>
+        <v>-1.7675</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.945</v>
+        <v>-2.5115</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.945</v>
+        <v>-1.5115</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.945</v>
+        <v>-1.5115</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0113</v>
+        <v>-0.8162</v>
       </c>
       <c r="J40" t="n">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>72</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0113</v>
+        <v>-1.8162</v>
       </c>
       <c r="N40" t="n">
         <v>154</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.1721</v>
+        <v>-3.0356</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.3159</v>
+        <v>-1.2592</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0701</v>
+        <v>-2.0061</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.1721</v>
+        <v>-3.0356</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4641</v>
+        <v>-1.3988</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.708</v>
+        <v>-1.6368</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4641</v>
+        <v>-1.3988</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4641</v>
+        <v>-1.3988</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.708</v>
+        <v>-1.6368</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2323,7 +2323,7 @@
         <v>213</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.1721</v>
+        <v>-3.0356</v>
       </c>
       <c r="N41" t="n">
         <v>318</v>
@@ -2429,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1351</v>
+        <v>1.1254</v>
       </c>
       <c r="J2" t="n">
-        <v>24.9722</v>
+        <v>24.7588</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5755</v>
+        <v>0.5557</v>
       </c>
       <c r="J3" t="n">
-        <v>12.661</v>
+        <v>12.2254</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5755</v>
+        <v>0.5557</v>
       </c>
       <c r="J4" t="n">
-        <v>12.661</v>
+        <v>12.2254</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1978</v>
+        <v>-0.1919</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.3516</v>
+        <v>-4.2218</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6825</v>
+        <v>-0.6353</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.015</v>
+        <v>-13.9766</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8806</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>19.3732</v>
+        <v>18.2622</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.37</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7611</v>
+        <v>0.7235</v>
       </c>
       <c r="J8" t="n">
-        <v>16.7442</v>
+        <v>15.917</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2724</v>
+        <v>-0.2865</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.9928</v>
+        <v>-6.303</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3111</v>
+        <v>-0.3244</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.8442</v>
+        <v>-7.1368</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5591</v>
+        <v>-0.5611</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.3002</v>
+        <v>-12.3442</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.52</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1893</v>
+        <v>1.2034</v>
       </c>
       <c r="J12" t="n">
-        <v>28.5432</v>
+        <v>28.8816</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.45</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0972</v>
+        <v>1.07</v>
       </c>
       <c r="J13" t="n">
-        <v>26.3328</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3734</v>
+        <v>0.3718</v>
       </c>
       <c r="J14" t="n">
-        <v>8.961600000000001</v>
+        <v>8.9232</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.79</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.6342</v>
       </c>
       <c r="J15" t="n">
-        <v>-16.3416</v>
+        <v>-15.2208</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.857</v>
+        <v>-0.789</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.568</v>
+        <v>-18.936</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4276</v>
+        <v>0.4183</v>
       </c>
       <c r="J17" t="n">
-        <v>10.2624</v>
+        <v>10.0392</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1578</v>
+        <v>0.1612</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7872</v>
+        <v>3.8688</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0935</v>
+        <v>-0.1065</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.244</v>
+        <v>-2.556</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0935</v>
+        <v>-0.1065</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.244</v>
+        <v>-2.556</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.54</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.476</v>
+        <v>-0.483</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.424</v>
+        <v>-11.592</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.46</v>
       </c>
       <c r="I22" t="n">
-        <v>0.67</v>
+        <v>0.6512</v>
       </c>
       <c r="J22" t="n">
-        <v>16.08</v>
+        <v>15.6288</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.19</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3156</v>
+        <v>0.3218</v>
       </c>
       <c r="J23" t="n">
-        <v>7.5744</v>
+        <v>7.7232</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0383</v>
+        <v>-0.0445</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9192</v>
+        <v>-1.068</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.1011</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.1792</v>
+        <v>-2.4264</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4681</v>
+        <v>-0.4739</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.2344</v>
+        <v>-11.3736</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5513</v>
       </c>
       <c r="J27" t="n">
-        <v>13.1256</v>
+        <v>13.2312</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5127</v>
+        <v>0.5191</v>
       </c>
       <c r="J28" t="n">
-        <v>12.3048</v>
+        <v>12.4584</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1445</v>
+        <v>0.1608</v>
       </c>
       <c r="J29" t="n">
-        <v>3.468</v>
+        <v>3.8592</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.115</v>
+        <v>-0.1232</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.76</v>
+        <v>-2.9568</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1715</v>
+        <v>-0.1813</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.116</v>
+        <v>-4.3512</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.65</v>
       </c>
       <c r="I32" t="n">
-        <v>1.356</v>
+        <v>1.4412</v>
       </c>
       <c r="J32" t="n">
-        <v>27.12</v>
+        <v>28.824</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.626</v>
+        <v>0.6005</v>
       </c>
       <c r="J33" t="n">
-        <v>12.52</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.18</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5266</v>
+        <v>0.5115</v>
       </c>
       <c r="J34" t="n">
-        <v>10.532</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.412</v>
+        <v>-0.3923</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.24</v>
+        <v>-7.846</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.67</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9791</v>
+        <v>-0.8953</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.582</v>
+        <v>-17.906</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7448</v>
+        <v>0.7087</v>
       </c>
       <c r="J37" t="n">
-        <v>14.896</v>
+        <v>14.174</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.19</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4389</v>
+        <v>0.4303</v>
       </c>
       <c r="J38" t="n">
-        <v>8.778</v>
+        <v>8.606</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.07</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1974</v>
+        <v>0.2016</v>
       </c>
       <c r="J39" t="n">
-        <v>3.948</v>
+        <v>4.032</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.61</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4142</v>
+        <v>-0.4238</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.284000000000001</v>
+        <v>-8.476000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.5</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5142</v>
+        <v>-0.5189</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.284</v>
+        <v>-10.378</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4353</v>
+        <v>0.4841</v>
       </c>
       <c r="J42" t="n">
-        <v>10.0119</v>
+        <v>11.1343</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2742</v>
+        <v>0.282</v>
       </c>
       <c r="J43" t="n">
-        <v>6.3066</v>
+        <v>6.486</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0519</v>
+        <v>-0.0596</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.1937</v>
+        <v>-1.3708</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1138</v>
+        <v>-0.1253</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.6174</v>
+        <v>-2.8819</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3194</v>
+        <v>-0.3309</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.3462</v>
+        <v>-7.6107</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8267</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>19.0141</v>
+        <v>21.7143</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.2944</v>
+        <v>-0.2254</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0339</v>
+        <v>-0.0355</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.8165</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1493</v>
+        <v>-0.1587</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.4339</v>
+        <v>-3.6501</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2441</v>
+        <v>-0.2543</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.6143</v>
+        <v>-5.8489</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.8</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2894</v>
+        <v>1.3956</v>
       </c>
       <c r="J52" t="n">
-        <v>30.9456</v>
+        <v>33.4944</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.05</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1811</v>
+        <v>0.1893</v>
       </c>
       <c r="J53" t="n">
-        <v>4.3464</v>
+        <v>4.5432</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4005</v>
+        <v>-0.3842</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.612</v>
+        <v>-9.220800000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4568</v>
+        <v>-0.4355</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.9632</v>
+        <v>-10.452</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.79</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6702</v>
+        <v>-0.6266</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.0848</v>
+        <v>-15.0384</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4511</v>
+        <v>0.4986</v>
       </c>
       <c r="J57" t="n">
-        <v>10.8264</v>
+        <v>11.9664</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.16</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3534</v>
+        <v>0.3663</v>
       </c>
       <c r="J58" t="n">
-        <v>8.4816</v>
+        <v>8.7912</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3087</v>
+        <v>0.3116</v>
       </c>
       <c r="J59" t="n">
-        <v>7.4088</v>
+        <v>7.4784</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2075</v>
+        <v>-0.2213</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.98</v>
+        <v>-5.3112</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.58</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4464</v>
+        <v>-0.4538</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.7136</v>
+        <v>-10.8912</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.11</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5034</v>
+        <v>1.641</v>
       </c>
       <c r="J62" t="n">
-        <v>22.551</v>
+        <v>24.615</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.75</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1036</v>
+        <v>1.2209</v>
       </c>
       <c r="J63" t="n">
-        <v>16.554</v>
+        <v>18.3135</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7343</v>
+        <v>0.8223</v>
       </c>
       <c r="J64" t="n">
-        <v>11.0145</v>
+        <v>12.3345</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.41</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7095</v>
+        <v>0.7952</v>
       </c>
       <c r="J65" t="n">
-        <v>10.6425</v>
+        <v>11.928</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.95</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3211</v>
+        <v>-0.287</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.8165</v>
+        <v>-4.305</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5746</v>
+        <v>0.6247</v>
       </c>
       <c r="J67" t="n">
-        <v>8.619</v>
+        <v>9.3705</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.91</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0944</v>
+        <v>-0.1134</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.416</v>
+        <v>-1.701</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.63</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3728</v>
+        <v>-0.3881</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.592</v>
+        <v>-5.8215</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.57</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4289</v>
+        <v>-0.4415</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.4335</v>
+        <v>-6.6225</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.46</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5308</v>
+        <v>-0.5374</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.962</v>
+        <v>-8.061</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3712</v>
+        <v>0.4066</v>
       </c>
       <c r="J72" t="n">
-        <v>8.166399999999999</v>
+        <v>8.9452</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.341</v>
+        <v>0.3597</v>
       </c>
       <c r="J73" t="n">
-        <v>7.502</v>
+        <v>7.9134</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.22</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3213</v>
+        <v>0.3355</v>
       </c>
       <c r="J74" t="n">
-        <v>7.0686</v>
+        <v>7.381</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.06</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1073</v>
+        <v>0.1206</v>
       </c>
       <c r="J75" t="n">
-        <v>2.3606</v>
+        <v>2.6532</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4635</v>
+        <v>-0.4688</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.197</v>
+        <v>-10.3136</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.72</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7108</v>
+        <v>0.7994</v>
       </c>
       <c r="J77" t="n">
-        <v>15.6376</v>
+        <v>17.5868</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.33</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4295</v>
+        <v>0.4786</v>
       </c>
       <c r="J78" t="n">
-        <v>9.449</v>
+        <v>10.5292</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2252</v>
+        <v>-0.2373</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.9544</v>
+        <v>-5.2206</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3233</v>
+        <v>-0.334</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.1126</v>
+        <v>-7.348</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3517</v>
+        <v>-0.3616</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.7374</v>
+        <v>-7.9552</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>0.595</v>
+        <v>0.656</v>
       </c>
       <c r="J82" t="n">
-        <v>11.9</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.024</v>
+        <v>-0.0335</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.48</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1233</v>
+        <v>-0.1386</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.466</v>
+        <v>-2.772</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3696</v>
+        <v>-0.3824</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.392</v>
+        <v>-7.648</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.54</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4715</v>
+        <v>-0.4794</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.43</v>
+        <v>-9.587999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8135</v>
+        <v>0.8992</v>
       </c>
       <c r="J87" t="n">
-        <v>16.27</v>
+        <v>17.984</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6431</v>
+        <v>0.7138</v>
       </c>
       <c r="J88" t="n">
-        <v>12.862</v>
+        <v>14.276</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6028</v>
+        <v>0.6694</v>
       </c>
       <c r="J89" t="n">
-        <v>12.056</v>
+        <v>13.388</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0815</v>
+        <v>0.1021</v>
       </c>
       <c r="J90" t="n">
-        <v>1.63</v>
+        <v>2.042</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2857</v>
+        <v>-0.2699</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.714</v>
+        <v>-5.398</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>17.223</v>
+        <v>19.158</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4299</v>
+        <v>0.4741</v>
       </c>
       <c r="J93" t="n">
-        <v>12.897</v>
+        <v>14.223</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.83</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2075</v>
+        <v>-0.2213</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.225</v>
+        <v>-6.639</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.83</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2075</v>
+        <v>-0.2213</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.225</v>
+        <v>-6.639</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3446</v>
+        <v>-0.356</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.338</v>
+        <v>-10.68</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9578</v>
+        <v>1.053</v>
       </c>
       <c r="J97" t="n">
-        <v>28.734</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6727</v>
+        <v>0.7456</v>
       </c>
       <c r="J98" t="n">
-        <v>20.181</v>
+        <v>22.368</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.18</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4395</v>
+        <v>0.4858</v>
       </c>
       <c r="J99" t="n">
-        <v>13.185</v>
+        <v>14.574</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1048</v>
       </c>
       <c r="J100" t="n">
-        <v>2.565</v>
+        <v>3.144</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.85</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5422</v>
+        <v>-0.5065</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.266</v>
+        <v>-15.195</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.71</v>
       </c>
       <c r="I102" t="n">
-        <v>1.115</v>
+        <v>1.2227</v>
       </c>
       <c r="J102" t="n">
-        <v>21.185</v>
+        <v>23.2313</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.46</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8047</v>
+        <v>0.8914</v>
       </c>
       <c r="J103" t="n">
-        <v>15.2893</v>
+        <v>16.9366</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.29</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5837</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="J104" t="n">
-        <v>11.0903</v>
+        <v>12.3443</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2637</v>
+        <v>-0.2466</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.0103</v>
+        <v>-4.6854</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5288</v>
+        <v>-0.4917</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.0472</v>
+        <v>-9.3423</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.26</v>
       </c>
       <c r="I107" t="n">
-        <v>0.475</v>
+        <v>0.523</v>
       </c>
       <c r="J107" t="n">
-        <v>9.025</v>
+        <v>9.936999999999999</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.22</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4317</v>
+        <v>0.4733</v>
       </c>
       <c r="J108" t="n">
-        <v>8.202299999999999</v>
+        <v>8.992699999999999</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.96</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.058</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.102</v>
+        <v>-1.3034</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.68</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3474</v>
+        <v>-0.3599</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.6006</v>
+        <v>-6.8381</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.55</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4678</v>
+        <v>-0.4751</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.888199999999999</v>
+        <v>-9.026899999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2799</v>
+        <v>1.404</v>
       </c>
       <c r="J112" t="n">
-        <v>20.4784</v>
+        <v>22.464</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.5</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8257</v>
+        <v>0.9202</v>
       </c>
       <c r="J113" t="n">
-        <v>13.2112</v>
+        <v>14.7232</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.41</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7188</v>
+        <v>0.8032</v>
       </c>
       <c r="J114" t="n">
-        <v>11.5008</v>
+        <v>12.8512</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.32</v>
       </c>
       <c r="I115" t="n">
-        <v>0.6047</v>
+        <v>0.6775</v>
       </c>
       <c r="J115" t="n">
-        <v>9.6752</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.07</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1606</v>
+        <v>0.1907</v>
       </c>
       <c r="J116" t="n">
-        <v>2.5696</v>
+        <v>3.0512</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1529</v>
+        <v>-0.1768</v>
       </c>
       <c r="J117" t="n">
-        <v>-2.4464</v>
+        <v>-2.8288</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.78</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2174</v>
+        <v>-0.24</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.4784</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.78</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2174</v>
+        <v>-0.24</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.4784</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.54</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4426</v>
+        <v>-0.4568</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.0816</v>
+        <v>-7.3088</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4989</v>
+        <v>-0.5095</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.9824</v>
+        <v>-8.151999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.37</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7209</v>
+        <v>0.7936</v>
       </c>
       <c r="J122" t="n">
-        <v>15.8598</v>
+        <v>17.4592</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4804</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>10.5688</v>
+        <v>11.6314</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3589</v>
+        <v>0.3736</v>
       </c>
       <c r="J124" t="n">
-        <v>7.8958</v>
+        <v>8.219200000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3187</v>
+        <v>-0.3075</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.0114</v>
+        <v>-6.765</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3778</v>
+        <v>-0.3621</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.3116</v>
+        <v>-7.9662</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.11</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2822</v>
+        <v>0.2832</v>
       </c>
       <c r="J127" t="n">
-        <v>6.2084</v>
+        <v>6.2304</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0479</v>
+        <v>0.0506</v>
       </c>
       <c r="J128" t="n">
-        <v>1.0538</v>
+        <v>1.1132</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0948</v>
+        <v>-0.1075</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.0856</v>
+        <v>-2.365</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1284</v>
+        <v>-0.1424</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.8248</v>
+        <v>-3.1328</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.78</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2525</v>
+        <v>-0.267</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.555</v>
+        <v>-5.874</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.89</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3841</v>
+        <v>1.4969</v>
       </c>
       <c r="J132" t="n">
-        <v>40.1389</v>
+        <v>43.4101</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2639</v>
+        <v>0.2698</v>
       </c>
       <c r="J133" t="n">
-        <v>7.6531</v>
+        <v>7.8242</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0276</v>
+        <v>-0.0189</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.8004</v>
+        <v>-0.5481</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1607</v>
+        <v>-0.1566</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.6603</v>
+        <v>-4.5414</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.0261</v>
+        <v>-0.9361</v>
       </c>
       <c r="J136" t="n">
-        <v>-29.7569</v>
+        <v>-27.1469</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.55</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7518</v>
+        <v>0.8365</v>
       </c>
       <c r="J137" t="n">
-        <v>21.8022</v>
+        <v>24.2585</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2298</v>
+        <v>0.2356</v>
       </c>
       <c r="J138" t="n">
-        <v>6.6642</v>
+        <v>6.8324</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0849</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.1576</v>
+        <v>-2.4621</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.89</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1435</v>
+        <v>-0.1568</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.1615</v>
+        <v>-4.5472</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.44</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.5719</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.5619</v>
+        <v>-16.5851</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2424</v>
+        <v>1.21</v>
       </c>
       <c r="J142" t="n">
-        <v>34.7872</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.46</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1003</v>
+        <v>1.0573</v>
       </c>
       <c r="J143" t="n">
-        <v>30.8084</v>
+        <v>29.6044</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.38</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9821</v>
+        <v>0.9218</v>
       </c>
       <c r="J144" t="n">
-        <v>27.4988</v>
+        <v>25.8104</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.86</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5054</v>
+        <v>-0.4752</v>
       </c>
       <c r="J145" t="n">
-        <v>-14.1512</v>
+        <v>-13.3056</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.3371</v>
+        <v>-1.2016</v>
       </c>
       <c r="J146" t="n">
-        <v>-37.4388</v>
+        <v>-33.6448</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.66</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1372</v>
+        <v>1.1056</v>
       </c>
       <c r="J147" t="n">
-        <v>31.8416</v>
+        <v>30.9568</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0439</v>
+        <v>0.0478</v>
       </c>
       <c r="J148" t="n">
-        <v>1.2292</v>
+        <v>1.3384</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.79</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2447</v>
+        <v>-0.259</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.8516</v>
+        <v>-7.252</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.71</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3226</v>
+        <v>-0.3352</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.0328</v>
+        <v>-9.3856</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3791</v>
+        <v>-0.3899</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.6148</v>
+        <v>-10.9172</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.72</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4542</v>
+        <v>1.4302</v>
       </c>
       <c r="J152" t="n">
-        <v>34.9008</v>
+        <v>34.3248</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.8517</v>
+        <v>0.7977</v>
       </c>
       <c r="J153" t="n">
-        <v>20.4408</v>
+        <v>19.1448</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.88</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4338</v>
+        <v>-0.4136</v>
       </c>
       <c r="J154" t="n">
-        <v>-10.4112</v>
+        <v>-9.926399999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6492</v>
+        <v>-0.6071</v>
       </c>
       <c r="J155" t="n">
-        <v>-15.5808</v>
+        <v>-14.5704</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7007</v>
+        <v>-0.6528</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.8168</v>
+        <v>-15.6672</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.28</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5867</v>
+        <v>0.5689</v>
       </c>
       <c r="J157" t="n">
-        <v>14.0808</v>
+        <v>13.6536</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.24</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5155</v>
+        <v>0.5038</v>
       </c>
       <c r="J158" t="n">
-        <v>12.372</v>
+        <v>12.0912</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.15</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3485</v>
+        <v>0.3488</v>
       </c>
       <c r="J159" t="n">
-        <v>8.364000000000001</v>
+        <v>8.3712</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.65</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3818</v>
+        <v>-0.392</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.1632</v>
+        <v>-9.407999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4096</v>
+        <v>-0.4186</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.830399999999999</v>
+        <v>-10.0464</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7788</v>
+        <v>0.7778</v>
       </c>
       <c r="J162" t="n">
-        <v>12.4608</v>
+        <v>12.4448</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.69</v>
       </c>
       <c r="I163" t="n">
-        <v>0.769</v>
+        <v>0.7688</v>
       </c>
       <c r="J163" t="n">
-        <v>12.304</v>
+        <v>12.3008</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.63</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7141</v>
       </c>
       <c r="J164" t="n">
-        <v>11.3632</v>
+        <v>11.4256</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.52</v>
       </c>
       <c r="I165" t="n">
-        <v>0.602</v>
+        <v>0.6125</v>
       </c>
       <c r="J165" t="n">
-        <v>9.632</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0083</v>
+        <v>0.0106</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.1328</v>
+        <v>0.1696</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.85</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1302</v>
+        <v>-0.1567</v>
       </c>
       <c r="J167" t="n">
-        <v>-2.0832</v>
+        <v>-2.5072</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.78</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.208</v>
+        <v>-0.2327</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.328</v>
+        <v>-3.7232</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2186</v>
+        <v>-0.243</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.4976</v>
+        <v>-3.888</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.45</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.331200000000001</v>
+        <v>-8.491199999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.38</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5868</v>
+        <v>-0.592</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.3888</v>
+        <v>-9.472</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.86</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1292</v>
+        <v>-0.1535</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.3256</v>
+        <v>-2.763</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1406</v>
+        <v>-0.1649</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.5308</v>
+        <v>-2.9682</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.71</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2859</v>
+        <v>-0.3068</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.1462</v>
+        <v>-5.5224</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.52</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4607</v>
+        <v>-0.4739</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.2926</v>
+        <v>-8.530200000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.517</v>
+        <v>-0.5265</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.305999999999999</v>
+        <v>-9.477</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.69</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3427</v>
+        <v>1.325</v>
       </c>
       <c r="J177" t="n">
-        <v>24.1686</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0074</v>
+        <v>0.9578</v>
       </c>
       <c r="J178" t="n">
-        <v>18.1332</v>
+        <v>17.2404</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.27</v>
       </c>
       <c r="I179" t="n">
-        <v>0.699</v>
+        <v>0.6747</v>
       </c>
       <c r="J179" t="n">
-        <v>12.582</v>
+        <v>12.1446</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6542</v>
       </c>
       <c r="J180" t="n">
-        <v>12.1662</v>
+        <v>11.7756</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.07</v>
       </c>
       <c r="I181" t="n">
-        <v>0.1814</v>
+        <v>0.2053</v>
       </c>
       <c r="J181" t="n">
-        <v>3.2652</v>
+        <v>3.6954</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7844</v>
+        <v>0.7514</v>
       </c>
       <c r="J182" t="n">
-        <v>18.8256</v>
+        <v>18.0336</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3136</v>
+        <v>0.3192</v>
       </c>
       <c r="J183" t="n">
-        <v>7.5264</v>
+        <v>7.6608</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0857</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>2.0568</v>
+        <v>2.2968</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.83</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2141</v>
+        <v>-0.2265</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.1384</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2141</v>
+        <v>-0.2265</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.1384</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.41</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0606</v>
+        <v>1.0048</v>
       </c>
       <c r="J187" t="n">
-        <v>25.4544</v>
+        <v>24.1152</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.31</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8672</v>
+        <v>0.8085</v>
       </c>
       <c r="J188" t="n">
-        <v>20.8128</v>
+        <v>19.404</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2152</v>
+        <v>0.221</v>
       </c>
       <c r="J189" t="n">
-        <v>5.1648</v>
+        <v>5.304</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.9</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3666</v>
+        <v>-0.3543</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.798400000000001</v>
+        <v>-8.5032</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.0602</v>
+        <v>-0.9676</v>
       </c>
       <c r="J191" t="n">
-        <v>-25.4448</v>
+        <v>-23.2224</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.14</v>
       </c>
       <c r="I192" t="n">
-        <v>1.8338</v>
+        <v>1.9078</v>
       </c>
       <c r="J192" t="n">
-        <v>40.3436</v>
+        <v>41.9716</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.27</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7165</v>
+        <v>0.6866</v>
       </c>
       <c r="J193" t="n">
-        <v>15.763</v>
+        <v>15.1052</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2945</v>
+        <v>0.3047</v>
       </c>
       <c r="J194" t="n">
-        <v>6.479</v>
+        <v>6.7034</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.92</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3528</v>
+        <v>-0.3314</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.7616</v>
+        <v>-7.2908</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.74</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>-18.3524</v>
+        <v>-16.8212</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.24</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5261</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="J197" t="n">
-        <v>11.5742</v>
+        <v>11.2552</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.21</v>
       </c>
       <c r="I198" t="n">
-        <v>0.471</v>
+        <v>0.461</v>
       </c>
       <c r="J198" t="n">
-        <v>10.362</v>
+        <v>10.142</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.85</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1833</v>
+        <v>-0.1979</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.0326</v>
+        <v>-4.3538</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1936</v>
+        <v>-0.2083</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.2592</v>
+        <v>-4.5826</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3693</v>
+        <v>-0.3805</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.124599999999999</v>
+        <v>-8.371</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.93</v>
       </c>
       <c r="I202" t="n">
-        <v>1.6735</v>
+        <v>1.6652</v>
       </c>
       <c r="J202" t="n">
-        <v>36.817</v>
+        <v>36.6344</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.34</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8862</v>
+        <v>0.8339</v>
       </c>
       <c r="J203" t="n">
-        <v>19.4964</v>
+        <v>18.3458</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2749</v>
+        <v>0.2845</v>
       </c>
       <c r="J204" t="n">
-        <v>6.0478</v>
+        <v>6.259</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.98</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1437</v>
+        <v>-0.1342</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.1614</v>
+        <v>-2.9524</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-1.067</v>
+        <v>-0.9688</v>
       </c>
       <c r="J206" t="n">
-        <v>-23.474</v>
+        <v>-21.3136</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.38</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7131</v>
       </c>
       <c r="J207" t="n">
-        <v>16.3548</v>
+        <v>15.6882</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.33</v>
       </c>
       <c r="I208" t="n">
-        <v>0.659</v>
+        <v>0.637</v>
       </c>
       <c r="J208" t="n">
-        <v>14.498</v>
+        <v>14.014</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0658</v>
+        <v>-0.0745</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.4476</v>
+        <v>-1.639</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2218</v>
+        <v>-0.2347</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.8796</v>
+        <v>-5.1634</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.64</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3952</v>
+        <v>-0.4041</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.6944</v>
+        <v>-8.8902</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.88</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2929</v>
+        <v>1.2822</v>
       </c>
       <c r="J212" t="n">
-        <v>31.0296</v>
+        <v>30.7728</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.12</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2677</v>
+        <v>0.2773</v>
       </c>
       <c r="J213" t="n">
-        <v>6.4248</v>
+        <v>6.6552</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1211</v>
+        <v>-0.131</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.9064</v>
+        <v>-3.144</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2686</v>
+        <v>-0.2797</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.4464</v>
+        <v>-6.7128</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.74</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3075</v>
+        <v>-0.3179</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.38</v>
+        <v>-7.6296</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.69</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3886</v>
+        <v>1.3657</v>
       </c>
       <c r="J217" t="n">
-        <v>33.3264</v>
+        <v>32.7768</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.37</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9577</v>
+        <v>0.8983</v>
       </c>
       <c r="J218" t="n">
-        <v>22.9848</v>
+        <v>21.5592</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.27</v>
       </c>
       <c r="I219" t="n">
-        <v>0.731</v>
+        <v>0.6965</v>
       </c>
       <c r="J219" t="n">
-        <v>17.544</v>
+        <v>16.716</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.04</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1257</v>
+        <v>0.1423</v>
       </c>
       <c r="J220" t="n">
-        <v>3.0168</v>
+        <v>3.4152</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.5</v>
       </c>
       <c r="I221" t="n">
-        <v>-1.3853</v>
+        <v>-1.2422</v>
       </c>
       <c r="J221" t="n">
-        <v>-33.2472</v>
+        <v>-29.8128</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.56</v>
       </c>
       <c r="I222" t="n">
-        <v>0.709</v>
+        <v>0.7012</v>
       </c>
       <c r="J222" t="n">
-        <v>29.778</v>
+        <v>29.4504</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2396</v>
+        <v>0.2557</v>
       </c>
       <c r="J223" t="n">
-        <v>10.0632</v>
+        <v>10.7394</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.14</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2138</v>
+        <v>0.2301</v>
       </c>
       <c r="J224" t="n">
-        <v>8.9796</v>
+        <v>9.664199999999999</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0134</v>
+        <v>0.0222</v>
       </c>
       <c r="J225" t="n">
-        <v>0.5628</v>
+        <v>0.9324</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.73</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3203</v>
+        <v>-0.3298</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.4526</v>
+        <v>-13.8516</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.34</v>
       </c>
       <c r="I227" t="n">
-        <v>0.519</v>
+        <v>0.5123</v>
       </c>
       <c r="J227" t="n">
-        <v>21.798</v>
+        <v>21.5166</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.13</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2303</v>
+        <v>0.2395</v>
       </c>
       <c r="J228" t="n">
-        <v>9.672599999999999</v>
+        <v>10.059</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.95</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0779</v>
+        <v>-0.0876</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.2718</v>
+        <v>-3.6792</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1902</v>
+        <v>-0.2033</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.9884</v>
+        <v>-8.538600000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2109</v>
+        <v>-0.224</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.857799999999999</v>
+        <v>-9.407999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.14</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3629</v>
+        <v>0.3552</v>
       </c>
       <c r="J232" t="n">
-        <v>6.8951</v>
+        <v>6.7488</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.13</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3426</v>
+        <v>0.3362</v>
       </c>
       <c r="J233" t="n">
-        <v>6.5094</v>
+        <v>6.3878</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.85</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1754</v>
+        <v>-0.1918</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.3326</v>
+        <v>-3.6442</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.72</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.304</v>
+        <v>-0.3188</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.776</v>
+        <v>-6.0572</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3985</v>
+        <v>-0.4099</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.5715</v>
+        <v>-7.7881</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.76</v>
       </c>
       <c r="I237" t="n">
-        <v>1.416</v>
+        <v>1.4043</v>
       </c>
       <c r="J237" t="n">
-        <v>26.904</v>
+        <v>26.6817</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.6</v>
       </c>
       <c r="I238" t="n">
-        <v>1.2269</v>
+        <v>1.2032</v>
       </c>
       <c r="J238" t="n">
-        <v>23.3111</v>
+        <v>22.8608</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.43</v>
       </c>
       <c r="I239" t="n">
-        <v>1.0165</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="J239" t="n">
-        <v>19.3135</v>
+        <v>18.4167</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.38</v>
       </c>
       <c r="I240" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.8819</v>
       </c>
       <c r="J240" t="n">
-        <v>17.6871</v>
+        <v>16.7561</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8393</v>
+        <v>-0.7639</v>
       </c>
       <c r="J241" t="n">
-        <v>-15.9467</v>
+        <v>-14.5141</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.3</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2031</v>
+        <v>1.2176</v>
       </c>
       <c r="J242" t="n">
-        <v>19.2496</v>
+        <v>19.4816</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.7</v>
       </c>
       <c r="I243" t="n">
-        <v>0.778</v>
+        <v>0.7772</v>
       </c>
       <c r="J243" t="n">
-        <v>12.448</v>
+        <v>12.4352</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.65</v>
       </c>
       <c r="I244" t="n">
-        <v>0.7291</v>
+        <v>0.7319</v>
       </c>
       <c r="J244" t="n">
-        <v>11.6656</v>
+        <v>11.7104</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0878</v>
+        <v>0.1138</v>
       </c>
       <c r="J245" t="n">
-        <v>1.4048</v>
+        <v>1.8208</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.86</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2237</v>
+        <v>-0.2272</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.5792</v>
+        <v>-3.6352</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.08</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2283</v>
+        <v>0.2201</v>
       </c>
       <c r="J247" t="n">
-        <v>3.6528</v>
+        <v>3.5216</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.9</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1036</v>
+        <v>-0.1233</v>
       </c>
       <c r="J248" t="n">
-        <v>-1.6576</v>
+        <v>-1.9728</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.86</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1488</v>
+        <v>-0.1689</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.3808</v>
+        <v>-2.7024</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.54</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4551</v>
+        <v>-0.4665</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.2816</v>
+        <v>-7.464</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.43</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5568</v>
+        <v>-0.5619</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.908799999999999</v>
+        <v>-8.990399999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3546</v>
+        <v>0.345</v>
       </c>
       <c r="J252" t="n">
-        <v>8.510400000000001</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.032</v>
+        <v>0.0231</v>
       </c>
       <c r="J253" t="n">
-        <v>0.768</v>
+        <v>0.5544</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.121</v>
+        <v>-0.1368</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.904</v>
+        <v>-3.2832</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.68</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3384</v>
+        <v>-0.3529</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.121600000000001</v>
+        <v>-8.4696</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.61</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4042</v>
+        <v>-0.4159</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.700799999999999</v>
+        <v>-9.9816</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.56</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2111</v>
+        <v>1.18</v>
       </c>
       <c r="J257" t="n">
-        <v>29.0664</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.52</v>
       </c>
       <c r="I258" t="n">
-        <v>1.1607</v>
+        <v>1.126</v>
       </c>
       <c r="J258" t="n">
-        <v>27.8568</v>
+        <v>27.024</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.16</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4573</v>
+        <v>0.4531</v>
       </c>
       <c r="J259" t="n">
-        <v>10.9752</v>
+        <v>10.8744</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.06</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1778</v>
+        <v>0.1953</v>
       </c>
       <c r="J260" t="n">
-        <v>4.2672</v>
+        <v>4.6872</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.83</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6029</v>
+        <v>-0.5597</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.4696</v>
+        <v>-13.4328</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.62</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0733</v>
+        <v>1.0379</v>
       </c>
       <c r="J262" t="n">
-        <v>24.6859</v>
+        <v>23.8717</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.36</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7037</v>
+        <v>0.6784</v>
       </c>
       <c r="J263" t="n">
-        <v>16.1851</v>
+        <v>15.6032</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1716</v>
+        <v>-0.1839</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.9468</v>
+        <v>-4.2297</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.71</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3314</v>
+        <v>-0.3421</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.6222</v>
+        <v>-7.8683</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.65</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3876</v>
+        <v>-0.3965</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.9148</v>
+        <v>-9.1195</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.44</v>
       </c>
       <c r="I267" t="n">
-        <v>1.072</v>
+        <v>1.025</v>
       </c>
       <c r="J267" t="n">
-        <v>24.656</v>
+        <v>23.575</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I268" t="n">
-        <v>0.9977</v>
+        <v>0.9387</v>
       </c>
       <c r="J268" t="n">
-        <v>22.9471</v>
+        <v>21.5901</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.11</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3381</v>
+        <v>0.3413</v>
       </c>
       <c r="J269" t="n">
-        <v>7.7763</v>
+        <v>7.8499</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0559</v>
+        <v>0.0736</v>
       </c>
       <c r="J270" t="n">
-        <v>1.2857</v>
+        <v>1.6928</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.87</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4799</v>
+        <v>-0.4517</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.0377</v>
+        <v>-10.3891</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.75</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J272" t="n">
-        <v>23.8394</v>
+        <v>25.1836</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>2.27</v>
       </c>
       <c r="I273" t="n">
-        <v>1.8338</v>
+        <v>1.9173</v>
       </c>
       <c r="J273" t="n">
-        <v>23.8394</v>
+        <v>24.9249</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.65</v>
       </c>
       <c r="I274" t="n">
-        <v>1.2404</v>
+        <v>1.2269</v>
       </c>
       <c r="J274" t="n">
-        <v>16.1252</v>
+        <v>15.9497</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.25</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5659</v>
+        <v>0.5729</v>
       </c>
       <c r="J275" t="n">
-        <v>7.3567</v>
+        <v>7.4477</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.07</v>
       </c>
       <c r="I276" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1459</v>
       </c>
       <c r="J276" t="n">
-        <v>1.2623</v>
+        <v>1.8967</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.59</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.3477</v>
+        <v>-0.3753</v>
       </c>
       <c r="J277" t="n">
-        <v>-4.5201</v>
+        <v>-4.8789</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.54</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.4</v>
+        <v>-0.4239</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.2</v>
+        <v>-5.5107</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.44</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4931</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.4103</v>
+        <v>-6.6378</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.39</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5545</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.0304</v>
+        <v>-7.2085</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.37</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5604</v>
+        <v>-0.5725</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.2852</v>
+        <v>-7.4425</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.93</v>
       </c>
       <c r="I282" t="n">
-        <v>1.5971</v>
+        <v>1.5972</v>
       </c>
       <c r="J282" t="n">
-        <v>27.1507</v>
+        <v>27.1524</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.57</v>
       </c>
       <c r="I283" t="n">
-        <v>1.1815</v>
+        <v>1.1564</v>
       </c>
       <c r="J283" t="n">
-        <v>20.0855</v>
+        <v>19.6588</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.29</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7241</v>
+        <v>0.7009</v>
       </c>
       <c r="J284" t="n">
-        <v>12.3097</v>
+        <v>11.9153</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.28</v>
       </c>
       <c r="I285" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.6806</v>
       </c>
       <c r="J285" t="n">
-        <v>11.9187</v>
+        <v>11.5702</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.16</v>
       </c>
       <c r="I286" t="n">
-        <v>0.4091</v>
+        <v>0.4196</v>
       </c>
       <c r="J286" t="n">
-        <v>6.9547</v>
+        <v>7.1332</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.74</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.2497</v>
+        <v>-0.2731</v>
       </c>
       <c r="J287" t="n">
-        <v>-4.2449</v>
+        <v>-4.6427</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.7</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2895</v>
+        <v>-0.3114</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.9215</v>
+        <v>-5.2938</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.68</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3086</v>
+        <v>-0.3299</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.2462</v>
+        <v>-5.6083</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.62</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3621</v>
+        <v>-0.3815</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.1557</v>
+        <v>-6.4855</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.49</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4829</v>
+        <v>-0.4956</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.209300000000001</v>
+        <v>-8.4252</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>2.18</v>
       </c>
       <c r="I292" t="n">
-        <v>1.8338</v>
+        <v>1.9123</v>
       </c>
       <c r="J292" t="n">
-        <v>36.676</v>
+        <v>38.246</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.61</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2436</v>
+        <v>1.2202</v>
       </c>
       <c r="J293" t="n">
-        <v>24.872</v>
+        <v>24.404</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5779</v>
+        <v>0.5676</v>
       </c>
       <c r="J294" t="n">
-        <v>11.558</v>
+        <v>11.352</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.402</v>
+        <v>0.4093</v>
       </c>
       <c r="J295" t="n">
-        <v>8.039999999999999</v>
+        <v>8.186</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.63</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.1203</v>
+        <v>-1.0102</v>
       </c>
       <c r="J296" t="n">
-        <v>-22.406</v>
+        <v>-20.204</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.37</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7832</v>
+        <v>0.7399</v>
       </c>
       <c r="J297" t="n">
-        <v>15.664</v>
+        <v>14.798</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.91</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1141</v>
+        <v>-0.1286</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.282</v>
+        <v>-2.572</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.86</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1667</v>
+        <v>-0.1826</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.334</v>
+        <v>-3.652</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.8</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2276</v>
+        <v>-0.2435</v>
       </c>
       <c r="J300" t="n">
-        <v>-4.552</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.59</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.428</v>
+        <v>-0.4377</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.56</v>
+        <v>-8.754</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.09</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2072</v>
+        <v>0.208</v>
       </c>
       <c r="J302" t="n">
-        <v>3.9368</v>
+        <v>3.952</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.1133</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.8639</v>
+        <v>-2.1527</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1207</v>
+        <v>-0.1366</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.2933</v>
+        <v>-2.5954</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.74</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2808</v>
+        <v>-0.297</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.3352</v>
+        <v>-5.643</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.66</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3571</v>
+        <v>-0.3709</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.7849</v>
+        <v>-7.0471</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.61</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7245</v>
+        <v>0.7216</v>
       </c>
       <c r="J307" t="n">
-        <v>13.7655</v>
+        <v>13.7104</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.38</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4783</v>
+        <v>0.4909</v>
       </c>
       <c r="J308" t="n">
-        <v>9.0877</v>
+        <v>9.3271</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.22</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2986</v>
+        <v>0.3174</v>
       </c>
       <c r="J309" t="n">
-        <v>5.6734</v>
+        <v>6.0306</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.11</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1566</v>
+        <v>0.1771</v>
       </c>
       <c r="J310" t="n">
-        <v>2.9754</v>
+        <v>3.3649</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.09</v>
       </c>
       <c r="I311" t="n">
-        <v>0.128</v>
+        <v>0.1483</v>
       </c>
       <c r="J311" t="n">
-        <v>2.432</v>
+        <v>2.8177</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.42</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0454</v>
+        <v>0.9928</v>
       </c>
       <c r="J312" t="n">
-        <v>22.9988</v>
+        <v>21.8416</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.21</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5905</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="J313" t="n">
-        <v>12.991</v>
+        <v>12.5642</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.19</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5274</v>
       </c>
       <c r="J314" t="n">
-        <v>11.9196</v>
+        <v>11.6028</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.14</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4184</v>
+        <v>0.4149</v>
       </c>
       <c r="J315" t="n">
-        <v>9.204800000000001</v>
+        <v>9.127800000000001</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.86</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5069</v>
+        <v>-0.4763</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.1518</v>
+        <v>-10.4786</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.11</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2923</v>
+        <v>0.2906</v>
       </c>
       <c r="J317" t="n">
-        <v>6.4306</v>
+        <v>6.3932</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.01</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0555</v>
+        <v>0.0561</v>
       </c>
       <c r="J318" t="n">
-        <v>1.221</v>
+        <v>1.2342</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.9</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1255</v>
+        <v>-0.1402</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.761</v>
+        <v>-3.0844</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.82</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2088</v>
+        <v>-0.2246</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.5936</v>
+        <v>-4.9412</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.74</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2878</v>
+        <v>-0.3025</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.3316</v>
+        <v>-6.655</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.91</v>
       </c>
       <c r="I322" t="n">
-        <v>1.5792</v>
+        <v>1.5777</v>
       </c>
       <c r="J322" t="n">
-        <v>28.4256</v>
+        <v>28.3986</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.69</v>
       </c>
       <c r="I323" t="n">
-        <v>1.3258</v>
+        <v>1.3101</v>
       </c>
       <c r="J323" t="n">
-        <v>23.8644</v>
+        <v>23.5818</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.52</v>
       </c>
       <c r="I324" t="n">
-        <v>1.1248</v>
+        <v>1.0946</v>
       </c>
       <c r="J324" t="n">
-        <v>20.2464</v>
+        <v>19.7028</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.1</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2511</v>
+        <v>0.2744</v>
       </c>
       <c r="J325" t="n">
-        <v>4.5198</v>
+        <v>4.9392</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.91</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4244</v>
+        <v>-0.3885</v>
       </c>
       <c r="J326" t="n">
-        <v>-7.6392</v>
+        <v>-6.993</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.08</v>
       </c>
       <c r="I327" t="n">
-        <v>0.3057</v>
+        <v>0.2864</v>
       </c>
       <c r="J327" t="n">
-        <v>5.5026</v>
+        <v>5.1552</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.04</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2078</v>
+        <v>0.1917</v>
       </c>
       <c r="J328" t="n">
-        <v>3.7404</v>
+        <v>3.4506</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.66</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.341</v>
+        <v>-0.3583</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.138</v>
+        <v>-6.4494</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.54</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4533</v>
+        <v>-0.4651</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.1594</v>
+        <v>-8.3718</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.43</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5552</v>
+        <v>-0.5606</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.993600000000001</v>
+        <v>-10.0908</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.36</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9202</v>
+        <v>0.8661</v>
       </c>
       <c r="J332" t="n">
-        <v>21.1646</v>
+        <v>19.9203</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.32</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.7875</v>
       </c>
       <c r="J333" t="n">
-        <v>19.1153</v>
+        <v>18.1125</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.32</v>
       </c>
       <c r="I334" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.7875</v>
       </c>
       <c r="J334" t="n">
-        <v>19.1153</v>
+        <v>18.1125</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.11</v>
       </c>
       <c r="I335" t="n">
-        <v>0.3235</v>
+        <v>0.3312</v>
       </c>
       <c r="J335" t="n">
-        <v>7.4405</v>
+        <v>7.6176</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>1.04</v>
       </c>
       <c r="I336" t="n">
-        <v>0.1118</v>
+        <v>0.1327</v>
       </c>
       <c r="J336" t="n">
-        <v>2.5714</v>
+        <v>3.0521</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.92</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1011</v>
+        <v>-0.1156</v>
       </c>
       <c r="J337" t="n">
-        <v>-2.3253</v>
+        <v>-2.6588</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.9</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1233</v>
+        <v>-0.1386</v>
       </c>
       <c r="J338" t="n">
-        <v>-2.8359</v>
+        <v>-3.1878</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.9</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1233</v>
+        <v>-0.1386</v>
       </c>
       <c r="J339" t="n">
-        <v>-2.8359</v>
+        <v>-3.1878</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.88</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.144</v>
+        <v>-0.16</v>
       </c>
       <c r="J340" t="n">
-        <v>-3.312</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.1951</v>
+        <v>-0.2117</v>
       </c>
       <c r="J341" t="n">
-        <v>-4.4873</v>
+        <v>-4.8691</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7556/event_7556_evp_summary.xlsx
+++ b/database/event/7556/event_7556_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.9345</v>
+        <v>9.1663</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7062</v>
+        <v>3.8024</v>
       </c>
       <c r="D2" t="n">
-        <v>3.443</v>
+        <v>3.4806</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9345</v>
+        <v>9.1663</v>
       </c>
       <c r="F2" t="n">
         <v>2.9912</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6161</v>
+        <v>6.7626</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7445</v>
+        <v>2.8053</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3876</v>
+        <v>2.4069</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6161</v>
+        <v>6.7626</v>
       </c>
       <c r="F3" t="n">
         <v>1.9924</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6768</v>
+        <v>5.8982</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3549</v>
+        <v>2.4467</v>
       </c>
       <c r="D4" t="n">
-        <v>1.96</v>
+        <v>2.0208</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6768</v>
+        <v>5.8982</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6351</v>
+        <v>4.5807</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0417</v>
+        <v>0.8355</v>
       </c>
       <c r="H4" t="n">
-        <v>7.0994</v>
+        <v>10.5815</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8336</v>
+        <v>5.7139</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0417</v>
+        <v>0.8355</v>
       </c>
       <c r="K4" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L4" t="n">
-        <v>152</v>
+        <v>72</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8753</v>
+        <v>6.549399999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5112</v>
+        <v>5.8618</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2862</v>
+        <v>2.4316</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8846</v>
+        <v>2.0045</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5112</v>
+        <v>5.8618</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7725</v>
+        <v>3.6351</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7387</v>
+        <v>2.0417</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3432</v>
+        <v>7.0994</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4294</v>
+        <v>3.8336</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7387</v>
+        <v>2.0417</v>
       </c>
       <c r="K5" t="n">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="L5" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="M5" t="n">
-        <v>6.1681</v>
+        <v>5.8753</v>
       </c>
       <c r="N5" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4162</v>
+        <v>5.8366</v>
       </c>
       <c r="C6" t="n">
-        <v>2.2468</v>
+        <v>2.4211</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8414</v>
+        <v>1.9933</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4162</v>
+        <v>5.8366</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5807</v>
+        <v>2.7725</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8355</v>
+        <v>2.7387</v>
       </c>
       <c r="H6" t="n">
-        <v>10.5815</v>
+        <v>3.3432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7139</v>
+        <v>3.4294</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8355</v>
+        <v>2.7387</v>
       </c>
       <c r="K6" t="n">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="L6" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="M6" t="n">
-        <v>6.549399999999999</v>
+        <v>6.1681</v>
       </c>
       <c r="N6" t="n">
-        <v>154</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7">
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.412</v>
+        <v>5.4731</v>
       </c>
       <c r="C7" t="n">
-        <v>2.245</v>
+        <v>2.2704</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8395</v>
+        <v>1.8309</v>
       </c>
       <c r="E7" t="n">
-        <v>5.412</v>
+        <v>5.4731</v>
       </c>
       <c r="F7" t="n">
         <v>0.8084</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7122</v>
+        <v>4.9513</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9547</v>
+        <v>2.0539</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5209</v>
+        <v>1.5978</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7122</v>
+        <v>4.9513</v>
       </c>
       <c r="F8" t="n">
         <v>3.9178</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6743</v>
+        <v>4.806</v>
       </c>
       <c r="C9" t="n">
-        <v>1.939</v>
+        <v>1.9936</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5036</v>
+        <v>1.5329</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6743</v>
+        <v>4.806</v>
       </c>
       <c r="F9" t="n">
         <v>1.821</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0641</v>
+        <v>4.1742</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6859</v>
+        <v>1.7315</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2259</v>
+        <v>1.2507</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0641</v>
+        <v>4.1742</v>
       </c>
       <c r="F10" t="n">
         <v>1.5801</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6968</v>
+        <v>3.8421</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5335</v>
+        <v>1.5938</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0587</v>
+        <v>1.1024</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6968</v>
+        <v>3.8421</v>
       </c>
       <c r="F11" t="n">
         <v>3.2955</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6593</v>
+        <v>3.727</v>
       </c>
       <c r="C12" t="n">
-        <v>1.518</v>
+        <v>1.546</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0416</v>
+        <v>1.0509</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6593</v>
+        <v>3.727</v>
       </c>
       <c r="F12" t="n">
         <v>2.813</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1649</v>
+        <v>3.2366</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3129</v>
+        <v>1.3426</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8165</v>
+        <v>0.8319</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1649</v>
+        <v>3.2366</v>
       </c>
       <c r="F13" t="n">
         <v>3.7085</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1134</v>
+        <v>3.1555</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2915</v>
+        <v>1.309</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7931</v>
+        <v>0.7957</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1134</v>
+        <v>3.1555</v>
       </c>
       <c r="F14" t="n">
         <v>2.429</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6269</v>
+        <v>2.8699</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0897</v>
+        <v>1.1905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5716</v>
+        <v>0.6681</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6269</v>
+        <v>2.8699</v>
       </c>
       <c r="F15" t="n">
         <v>2.4286</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4671</v>
+        <v>2.6882</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0234</v>
+        <v>1.1151</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4989</v>
+        <v>0.5869</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4671</v>
+        <v>2.6882</v>
       </c>
       <c r="F16" t="n">
         <v>2.7757</v>
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.207</v>
+        <v>2.3196</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9155</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3805</v>
+        <v>0.4223</v>
       </c>
       <c r="E17" t="n">
-        <v>2.207</v>
+        <v>2.3196</v>
       </c>
       <c r="F17" t="n">
         <v>1.6375</v>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7654</v>
+        <v>1.8255</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7323</v>
+        <v>0.7573</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1794</v>
+        <v>0.2016</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7654</v>
+        <v>1.8255</v>
       </c>
       <c r="F18" t="n">
         <v>1.6373</v>
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1555</v>
+        <v>1.2042</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4793</v>
+        <v>0.4995</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0982</v>
+        <v>-0.0759</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1555</v>
+        <v>1.2042</v>
       </c>
       <c r="F19" t="n">
         <v>1.1555</v>
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.629</v>
+        <v>0.699</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2609</v>
+        <v>0.29</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3379</v>
+        <v>-0.3016</v>
       </c>
       <c r="E20" t="n">
-        <v>0.629</v>
+        <v>0.699</v>
       </c>
       <c r="F20" t="n">
         <v>0.6155</v>
@@ -1366,216 +1366,216 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5984</v>
+        <v>0.5743</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3518</v>
+        <v>-0.3573</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5984</v>
+        <v>0.5743</v>
       </c>
       <c r="F21" t="n">
-        <v>0.185</v>
+        <v>0.7037</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4134</v>
+        <v>-0.1062</v>
       </c>
       <c r="H21" t="n">
-        <v>0.185</v>
+        <v>0.7037</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1898</v>
+        <v>0.7218</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4134</v>
+        <v>-0.1062</v>
       </c>
       <c r="K21" t="n">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="L21" t="n">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6032</v>
+        <v>0.6156</v>
       </c>
       <c r="N21" t="n">
-        <v>243</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5975</v>
+        <v>0.5447</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2479</v>
+        <v>0.226</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3522</v>
+        <v>-0.3705</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5975</v>
+        <v>0.5447</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7037</v>
+        <v>0.2684</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1062</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7037</v>
+        <v>0.2684</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7218</v>
+        <v>0.2684</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1062</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6156</v>
+        <v>0.2684</v>
       </c>
       <c r="N22" t="n">
-        <v>172</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.505</v>
+        <v>0.4161</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2095</v>
+        <v>0.1726</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3943</v>
+        <v>-0.428</v>
       </c>
       <c r="E23" t="n">
-        <v>0.505</v>
+        <v>0.4161</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2085</v>
+        <v>0.185</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2965</v>
+        <v>0.4134</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2085</v>
+        <v>0.185</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2085</v>
+        <v>0.1898</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2965</v>
+        <v>0.4134</v>
       </c>
       <c r="K23" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L23" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="M23" t="n">
-        <v>0.505</v>
+        <v>0.6032</v>
       </c>
       <c r="N23" t="n">
-        <v>150</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2684</v>
+        <v>0.3923</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1113</v>
+        <v>0.1627</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.502</v>
+        <v>-0.4386</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2684</v>
+        <v>0.3923</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2684</v>
+        <v>0.2085</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.2965</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2684</v>
+        <v>0.2085</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2684</v>
+        <v>0.2085</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.2965</v>
       </c>
       <c r="K24" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2684</v>
+        <v>0.505</v>
       </c>
       <c r="N24" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0721</v>
+        <v>0.1014</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0299</v>
+        <v>0.0421</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5914</v>
+        <v>-0.5685</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0721</v>
+        <v>0.1014</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0721</v>
+        <v>0.0334</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0721</v>
+        <v>0.0334</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0721</v>
+        <v>0.0334</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0721</v>
+        <v>0.0334</v>
       </c>
       <c r="N25" t="n">
         <v>88</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0334</v>
+        <v>-0.0509</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0139</v>
+        <v>-0.0211</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.609</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0334</v>
+        <v>-0.0509</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0334</v>
+        <v>0.0721</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0334</v>
+        <v>0.0721</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0334</v>
+        <v>0.0721</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0334</v>
+        <v>0.0721</v>
       </c>
       <c r="N26" t="n">
         <v>88</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.212</v>
+        <v>-0.2844</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.118</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7207</v>
+        <v>-0.7409</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.212</v>
+        <v>-0.2844</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.07779999999999999</v>
+        <v>0.6708</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1342</v>
+        <v>-0.9319</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.07779999999999999</v>
+        <v>0.6708</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.042</v>
+        <v>0.6708</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1342</v>
+        <v>-0.9319</v>
       </c>
       <c r="K27" t="n">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="L27" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1762</v>
+        <v>-0.2611</v>
       </c>
       <c r="N27" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2611</v>
+        <v>-0.3409</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1083</v>
+        <v>-0.1414</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7431</v>
+        <v>-0.7661</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2611</v>
+        <v>-0.3409</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6708</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.9319</v>
+        <v>-0.1342</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6708</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6708</v>
+        <v>-0.042</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9319</v>
+        <v>-0.1342</v>
       </c>
       <c r="K28" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2611</v>
+        <v>-0.1762</v>
       </c>
       <c r="N28" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29">
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2685</v>
+        <v>-0.3835</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1114</v>
+        <v>-0.1591</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7464</v>
+        <v>-0.7851</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2685</v>
+        <v>-0.3835</v>
       </c>
       <c r="F29" t="n">
         <v>-0.2685</v>
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3411</v>
+        <v>-0.58</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1415</v>
+        <v>-0.2406</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7795</v>
+        <v>-0.8729</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3411</v>
+        <v>-0.58</v>
       </c>
       <c r="F30" t="n">
         <v>-0.3411</v>
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4667</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1936</v>
+        <v>-0.2419</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8367</v>
+        <v>-0.8743</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4667</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>-0.4667</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6869</v>
+        <v>-0.9225</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2849</v>
+        <v>-0.3827</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9369</v>
+        <v>-1.0259</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6869</v>
+        <v>-0.9225</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.6539</v>
+        <v>-0.8062</v>
       </c>
       <c r="G32" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.6539</v>
+        <v>-0.8062</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8931</v>
+        <v>-0.8062</v>
       </c>
       <c r="J32" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L32" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.07389999999999997</v>
+        <v>-0.8062</v>
       </c>
       <c r="N32" t="n">
-        <v>237</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8062</v>
+        <v>-1.0087</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3344</v>
+        <v>-0.4184</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9912</v>
+        <v>-1.0644</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8062</v>
+        <v>-1.0087</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8062</v>
+        <v>-1.6539</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8062</v>
+        <v>-1.6539</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8062</v>
+        <v>-0.8931</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="K33" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8062</v>
+        <v>0.07389999999999997</v>
       </c>
       <c r="N33" t="n">
-        <v>88</v>
+        <v>237</v>
       </c>
     </row>
     <row r="34">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8779</v>
+        <v>-1.0701</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3642</v>
+        <v>-0.4439</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0238</v>
+        <v>-1.0918</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8779</v>
+        <v>-1.0701</v>
       </c>
       <c r="F34" t="n">
         <v>-0.8779</v>
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.948</v>
+        <v>-1.0942</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3933</v>
+        <v>-0.4539</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0558</v>
+        <v>-1.1026</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.948</v>
+        <v>-1.0942</v>
       </c>
       <c r="F35" t="n">
         <v>-0.803</v>
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.215</v>
+        <v>-1.3112</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.504</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1773</v>
+        <v>-1.1995</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.215</v>
+        <v>-1.3112</v>
       </c>
       <c r="F36" t="n">
         <v>-1.215</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4436</v>
+        <v>-1.7125</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5988</v>
+        <v>-0.7104</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2814</v>
+        <v>-1.3788</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4436</v>
+        <v>-1.7125</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8437</v>
+        <v>0.0182</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5999</v>
+        <v>-1.6698</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8437</v>
+        <v>0.0182</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8437</v>
+        <v>0.0182</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5999</v>
+        <v>-1.6698</v>
       </c>
       <c r="K37" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="L37" t="n">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4436</v>
+        <v>-1.6516</v>
       </c>
       <c r="N37" t="n">
-        <v>150</v>
+        <v>318</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6516</v>
+        <v>-1.7161</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6851</v>
+        <v>-0.7119</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.376</v>
+        <v>-1.3804</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6516</v>
+        <v>-1.7161</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0182</v>
+        <v>-0.8437</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.6698</v>
+        <v>-0.5999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0182</v>
+        <v>-0.8437</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0182</v>
+        <v>-0.8437</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.6698</v>
+        <v>-0.5999</v>
       </c>
       <c r="K38" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L38" t="n">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6516</v>
+        <v>-1.4436</v>
       </c>
       <c r="N38" t="n">
-        <v>318</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39">
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7812</v>
+        <v>-2.1385</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7389</v>
+        <v>-0.8871</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.435</v>
+        <v>-1.569</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7812</v>
+        <v>-2.1385</v>
       </c>
       <c r="F39" t="n">
         <v>-1.0669</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.5115</v>
+        <v>-2.8201</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.0418</v>
+        <v>-1.1698</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7675</v>
+        <v>-1.8735</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.5115</v>
+        <v>-2.8201</v>
       </c>
       <c r="F40" t="n">
         <v>-1.5115</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0356</v>
+        <v>-3.439</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.2592</v>
+        <v>-1.4266</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0061</v>
+        <v>-2.1499</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0356</v>
+        <v>-3.439</v>
       </c>
       <c r="F41" t="n">
         <v>-1.3988</v>

--- a/database/event/7556/event_7556_evp_summary.xlsx
+++ b/database/event/7556/event_7556_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.1663</v>
+        <v>9.084300000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8024</v>
+        <v>3.7684</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4806</v>
+        <v>3.5325</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1663</v>
+        <v>9.084300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9912</v>
+        <v>2.9097</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9433</v>
+        <v>5.9428</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8218</v>
+        <v>3.7181</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8218</v>
+        <v>3.7181</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9433</v>
+        <v>5.9428</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -529,7 +529,7 @@
         <v>213</v>
       </c>
       <c r="M2" t="n">
-        <v>9.7651</v>
+        <v>9.6609</v>
       </c>
       <c r="N2" t="n">
         <v>318</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7626</v>
+        <v>6.5631</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8053</v>
+        <v>2.7225</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4069</v>
+        <v>2.384</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7626</v>
+        <v>6.5631</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9924</v>
+        <v>1.8172</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6237</v>
+        <v>4.5995</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9924</v>
+        <v>1.8172</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9924</v>
+        <v>1.8172</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6237</v>
+        <v>4.5995</v>
       </c>
       <c r="K3" t="n">
         <v>105</v>
@@ -575,7 +575,7 @@
         <v>213</v>
       </c>
       <c r="M3" t="n">
-        <v>6.6161</v>
+        <v>6.4167</v>
       </c>
       <c r="N3" t="n">
         <v>318</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8982</v>
+        <v>5.7887</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4467</v>
+        <v>2.4013</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0208</v>
+        <v>2.0312</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8982</v>
+        <v>5.7887</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5807</v>
+        <v>3.5487</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8355</v>
+        <v>2.0549</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5815</v>
+        <v>6.8809</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7139</v>
+        <v>3.8634</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8355</v>
+        <v>2.0549</v>
       </c>
       <c r="K4" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L4" t="n">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="M4" t="n">
-        <v>6.549399999999999</v>
+        <v>5.9183</v>
       </c>
       <c r="N4" t="n">
-        <v>154</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8618</v>
+        <v>5.7361</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4316</v>
+        <v>2.3795</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0045</v>
+        <v>2.0073</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8618</v>
+        <v>5.7361</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6351</v>
+        <v>4.4895</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0417</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>7.0994</v>
+        <v>10.4129</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8336</v>
+        <v>5.8465</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0417</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L5" t="n">
-        <v>152</v>
+        <v>72</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8753</v>
+        <v>6.6111</v>
       </c>
       <c r="N5" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8366</v>
+        <v>5.6989</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4211</v>
+        <v>2.364</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9933</v>
+        <v>1.9903</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8366</v>
+        <v>5.6989</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7725</v>
+        <v>2.7225</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7387</v>
+        <v>2.651</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3432</v>
+        <v>3.289</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4294</v>
+        <v>3.3769</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7387</v>
+        <v>2.651</v>
       </c>
       <c r="K6" t="n">
         <v>146</v>
@@ -713,7 +713,7 @@
         <v>97</v>
       </c>
       <c r="M6" t="n">
-        <v>6.1681</v>
+        <v>6.0279</v>
       </c>
       <c r="N6" t="n">
         <v>243</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.4731</v>
+        <v>5.4822</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2704</v>
+        <v>2.2741</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8309</v>
+        <v>1.8916</v>
       </c>
       <c r="E7" t="n">
-        <v>5.4731</v>
+        <v>5.4822</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8084</v>
+        <v>0.8215</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6036</v>
+        <v>4.5996</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8084</v>
+        <v>0.8215</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8084</v>
+        <v>0.8215</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6036</v>
+        <v>4.5996</v>
       </c>
       <c r="K7" t="n">
         <v>105</v>
@@ -759,7 +759,7 @@
         <v>213</v>
       </c>
       <c r="M7" t="n">
-        <v>5.412</v>
+        <v>5.4211</v>
       </c>
       <c r="N7" t="n">
         <v>318</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.9513</v>
+        <v>4.7331</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0539</v>
+        <v>1.9634</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5978</v>
+        <v>1.5504</v>
       </c>
       <c r="E8" t="n">
-        <v>4.9513</v>
+        <v>4.7331</v>
       </c>
       <c r="F8" t="n">
-        <v>3.9178</v>
+        <v>3.765</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7944</v>
+        <v>0.729</v>
       </c>
       <c r="H8" t="n">
-        <v>8.0322</v>
+        <v>7.6927</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3373</v>
+        <v>4.3192</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7944</v>
+        <v>0.729</v>
       </c>
       <c r="K8" t="n">
         <v>82</v>
@@ -805,7 +805,7 @@
         <v>72</v>
       </c>
       <c r="M8" t="n">
-        <v>5.1317</v>
+        <v>5.0482</v>
       </c>
       <c r="N8" t="n">
         <v>154</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.806</v>
+        <v>4.663</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9936</v>
+        <v>1.9343</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5329</v>
+        <v>1.5184</v>
       </c>
       <c r="E9" t="n">
-        <v>4.806</v>
+        <v>4.663</v>
       </c>
       <c r="F9" t="n">
-        <v>1.821</v>
+        <v>1.8238</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8533</v>
+        <v>2.7075</v>
       </c>
       <c r="H9" t="n">
-        <v>1.821</v>
+        <v>1.8238</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9833</v>
+        <v>1.024</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8533</v>
+        <v>2.7075</v>
       </c>
       <c r="K9" t="n">
         <v>85</v>
@@ -851,7 +851,7 @@
         <v>152</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8366</v>
+        <v>3.7315</v>
       </c>
       <c r="N9" t="n">
         <v>237</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1742</v>
+        <v>4.0734</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7315</v>
+        <v>1.6897</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2507</v>
+        <v>1.2498</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1742</v>
+        <v>4.0734</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5801</v>
+        <v>1.5041</v>
       </c>
       <c r="G10" t="n">
-        <v>2.484</v>
+        <v>2.4593</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5801</v>
+        <v>1.5041</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6208</v>
+        <v>1.5443</v>
       </c>
       <c r="J10" t="n">
-        <v>2.484</v>
+        <v>2.4593</v>
       </c>
       <c r="K10" t="n">
         <v>146</v>
@@ -897,7 +897,7 @@
         <v>97</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1048</v>
+        <v>4.0036</v>
       </c>
       <c r="N10" t="n">
         <v>243</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8421</v>
+        <v>3.7383</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5938</v>
+        <v>1.5507</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1024</v>
+        <v>1.0972</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8421</v>
+        <v>3.7383</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2955</v>
+        <v>3.2989</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4013</v>
+        <v>0.2941</v>
       </c>
       <c r="H11" t="n">
-        <v>5.979</v>
+        <v>5.943</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2286</v>
+        <v>3.3368</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4013</v>
+        <v>0.2941</v>
       </c>
       <c r="K11" t="n">
         <v>82</v>
@@ -943,7 +943,7 @@
         <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6299</v>
+        <v>3.6309</v>
       </c>
       <c r="N11" t="n">
         <v>154</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.727</v>
+        <v>3.713</v>
       </c>
       <c r="C12" t="n">
-        <v>1.546</v>
+        <v>1.5402</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0509</v>
+        <v>1.0857</v>
       </c>
       <c r="E12" t="n">
-        <v>3.727</v>
+        <v>3.713</v>
       </c>
       <c r="F12" t="n">
-        <v>2.813</v>
+        <v>2.8551</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7902</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3869</v>
+        <v>4.2766</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3689</v>
+        <v>2.4012</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7902</v>
       </c>
       <c r="K12" t="n">
         <v>85</v>
@@ -989,7 +989,7 @@
         <v>152</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2152</v>
+        <v>3.1914</v>
       </c>
       <c r="N12" t="n">
         <v>237</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2366</v>
+        <v>3.1357</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3426</v>
+        <v>1.3008</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8319</v>
+        <v>0.8227</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2366</v>
+        <v>3.1357</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7085</v>
+        <v>2.4094</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5436</v>
+        <v>0.6842</v>
       </c>
       <c r="H13" t="n">
-        <v>7.3414</v>
+        <v>2.5715</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9643</v>
+        <v>2.6402</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5436</v>
+        <v>0.6842</v>
       </c>
       <c r="K13" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="L13" t="n">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4207</v>
+        <v>3.3244</v>
       </c>
       <c r="N13" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1555</v>
+        <v>3.1313</v>
       </c>
       <c r="C14" t="n">
-        <v>1.309</v>
+        <v>1.2989</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7957</v>
+        <v>0.8207</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1555</v>
+        <v>3.1313</v>
       </c>
       <c r="F14" t="n">
-        <v>2.429</v>
+        <v>3.5813</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6844</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5914</v>
+        <v>7.0032</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6582</v>
+        <v>3.9321</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6844</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="L14" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3426</v>
+        <v>3.4104</v>
       </c>
       <c r="N14" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8699</v>
+        <v>2.8113</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1905</v>
+        <v>1.1662</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6681</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8699</v>
+        <v>2.8113</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4286</v>
+        <v>2.4053</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1983</v>
+        <v>0.1631</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5905</v>
+        <v>2.562</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6573</v>
+        <v>2.6305</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1983</v>
+        <v>0.1631</v>
       </c>
       <c r="K15" t="n">
         <v>121</v>
@@ -1127,7 +1127,7 @@
         <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8556</v>
+        <v>2.7936</v>
       </c>
       <c r="N15" t="n">
         <v>172</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6882</v>
+        <v>2.6652</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1151</v>
+        <v>1.1056</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5869</v>
+        <v>0.6083</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6882</v>
+        <v>2.6652</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7757</v>
+        <v>2.7258</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3086</v>
+        <v>-0.2817</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3502</v>
+        <v>3.2966</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3502</v>
+        <v>3.2966</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3086</v>
+        <v>-0.2817</v>
       </c>
       <c r="K16" t="n">
         <v>115</v>
@@ -1173,7 +1173,7 @@
         <v>35</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0416</v>
+        <v>3.0149</v>
       </c>
       <c r="N16" t="n">
         <v>150</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3196</v>
+        <v>2.253</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9346</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4223</v>
+        <v>0.4206</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3196</v>
+        <v>2.253</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6375</v>
+        <v>1.5886</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5695</v>
+        <v>0.5518</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6375</v>
+        <v>1.5886</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6797</v>
+        <v>1.631</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5695</v>
+        <v>0.5518</v>
       </c>
       <c r="K17" t="n">
         <v>121</v>
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2492</v>
+        <v>2.1828</v>
       </c>
       <c r="N17" t="n">
         <v>172</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8255</v>
+        <v>1.6868</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7573</v>
+        <v>0.6997</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2016</v>
+        <v>0.1626</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8255</v>
+        <v>1.6868</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6373</v>
+        <v>1.5277</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1281</v>
+        <v>0.0989</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6373</v>
+        <v>1.5277</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6795</v>
+        <v>1.5686</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1281</v>
+        <v>0.0989</v>
       </c>
       <c r="K18" t="n">
         <v>121</v>
@@ -1265,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8076</v>
+        <v>1.6675</v>
       </c>
       <c r="N18" t="n">
         <v>172</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2042</v>
+        <v>1.1414</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4995</v>
+        <v>0.4735</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0759</v>
+        <v>-0.0858</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2042</v>
+        <v>1.1414</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1555</v>
+        <v>1.0927</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1555</v>
+        <v>1.0927</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1555</v>
+        <v>1.0927</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1555</v>
+        <v>1.0927</v>
       </c>
       <c r="N19" t="n">
         <v>126</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.699</v>
+        <v>0.6351</v>
       </c>
       <c r="C20" t="n">
-        <v>0.29</v>
+        <v>0.2635</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3016</v>
+        <v>-0.3165</v>
       </c>
       <c r="E20" t="n">
-        <v>0.699</v>
+        <v>0.6351</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6155</v>
+        <v>0.5799</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0135</v>
+        <v>-0.0148</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6155</v>
+        <v>0.5799</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6155</v>
+        <v>0.5799</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0135</v>
+        <v>-0.0148</v>
       </c>
       <c r="K20" t="n">
         <v>115</v>
@@ -1357,7 +1357,7 @@
         <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>0.629</v>
+        <v>0.5650999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>150</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5743</v>
+        <v>0.5331</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2382</v>
+        <v>0.2211</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3573</v>
+        <v>-0.3629</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5743</v>
+        <v>0.5331</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7037</v>
+        <v>0.6594</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1062</v>
+        <v>-0.1031</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7037</v>
+        <v>0.6594</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7218</v>
+        <v>0.677</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1062</v>
+        <v>-0.1031</v>
       </c>
       <c r="K21" t="n">
         <v>121</v>
@@ -1403,7 +1403,7 @@
         <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6156</v>
+        <v>0.5739000000000001</v>
       </c>
       <c r="N21" t="n">
         <v>172</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5447</v>
+        <v>0.4741</v>
       </c>
       <c r="C22" t="n">
-        <v>0.226</v>
+        <v>0.1967</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3705</v>
+        <v>-0.3898</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5447</v>
+        <v>0.4741</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2684</v>
+        <v>0.1978</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2684</v>
+        <v>0.1978</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2684</v>
+        <v>0.1978</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2684</v>
+        <v>0.1978</v>
       </c>
       <c r="N22" t="n">
         <v>126</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4161</v>
+        <v>0.344</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1726</v>
+        <v>0.1427</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.428</v>
+        <v>-0.4491</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4161</v>
+        <v>0.344</v>
       </c>
       <c r="F23" t="n">
-        <v>0.185</v>
+        <v>0.1456</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4134</v>
+        <v>0.3807</v>
       </c>
       <c r="H23" t="n">
-        <v>0.185</v>
+        <v>0.1456</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1898</v>
+        <v>0.1495</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4134</v>
+        <v>0.3807</v>
       </c>
       <c r="K23" t="n">
         <v>146</v>
@@ -1495,7 +1495,7 @@
         <v>97</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6032</v>
+        <v>0.5302</v>
       </c>
       <c r="N23" t="n">
         <v>243</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3923</v>
+        <v>0.3265</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1627</v>
+        <v>0.1354</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4386</v>
+        <v>-0.4571</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3923</v>
+        <v>0.3265</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2085</v>
+        <v>0.1738</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2965</v>
+        <v>0.2655</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2085</v>
+        <v>0.1738</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2085</v>
+        <v>0.1738</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2965</v>
+        <v>0.2655</v>
       </c>
       <c r="K24" t="n">
         <v>115</v>
@@ -1541,7 +1541,7 @@
         <v>35</v>
       </c>
       <c r="M24" t="n">
-        <v>0.505</v>
+        <v>0.4393</v>
       </c>
       <c r="N24" t="n">
         <v>150</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1014</v>
+        <v>0.0043</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0421</v>
+        <v>0.0018</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5685</v>
+        <v>-0.6038</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1014</v>
+        <v>0.0043</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0334</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0334</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0334</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0334</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>88</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0509</v>
+        <v>-0.1736</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0211</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.6849</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0509</v>
+        <v>-0.1736</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0721</v>
+        <v>-0.0506</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0721</v>
+        <v>-0.0506</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0721</v>
+        <v>-0.0506</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0721</v>
+        <v>-0.0506</v>
       </c>
       <c r="N26" t="n">
         <v>88</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2844</v>
+        <v>-0.254</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.118</v>
+        <v>-0.1054</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7409</v>
+        <v>-0.7215</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2844</v>
+        <v>-0.254</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6708</v>
+        <v>0.6923</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.9319</v>
+        <v>-0.923</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6708</v>
+        <v>0.6923</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6708</v>
+        <v>0.6923</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9319</v>
+        <v>-0.923</v>
       </c>
       <c r="K27" t="n">
         <v>115</v>
@@ -1679,7 +1679,7 @@
         <v>35</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2611</v>
+        <v>-0.2307</v>
       </c>
       <c r="N27" t="n">
         <v>150</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3409</v>
+        <v>-0.2972</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1414</v>
+        <v>-0.1233</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7661</v>
+        <v>-0.7412</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3409</v>
+        <v>-0.2972</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0319</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1342</v>
+        <v>-0.1364</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0319</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.042</v>
+        <v>-0.0179</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1342</v>
+        <v>-0.1364</v>
       </c>
       <c r="K28" t="n">
         <v>82</v>
@@ -1725,7 +1725,7 @@
         <v>72</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1762</v>
+        <v>-0.1543</v>
       </c>
       <c r="N28" t="n">
         <v>154</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3835</v>
+        <v>-0.4469</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1591</v>
+        <v>-0.1854</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7851</v>
+        <v>-0.8094</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3835</v>
+        <v>-0.4469</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2685</v>
+        <v>-0.3319</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2685</v>
+        <v>-0.3319</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2685</v>
+        <v>-0.3319</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2685</v>
+        <v>-0.3319</v>
       </c>
       <c r="N29" t="n">
         <v>126</v>
@@ -1780,7 +1780,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1790,83 +1790,83 @@
         <v>-0.2406</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8729</v>
+        <v>-0.87</v>
       </c>
       <c r="E30" t="n">
         <v>-0.58</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3411</v>
+        <v>-0.4635</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3411</v>
+        <v>-0.4635</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3411</v>
+        <v>-0.4635</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3411</v>
+        <v>-0.4635</v>
       </c>
       <c r="N30" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.6511</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2419</v>
+        <v>-0.2701</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8743</v>
+        <v>-0.9024</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.6511</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4667</v>
+        <v>-0.4122</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4667</v>
+        <v>-0.4122</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4667</v>
+        <v>-0.4122</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4667</v>
+        <v>-0.4122</v>
       </c>
       <c r="N31" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9225</v>
+        <v>-0.9641</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3827</v>
+        <v>-0.3999</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.0259</v>
+        <v>-1.045</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9225</v>
+        <v>-0.9641</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8062</v>
+        <v>-0.8478</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8062</v>
+        <v>-0.8478</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8062</v>
+        <v>-0.8478</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8062</v>
+        <v>-0.8478</v>
       </c>
       <c r="N32" t="n">
         <v>88</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0087</v>
+        <v>-0.9984</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4184</v>
+        <v>-0.4142</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0644</v>
+        <v>-1.0606</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0087</v>
+        <v>-0.9984</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.6539</v>
+        <v>-1.6165</v>
       </c>
       <c r="G33" t="n">
-        <v>0.967</v>
+        <v>0.9399</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.6539</v>
+        <v>-1.6165</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8931</v>
+        <v>-0.9076</v>
       </c>
       <c r="J33" t="n">
-        <v>0.967</v>
+        <v>0.9399</v>
       </c>
       <c r="K33" t="n">
         <v>85</v>
@@ -1955,7 +1955,7 @@
         <v>152</v>
       </c>
       <c r="M33" t="n">
-        <v>0.07389999999999997</v>
+        <v>0.0323</v>
       </c>
       <c r="N33" t="n">
         <v>237</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0701</v>
+        <v>-1.0762</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4439</v>
+        <v>-0.4464</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0918</v>
+        <v>-1.096</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0701</v>
+        <v>-1.0762</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8779</v>
+        <v>-0.884</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8779</v>
+        <v>-0.884</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8779</v>
+        <v>-0.884</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8779</v>
+        <v>-0.884</v>
       </c>
       <c r="N34" t="n">
         <v>126</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0942</v>
+        <v>-1.1398</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4539</v>
+        <v>-0.4728</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1026</v>
+        <v>-1.125</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0942</v>
+        <v>-1.1398</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.803</v>
+        <v>-0.861</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.145</v>
+        <v>-0.1326</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.803</v>
+        <v>-0.861</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8237</v>
+        <v>-0.884</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.145</v>
+        <v>-0.1326</v>
       </c>
       <c r="K35" t="n">
         <v>146</v>
@@ -2047,7 +2047,7 @@
         <v>97</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9687</v>
+        <v>-1.0166</v>
       </c>
       <c r="N35" t="n">
         <v>243</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3112</v>
+        <v>-1.2799</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.5309</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1995</v>
+        <v>-1.1888</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3112</v>
+        <v>-1.2799</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.215</v>
+        <v>-1.1837</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.215</v>
+        <v>-1.1837</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.215</v>
+        <v>-1.1837</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.215</v>
+        <v>-1.1837</v>
       </c>
       <c r="N36" t="n">
         <v>88</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.7125</v>
+        <v>-1.5555</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.7104</v>
+        <v>-0.6453</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.3788</v>
+        <v>-1.3144</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.7125</v>
+        <v>-1.5555</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0182</v>
+        <v>0.1204</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.6698</v>
+        <v>-1.615</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0182</v>
+        <v>0.1204</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0182</v>
+        <v>0.1204</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.6698</v>
+        <v>-1.615</v>
       </c>
       <c r="K37" t="n">
         <v>105</v>
@@ -2139,7 +2139,7 @@
         <v>213</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.6516</v>
+        <v>-1.4946</v>
       </c>
       <c r="N37" t="n">
         <v>318</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7161</v>
+        <v>-1.7249</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7119</v>
+        <v>-0.7155</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.3804</v>
+        <v>-1.3916</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7161</v>
+        <v>-1.7249</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8437</v>
+        <v>-0.8812</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5999</v>
+        <v>-0.5712</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8437</v>
+        <v>-0.8812</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8437</v>
+        <v>-0.8812</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5999</v>
+        <v>-0.5712</v>
       </c>
       <c r="K38" t="n">
         <v>115</v>
@@ -2185,7 +2185,7 @@
         <v>35</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4436</v>
+        <v>-1.4524</v>
       </c>
       <c r="N38" t="n">
         <v>150</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.1385</v>
+        <v>-2.1986</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8871</v>
+        <v>-0.912</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.569</v>
+        <v>-1.6074</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.1385</v>
+        <v>-2.1986</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0669</v>
+        <v>-1.1334</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7143</v>
+        <v>-0.7079</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0669</v>
+        <v>-1.1334</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0944</v>
+        <v>-1.1637</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7143</v>
+        <v>-0.7079</v>
       </c>
       <c r="K39" t="n">
         <v>121</v>
@@ -2231,7 +2231,7 @@
         <v>51</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8087</v>
+        <v>-1.8716</v>
       </c>
       <c r="N39" t="n">
         <v>172</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.8201</v>
+        <v>-2.8544</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.1698</v>
+        <v>-1.1841</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.8735</v>
+        <v>-1.9061</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.8201</v>
+        <v>-2.8544</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5115</v>
+        <v>-1.5458</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5115</v>
+        <v>-1.5458</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8162</v>
+        <v>-0.8679</v>
       </c>
       <c r="J40" t="n">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>72</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8162</v>
+        <v>-1.8679</v>
       </c>
       <c r="N40" t="n">
         <v>154</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.439</v>
+        <v>-3.3196</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.4266</v>
+        <v>-1.377</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.1499</v>
+        <v>-2.118</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.439</v>
+        <v>-3.3196</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3988</v>
+        <v>-1.3884</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.6368</v>
+        <v>-1.5278</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3988</v>
+        <v>-1.3884</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3988</v>
+        <v>-1.3884</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.6368</v>
+        <v>-1.5278</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2323,7 +2323,7 @@
         <v>213</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.0356</v>
+        <v>-2.9162</v>
       </c>
       <c r="N41" t="n">
         <v>318</v>
@@ -2429,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1254</v>
+        <v>1.132</v>
       </c>
       <c r="J2" t="n">
-        <v>24.7588</v>
+        <v>24.904</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5557</v>
+        <v>0.5179</v>
       </c>
       <c r="J3" t="n">
-        <v>12.2254</v>
+        <v>11.3938</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5557</v>
+        <v>0.5179</v>
       </c>
       <c r="J4" t="n">
-        <v>12.2254</v>
+        <v>11.3938</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1919</v>
+        <v>-0.1573</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.2218</v>
+        <v>-3.4606</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6353</v>
+        <v>-0.6002</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.9766</v>
+        <v>-13.2044</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.7841</v>
       </c>
       <c r="J7" t="n">
-        <v>18.2622</v>
+        <v>17.2502</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.37</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7235</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>15.917</v>
+        <v>14.7598</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2865</v>
+        <v>-0.2678</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.303</v>
+        <v>-5.8916</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3244</v>
+        <v>-0.3076</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.1368</v>
+        <v>-6.7672</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.45</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5611</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.3442</v>
+        <v>-12.5642</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.52</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2034</v>
+        <v>1.2207</v>
       </c>
       <c r="J12" t="n">
-        <v>28.8816</v>
+        <v>29.2968</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.45</v>
       </c>
       <c r="I13" t="n">
-        <v>1.07</v>
+        <v>1.0698</v>
       </c>
       <c r="J13" t="n">
-        <v>25.68</v>
+        <v>25.6752</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3718</v>
+        <v>0.3342</v>
       </c>
       <c r="J14" t="n">
-        <v>8.9232</v>
+        <v>8.020799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.79</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6342</v>
+        <v>-0.5989</v>
       </c>
       <c r="J15" t="n">
-        <v>-15.2208</v>
+        <v>-14.3736</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.789</v>
+        <v>-0.7655</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.936</v>
+        <v>-18.372</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4183</v>
+        <v>0.3624</v>
       </c>
       <c r="J17" t="n">
-        <v>10.0392</v>
+        <v>8.6976</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1612</v>
+        <v>0.1245</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8688</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1065</v>
+        <v>-0.0905</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.556</v>
+        <v>-2.172</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1065</v>
+        <v>-0.0905</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.556</v>
+        <v>-2.172</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.54</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.483</v>
+        <v>-0.4814</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.592</v>
+        <v>-11.5536</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.46</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6512</v>
+        <v>0.6863</v>
       </c>
       <c r="J22" t="n">
-        <v>15.6288</v>
+        <v>16.4712</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.19</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3218</v>
+        <v>0.3114</v>
       </c>
       <c r="J23" t="n">
-        <v>7.7232</v>
+        <v>7.4736</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0445</v>
+        <v>-0.0336</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.068</v>
+        <v>-0.8064</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1011</v>
+        <v>-0.0839</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.4264</v>
+        <v>-2.0136</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4739</v>
+        <v>-0.4724</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.3736</v>
+        <v>-11.3376</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5513</v>
+        <v>0.4812</v>
       </c>
       <c r="J27" t="n">
-        <v>13.2312</v>
+        <v>11.5488</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5191</v>
+        <v>0.45</v>
       </c>
       <c r="J28" t="n">
-        <v>12.4584</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1608</v>
+        <v>0.1251</v>
       </c>
       <c r="J29" t="n">
-        <v>3.8592</v>
+        <v>3.0024</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1232</v>
+        <v>-0.1046</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.9568</v>
+        <v>-2.5104</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1813</v>
+        <v>-0.1611</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.3512</v>
+        <v>-3.8664</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.65</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4412</v>
+        <v>1.4816</v>
       </c>
       <c r="J32" t="n">
-        <v>28.824</v>
+        <v>29.632</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6005</v>
+        <v>0.5637</v>
       </c>
       <c r="J33" t="n">
-        <v>12.01</v>
+        <v>11.274</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.18</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5115</v>
+        <v>0.4729</v>
       </c>
       <c r="J34" t="n">
-        <v>10.23</v>
+        <v>9.458</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3923</v>
+        <v>-0.3498</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.846</v>
+        <v>-6.996</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.67</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8953</v>
+        <v>-0.8824</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.906</v>
+        <v>-17.648</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7087</v>
+        <v>0.6555</v>
       </c>
       <c r="J37" t="n">
-        <v>14.174</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.19</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4303</v>
+        <v>0.3735</v>
       </c>
       <c r="J38" t="n">
-        <v>8.606</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.07</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2016</v>
+        <v>0.1599</v>
       </c>
       <c r="J39" t="n">
-        <v>4.032</v>
+        <v>3.198</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.61</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4238</v>
+        <v>-0.4155</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.476000000000001</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.5</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5189</v>
+        <v>-0.5225</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.378</v>
+        <v>-10.45</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4841</v>
+        <v>0.5067</v>
       </c>
       <c r="J42" t="n">
-        <v>11.1343</v>
+        <v>11.6541</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.282</v>
+        <v>0.2688</v>
       </c>
       <c r="J43" t="n">
-        <v>6.486</v>
+        <v>6.1824</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0596</v>
+        <v>-0.0466</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.3708</v>
+        <v>-1.0718</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1253</v>
+        <v>-0.1065</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.8819</v>
+        <v>-2.4495</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3309</v>
+        <v>-0.3151</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.6107</v>
+        <v>-7.2473</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.8944</v>
       </c>
       <c r="J47" t="n">
-        <v>21.7143</v>
+        <v>20.5712</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0098</v>
+        <v>-0.0075</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.2254</v>
+        <v>-0.1725</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0355</v>
+        <v>-0.0262</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.8165</v>
+        <v>-0.6026</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1587</v>
+        <v>-0.1388</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.6501</v>
+        <v>-3.1924</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2543</v>
+        <v>-0.2353</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.8489</v>
+        <v>-5.4119</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.8</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3956</v>
+        <v>1.4188</v>
       </c>
       <c r="J52" t="n">
-        <v>33.4944</v>
+        <v>34.0512</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.05</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1893</v>
+        <v>0.1596</v>
       </c>
       <c r="J53" t="n">
-        <v>4.5432</v>
+        <v>3.8304</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3842</v>
+        <v>-0.3413</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.220800000000001</v>
+        <v>-8.1912</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4355</v>
+        <v>-0.3926</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.452</v>
+        <v>-9.4224</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.79</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6266</v>
+        <v>-0.5901</v>
       </c>
       <c r="J56" t="n">
-        <v>-15.0384</v>
+        <v>-14.1624</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4986</v>
+        <v>0.4607</v>
       </c>
       <c r="J57" t="n">
-        <v>11.9664</v>
+        <v>11.0568</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.16</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3663</v>
+        <v>0.3115</v>
       </c>
       <c r="J58" t="n">
-        <v>8.7912</v>
+        <v>7.476</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3116</v>
+        <v>0.2601</v>
       </c>
       <c r="J59" t="n">
-        <v>7.4784</v>
+        <v>6.2424</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2213</v>
+        <v>-0.2008</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.3112</v>
+        <v>-4.8192</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.58</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4538</v>
+        <v>-0.4494</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.8912</v>
+        <v>-10.7856</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.11</v>
       </c>
       <c r="I62" t="n">
-        <v>1.641</v>
+        <v>1.6715</v>
       </c>
       <c r="J62" t="n">
-        <v>24.615</v>
+        <v>25.0725</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.75</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2209</v>
+        <v>1.2203</v>
       </c>
       <c r="J63" t="n">
-        <v>18.3135</v>
+        <v>18.3045</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8223</v>
+        <v>0.8161</v>
       </c>
       <c r="J64" t="n">
-        <v>12.3345</v>
+        <v>12.2415</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.41</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7952</v>
+        <v>0.7892</v>
       </c>
       <c r="J65" t="n">
-        <v>11.928</v>
+        <v>11.838</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.95</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.287</v>
+        <v>-0.2592</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.305</v>
+        <v>-3.888</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6247</v>
+        <v>0.61</v>
       </c>
       <c r="J67" t="n">
-        <v>9.3705</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.91</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1134</v>
+        <v>-0.0988</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.701</v>
+        <v>-1.482</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.63</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3881</v>
+        <v>-0.3757</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.8215</v>
+        <v>-5.6355</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.57</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4415</v>
+        <v>-0.4337</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.6225</v>
+        <v>-6.5055</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.46</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5374</v>
+        <v>-0.5413</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.061</v>
+        <v>-8.1195</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4066</v>
+        <v>0.343</v>
       </c>
       <c r="J72" t="n">
-        <v>8.9452</v>
+        <v>7.546</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3597</v>
+        <v>0.2991</v>
       </c>
       <c r="J73" t="n">
-        <v>7.9134</v>
+        <v>6.5802</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.22</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3355</v>
+        <v>0.2769</v>
       </c>
       <c r="J74" t="n">
-        <v>7.381</v>
+        <v>6.0918</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.06</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1206</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>2.6532</v>
+        <v>1.9888</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4688</v>
+        <v>-0.4673</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.3136</v>
+        <v>-10.2806</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.72</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7994</v>
+        <v>0.8588</v>
       </c>
       <c r="J77" t="n">
-        <v>17.5868</v>
+        <v>18.8936</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.33</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4786</v>
+        <v>0.4988</v>
       </c>
       <c r="J78" t="n">
-        <v>10.5292</v>
+        <v>10.9736</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2373</v>
+        <v>-0.2172</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.2206</v>
+        <v>-4.7784</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.334</v>
+        <v>-0.3187</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.348</v>
+        <v>-7.0114</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3616</v>
+        <v>-0.3484</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.9552</v>
+        <v>-7.6648</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>0.656</v>
+        <v>0.6307</v>
       </c>
       <c r="J82" t="n">
-        <v>13.12</v>
+        <v>12.614</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0335</v>
+        <v>-0.026</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.67</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1386</v>
+        <v>-0.1215</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.772</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3824</v>
+        <v>-0.3696</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.648</v>
+        <v>-7.392</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.54</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4794</v>
+        <v>-0.4769</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.587999999999999</v>
+        <v>-9.538</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8992</v>
+        <v>0.8842</v>
       </c>
       <c r="J87" t="n">
-        <v>17.984</v>
+        <v>17.684</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7138</v>
+        <v>0.6998</v>
       </c>
       <c r="J88" t="n">
-        <v>14.276</v>
+        <v>13.996</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6694</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>13.388</v>
+        <v>13.136</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1021</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>2.042</v>
+        <v>1.634</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2699</v>
+        <v>-0.2318</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.398</v>
+        <v>-4.636</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.6092</v>
       </c>
       <c r="J92" t="n">
-        <v>19.158</v>
+        <v>18.276</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4741</v>
+        <v>0.428</v>
       </c>
       <c r="J93" t="n">
-        <v>14.223</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.83</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2213</v>
+        <v>-0.2008</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.639</v>
+        <v>-6.024</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.83</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2213</v>
+        <v>-0.2008</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.639</v>
+        <v>-6.024</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.356</v>
+        <v>-0.3417</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.68</v>
+        <v>-10.251</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.053</v>
+        <v>1.0427</v>
       </c>
       <c r="J97" t="n">
-        <v>31.59</v>
+        <v>31.281</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7456</v>
+        <v>0.7305</v>
       </c>
       <c r="J98" t="n">
-        <v>22.368</v>
+        <v>21.915</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.18</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4858</v>
+        <v>0.4675</v>
       </c>
       <c r="J99" t="n">
-        <v>14.574</v>
+        <v>14.025</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.03</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1048</v>
+        <v>0.0844</v>
       </c>
       <c r="J100" t="n">
-        <v>3.144</v>
+        <v>2.532</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.85</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5065</v>
+        <v>-0.4672</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.195</v>
+        <v>-14.016</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.71</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2227</v>
+        <v>1.221</v>
       </c>
       <c r="J102" t="n">
-        <v>23.2313</v>
+        <v>23.199</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.46</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8914</v>
+        <v>0.8769</v>
       </c>
       <c r="J103" t="n">
-        <v>16.9366</v>
+        <v>16.6611</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.29</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6393</v>
       </c>
       <c r="J104" t="n">
-        <v>12.3443</v>
+        <v>12.1467</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2466</v>
+        <v>-0.2109</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.6854</v>
+        <v>-4.0071</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4917</v>
+        <v>-0.4534</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.3423</v>
+        <v>-8.614599999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.26</v>
       </c>
       <c r="I107" t="n">
-        <v>0.523</v>
+        <v>0.494</v>
       </c>
       <c r="J107" t="n">
-        <v>9.936999999999999</v>
+        <v>9.385999999999999</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.22</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4733</v>
+        <v>0.4283</v>
       </c>
       <c r="J108" t="n">
-        <v>8.992699999999999</v>
+        <v>8.137700000000001</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.96</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0561</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.3034</v>
+        <v>-1.0659</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.68</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3599</v>
+        <v>-0.3456</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.8381</v>
+        <v>-6.5664</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.55</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4751</v>
+        <v>-0.4726</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.026899999999999</v>
+        <v>-8.9794</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.89</v>
       </c>
       <c r="I112" t="n">
-        <v>1.404</v>
+        <v>1.4137</v>
       </c>
       <c r="J112" t="n">
-        <v>22.464</v>
+        <v>22.6192</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.5</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9202</v>
+        <v>0.9104</v>
       </c>
       <c r="J113" t="n">
-        <v>14.7232</v>
+        <v>14.5664</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.41</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8032</v>
+        <v>0.7945</v>
       </c>
       <c r="J114" t="n">
-        <v>12.8512</v>
+        <v>12.712</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.32</v>
       </c>
       <c r="I115" t="n">
-        <v>0.6775</v>
+        <v>0.6717</v>
       </c>
       <c r="J115" t="n">
-        <v>10.84</v>
+        <v>10.7472</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.07</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1907</v>
+        <v>0.1597</v>
       </c>
       <c r="J116" t="n">
-        <v>3.0512</v>
+        <v>2.5552</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1768</v>
+        <v>-0.161</v>
       </c>
       <c r="J117" t="n">
-        <v>-2.8288</v>
+        <v>-2.576</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.78</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.24</v>
+        <v>-0.2256</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.84</v>
+        <v>-3.6096</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.78</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.24</v>
+        <v>-0.2256</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.84</v>
+        <v>-3.6096</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.54</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4568</v>
+        <v>-0.4504</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.3088</v>
+        <v>-7.2064</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5095</v>
+        <v>-0.5088</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.151999999999999</v>
+        <v>-8.1408</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.37</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7936</v>
+        <v>0.7775</v>
       </c>
       <c r="J122" t="n">
-        <v>17.4592</v>
+        <v>17.105</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5168</v>
       </c>
       <c r="J123" t="n">
-        <v>11.6314</v>
+        <v>11.3696</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3736</v>
+        <v>0.335</v>
       </c>
       <c r="J124" t="n">
-        <v>8.219200000000001</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3075</v>
+        <v>-0.2662</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.765</v>
+        <v>-5.8564</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3621</v>
+        <v>-0.3196</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.9662</v>
+        <v>-7.0312</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.11</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2832</v>
+        <v>0.2338</v>
       </c>
       <c r="J127" t="n">
-        <v>6.2304</v>
+        <v>5.1436</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0506</v>
+        <v>0.0339</v>
       </c>
       <c r="J128" t="n">
-        <v>1.1132</v>
+        <v>0.7458</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1075</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.365</v>
+        <v>-1.9998</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1424</v>
+        <v>-0.1237</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.1328</v>
+        <v>-2.7214</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.78</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.267</v>
+        <v>-0.2476</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.874</v>
+        <v>-5.4472</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.89</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4969</v>
+        <v>1.5289</v>
       </c>
       <c r="J132" t="n">
-        <v>43.4101</v>
+        <v>44.3381</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2698</v>
+        <v>0.2361</v>
       </c>
       <c r="J133" t="n">
-        <v>7.8242</v>
+        <v>6.8469</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0189</v>
+        <v>-0.014</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.5481</v>
+        <v>-0.406</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1566</v>
+        <v>-0.1252</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.5414</v>
+        <v>-3.6308</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9361</v>
+        <v>-0.9277</v>
       </c>
       <c r="J136" t="n">
-        <v>-27.1469</v>
+        <v>-26.9033</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.55</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8365</v>
+        <v>0.8032</v>
       </c>
       <c r="J137" t="n">
-        <v>24.2585</v>
+        <v>23.2928</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2356</v>
+        <v>0.1905</v>
       </c>
       <c r="J138" t="n">
-        <v>6.8324</v>
+        <v>5.5245</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0849</v>
+        <v>-0.0696</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.4621</v>
+        <v>-2.0184</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.89</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1568</v>
+        <v>-0.137</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.5472</v>
+        <v>-3.973</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.44</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5719</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.5851</v>
+        <v>-16.9418</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.21</v>
+        <v>1.2263</v>
       </c>
       <c r="J142" t="n">
-        <v>33.88</v>
+        <v>34.3364</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.46</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0573</v>
+        <v>1.0638</v>
       </c>
       <c r="J143" t="n">
-        <v>29.6044</v>
+        <v>29.7864</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.38</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9218</v>
+        <v>0.9062</v>
       </c>
       <c r="J144" t="n">
-        <v>25.8104</v>
+        <v>25.3736</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.86</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4752</v>
+        <v>-0.4342</v>
       </c>
       <c r="J145" t="n">
-        <v>-13.3056</v>
+        <v>-12.1576</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.2016</v>
+        <v>-1.2313</v>
       </c>
       <c r="J146" t="n">
-        <v>-33.6448</v>
+        <v>-34.4764</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.66</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1056</v>
+        <v>1.1007</v>
       </c>
       <c r="J147" t="n">
-        <v>30.9568</v>
+        <v>30.8196</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0478</v>
+        <v>0.0319</v>
       </c>
       <c r="J148" t="n">
-        <v>1.3384</v>
+        <v>0.8932</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.79</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.259</v>
+        <v>-0.2392</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.252</v>
+        <v>-6.6976</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.71</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3352</v>
+        <v>-0.3192</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.3856</v>
+        <v>-8.9376</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3899</v>
+        <v>-0.3783</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.9172</v>
+        <v>-10.5924</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.72</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4302</v>
+        <v>1.4654</v>
       </c>
       <c r="J152" t="n">
-        <v>34.3248</v>
+        <v>35.1696</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7977</v>
+        <v>0.7709</v>
       </c>
       <c r="J153" t="n">
-        <v>19.1448</v>
+        <v>18.5016</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.88</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4136</v>
+        <v>-0.3708</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.926399999999999</v>
+        <v>-8.8992</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6071</v>
+        <v>-0.5699</v>
       </c>
       <c r="J155" t="n">
-        <v>-14.5704</v>
+        <v>-13.6776</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6528</v>
+        <v>-0.6182</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.6672</v>
+        <v>-14.8368</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.28</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5689</v>
+        <v>0.51</v>
       </c>
       <c r="J157" t="n">
-        <v>13.6536</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.24</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5038</v>
+        <v>0.445</v>
       </c>
       <c r="J158" t="n">
-        <v>12.0912</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.15</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3488</v>
+        <v>0.2949</v>
       </c>
       <c r="J159" t="n">
-        <v>8.3712</v>
+        <v>7.0776</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.65</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.392</v>
+        <v>-0.3809</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.407999999999999</v>
+        <v>-9.1416</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4186</v>
+        <v>-0.4102</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.0464</v>
+        <v>-9.844799999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7778</v>
+        <v>0.7077</v>
       </c>
       <c r="J162" t="n">
-        <v>12.4448</v>
+        <v>11.3232</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.69</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7688</v>
+        <v>0.6987</v>
       </c>
       <c r="J163" t="n">
-        <v>12.3008</v>
+        <v>11.1792</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.63</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7141</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>11.4256</v>
+        <v>10.3152</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.52</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6125</v>
+        <v>0.546</v>
       </c>
       <c r="J165" t="n">
-        <v>9.800000000000001</v>
+        <v>8.736000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0106</v>
+        <v>-0.0009</v>
       </c>
       <c r="J166" t="n">
-        <v>0.1696</v>
+        <v>-0.0144</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.85</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1567</v>
+        <v>-0.1393</v>
       </c>
       <c r="J167" t="n">
-        <v>-2.5072</v>
+        <v>-2.2288</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.78</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2327</v>
+        <v>-0.2182</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.7232</v>
+        <v>-3.4912</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.243</v>
+        <v>-0.2289</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.888</v>
+        <v>-3.6624</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.45</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.5325</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.491199999999999</v>
+        <v>-8.52</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.38</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.592</v>
+        <v>-0.6027</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.472</v>
+        <v>-9.6432</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.86</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1535</v>
+        <v>-0.1372</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.763</v>
+        <v>-2.4696</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1649</v>
+        <v>-0.1487</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.9682</v>
+        <v>-2.6766</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.71</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3068</v>
+        <v>-0.2938</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.5224</v>
+        <v>-5.2884</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.52</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4739</v>
+        <v>-0.4692</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.530200000000001</v>
+        <v>-8.445600000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5265</v>
+        <v>-0.5279</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.477</v>
+        <v>-9.5022</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.69</v>
       </c>
       <c r="I177" t="n">
-        <v>1.325</v>
+        <v>1.3456</v>
       </c>
       <c r="J177" t="n">
-        <v>23.85</v>
+        <v>24.2208</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9578</v>
+        <v>0.9526</v>
       </c>
       <c r="J178" t="n">
-        <v>17.2404</v>
+        <v>17.1468</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.27</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6747</v>
+        <v>0.651</v>
       </c>
       <c r="J179" t="n">
-        <v>12.1446</v>
+        <v>11.718</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6542</v>
+        <v>0.6296</v>
       </c>
       <c r="J180" t="n">
-        <v>11.7756</v>
+        <v>11.3328</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.07</v>
       </c>
       <c r="I181" t="n">
-        <v>0.2053</v>
+        <v>0.1758</v>
       </c>
       <c r="J181" t="n">
-        <v>3.6954</v>
+        <v>3.1644</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7514</v>
+        <v>0.6955</v>
       </c>
       <c r="J182" t="n">
-        <v>18.0336</v>
+        <v>16.692</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3192</v>
+        <v>0.268</v>
       </c>
       <c r="J183" t="n">
-        <v>7.6608</v>
+        <v>6.432</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I184" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0718</v>
       </c>
       <c r="J184" t="n">
-        <v>2.2968</v>
+        <v>1.7232</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.83</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2265</v>
+        <v>-0.2061</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.436</v>
+        <v>-4.9464</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2265</v>
+        <v>-0.2061</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.436</v>
+        <v>-4.9464</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.41</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0048</v>
+        <v>1.0038</v>
       </c>
       <c r="J187" t="n">
-        <v>24.1152</v>
+        <v>24.0912</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.31</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8085</v>
+        <v>0.7826</v>
       </c>
       <c r="J188" t="n">
-        <v>19.404</v>
+        <v>18.7824</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.221</v>
+        <v>0.1878</v>
       </c>
       <c r="J189" t="n">
-        <v>5.304</v>
+        <v>4.5072</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.9</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3543</v>
+        <v>-0.3117</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.5032</v>
+        <v>-7.4808</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9676</v>
+        <v>-0.9614</v>
       </c>
       <c r="J191" t="n">
-        <v>-23.2224</v>
+        <v>-23.0736</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.14</v>
       </c>
       <c r="I192" t="n">
-        <v>1.9078</v>
+        <v>1.9818</v>
       </c>
       <c r="J192" t="n">
-        <v>41.9716</v>
+        <v>43.5996</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.27</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6866</v>
+        <v>0.658</v>
       </c>
       <c r="J193" t="n">
-        <v>15.1052</v>
+        <v>14.476</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3047</v>
+        <v>0.2726</v>
       </c>
       <c r="J194" t="n">
-        <v>6.7034</v>
+        <v>5.9972</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.92</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3314</v>
+        <v>-0.2919</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.2908</v>
+        <v>-6.4218</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.74</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.742</v>
       </c>
       <c r="J196" t="n">
-        <v>-16.8212</v>
+        <v>-16.324</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.24</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4533</v>
       </c>
       <c r="J197" t="n">
-        <v>11.2552</v>
+        <v>9.9726</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.21</v>
       </c>
       <c r="I198" t="n">
-        <v>0.461</v>
+        <v>0.4032</v>
       </c>
       <c r="J198" t="n">
-        <v>10.142</v>
+        <v>8.8704</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.85</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1979</v>
+        <v>-0.1774</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.3538</v>
+        <v>-3.9028</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2083</v>
+        <v>-0.1878</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.5826</v>
+        <v>-4.1316</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3805</v>
+        <v>-0.3681</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.371</v>
+        <v>-8.0982</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.93</v>
       </c>
       <c r="I202" t="n">
-        <v>1.6652</v>
+        <v>1.7193</v>
       </c>
       <c r="J202" t="n">
-        <v>36.6344</v>
+        <v>37.8246</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.34</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8339</v>
+        <v>0.8117</v>
       </c>
       <c r="J203" t="n">
-        <v>18.3458</v>
+        <v>17.8574</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2845</v>
+        <v>0.2524</v>
       </c>
       <c r="J204" t="n">
-        <v>6.259</v>
+        <v>5.5528</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.98</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1342</v>
+        <v>-0.107</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.9524</v>
+        <v>-2.354</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.9688</v>
+        <v>-0.9667</v>
       </c>
       <c r="J206" t="n">
-        <v>-21.3136</v>
+        <v>-21.2674</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.38</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7131</v>
+        <v>0.6564</v>
       </c>
       <c r="J207" t="n">
-        <v>15.6882</v>
+        <v>14.4408</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.33</v>
       </c>
       <c r="I208" t="n">
-        <v>0.637</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>14.014</v>
+        <v>12.7182</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0745</v>
+        <v>-0.0597</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.639</v>
+        <v>-1.3134</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2347</v>
+        <v>-0.2144</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.1634</v>
+        <v>-4.7168</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.64</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4041</v>
+        <v>-0.3946</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.8902</v>
+        <v>-8.6812</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.88</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2822</v>
+        <v>1.2764</v>
       </c>
       <c r="J212" t="n">
-        <v>30.7728</v>
+        <v>30.6336</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.12</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2773</v>
+        <v>0.2308</v>
       </c>
       <c r="J213" t="n">
-        <v>6.6552</v>
+        <v>5.5392</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.131</v>
+        <v>-0.1118</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.144</v>
+        <v>-2.6832</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2797</v>
+        <v>-0.2614</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.7128</v>
+        <v>-6.2736</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.74</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3179</v>
+        <v>-0.3018</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.6296</v>
+        <v>-7.2432</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.69</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3657</v>
+        <v>1.3914</v>
       </c>
       <c r="J217" t="n">
-        <v>32.7768</v>
+        <v>33.3936</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.37</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8983</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="J218" t="n">
-        <v>21.5592</v>
+        <v>21.132</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.27</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6965</v>
+        <v>0.6655</v>
       </c>
       <c r="J219" t="n">
-        <v>16.716</v>
+        <v>15.972</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.04</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1423</v>
+        <v>0.1183</v>
       </c>
       <c r="J220" t="n">
-        <v>3.4152</v>
+        <v>2.8392</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.5</v>
       </c>
       <c r="I221" t="n">
-        <v>-1.2422</v>
+        <v>-1.279</v>
       </c>
       <c r="J221" t="n">
-        <v>-29.8128</v>
+        <v>-30.696</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.56</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7012</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>29.4504</v>
+        <v>26.481</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2557</v>
+        <v>0.2062</v>
       </c>
       <c r="J223" t="n">
-        <v>10.7394</v>
+        <v>8.660399999999999</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.14</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2301</v>
+        <v>0.1838</v>
       </c>
       <c r="J224" t="n">
-        <v>9.664199999999999</v>
+        <v>7.7196</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0222</v>
+        <v>0.0144</v>
       </c>
       <c r="J225" t="n">
-        <v>0.9324</v>
+        <v>0.6048</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.73</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3298</v>
+        <v>-0.3148</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.8516</v>
+        <v>-13.2216</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.34</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5123</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="J227" t="n">
-        <v>21.5166</v>
+        <v>21.9954</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.13</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2395</v>
+        <v>0.2243</v>
       </c>
       <c r="J228" t="n">
-        <v>10.059</v>
+        <v>9.4206</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.95</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0876</v>
+        <v>-0.0716</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.6792</v>
+        <v>-3.0072</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2033</v>
+        <v>-0.1826</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.538600000000001</v>
+        <v>-7.6692</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.224</v>
+        <v>-0.2035</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.407999999999999</v>
+        <v>-8.547000000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.14</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3552</v>
+        <v>0.3026</v>
       </c>
       <c r="J232" t="n">
-        <v>6.7488</v>
+        <v>5.7494</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.13</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3362</v>
+        <v>0.2845</v>
       </c>
       <c r="J233" t="n">
-        <v>6.3878</v>
+        <v>5.4055</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.85</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1918</v>
+        <v>-0.1725</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.6442</v>
+        <v>-3.2775</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.72</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3188</v>
+        <v>-0.3017</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.0572</v>
+        <v>-5.7323</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4099</v>
+        <v>-0.3996</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.7881</v>
+        <v>-7.5924</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.76</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4043</v>
+        <v>1.4294</v>
       </c>
       <c r="J237" t="n">
-        <v>26.6817</v>
+        <v>27.1586</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.6</v>
       </c>
       <c r="I238" t="n">
-        <v>1.2032</v>
+        <v>1.2193</v>
       </c>
       <c r="J238" t="n">
-        <v>22.8608</v>
+        <v>23.1667</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.43</v>
       </c>
       <c r="I239" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9677</v>
       </c>
       <c r="J239" t="n">
-        <v>18.4167</v>
+        <v>18.3863</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.38</v>
       </c>
       <c r="I240" t="n">
-        <v>0.8819</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>16.7561</v>
+        <v>16.5585</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7639</v>
+        <v>-0.7458</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.5141</v>
+        <v>-14.1702</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.3</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2176</v>
+        <v>1.1824</v>
       </c>
       <c r="J242" t="n">
-        <v>19.4816</v>
+        <v>18.9184</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.7</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7772</v>
+        <v>0.7073</v>
       </c>
       <c r="J243" t="n">
-        <v>12.4352</v>
+        <v>11.3168</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.65</v>
       </c>
       <c r="I244" t="n">
-        <v>0.7319</v>
+        <v>0.6623</v>
       </c>
       <c r="J244" t="n">
-        <v>11.7104</v>
+        <v>10.5968</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1138</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J245" t="n">
-        <v>1.8208</v>
+        <v>1.344</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.86</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2272</v>
+        <v>-0.2121</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.6352</v>
+        <v>-3.3936</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.08</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2201</v>
+        <v>0.2123</v>
       </c>
       <c r="J247" t="n">
-        <v>3.5216</v>
+        <v>3.3968</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.9</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1233</v>
+        <v>-0.1084</v>
       </c>
       <c r="J248" t="n">
-        <v>-1.9728</v>
+        <v>-1.7344</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.86</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1689</v>
+        <v>-0.1532</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.7024</v>
+        <v>-2.4512</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.54</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4665</v>
+        <v>-0.4613</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.464</v>
+        <v>-7.3808</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.43</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5619</v>
+        <v>-0.5694</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.990399999999999</v>
+        <v>-9.1104</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I252" t="n">
-        <v>0.345</v>
+        <v>0.2941</v>
       </c>
       <c r="J252" t="n">
-        <v>8.279999999999999</v>
+        <v>7.0584</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0231</v>
+        <v>0.0176</v>
       </c>
       <c r="J253" t="n">
-        <v>0.5544</v>
+        <v>0.4224</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1368</v>
+        <v>-0.1204</v>
       </c>
       <c r="J254" t="n">
-        <v>-3.2832</v>
+        <v>-2.8896</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.68</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3529</v>
+        <v>-0.3378</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.4696</v>
+        <v>-8.107200000000001</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.61</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4159</v>
+        <v>-0.4061</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.9816</v>
+        <v>-9.7464</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.56</v>
       </c>
       <c r="I257" t="n">
-        <v>1.18</v>
+        <v>1.1941</v>
       </c>
       <c r="J257" t="n">
-        <v>28.32</v>
+        <v>28.6584</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.52</v>
       </c>
       <c r="I258" t="n">
-        <v>1.126</v>
+        <v>1.1384</v>
       </c>
       <c r="J258" t="n">
-        <v>27.024</v>
+        <v>27.3216</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.16</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4531</v>
+        <v>0.4195</v>
       </c>
       <c r="J259" t="n">
-        <v>10.8744</v>
+        <v>10.068</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.06</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1953</v>
+        <v>0.1674</v>
       </c>
       <c r="J260" t="n">
-        <v>4.6872</v>
+        <v>4.0176</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.83</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5597</v>
+        <v>-0.5232</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.4328</v>
+        <v>-12.5568</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.62</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0379</v>
+        <v>1.0146</v>
       </c>
       <c r="J262" t="n">
-        <v>23.8717</v>
+        <v>23.3358</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.36</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6784</v>
+        <v>0.6202</v>
       </c>
       <c r="J263" t="n">
-        <v>15.6032</v>
+        <v>14.2646</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1839</v>
+        <v>-0.1633</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.2297</v>
+        <v>-3.7559</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.71</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3421</v>
+        <v>-0.3272</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.8683</v>
+        <v>-7.5256</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.65</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3965</v>
+        <v>-0.3864</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.1195</v>
+        <v>-8.8872</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.44</v>
       </c>
       <c r="I267" t="n">
-        <v>1.025</v>
+        <v>1.0262</v>
       </c>
       <c r="J267" t="n">
-        <v>23.575</v>
+        <v>23.6026</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I268" t="n">
-        <v>0.9387</v>
+        <v>0.9254</v>
       </c>
       <c r="J268" t="n">
-        <v>21.5901</v>
+        <v>21.2842</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.11</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3413</v>
+        <v>0.3067</v>
       </c>
       <c r="J269" t="n">
-        <v>7.8499</v>
+        <v>7.0541</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0736</v>
+        <v>0.0572</v>
       </c>
       <c r="J270" t="n">
-        <v>1.6928</v>
+        <v>1.3156</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.87</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4517</v>
+        <v>-0.4103</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.3891</v>
+        <v>-9.4369</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.75</v>
       </c>
       <c r="I272" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J272" t="n">
-        <v>25.1836</v>
+        <v>25.7634</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>2.27</v>
       </c>
       <c r="I273" t="n">
-        <v>1.9173</v>
+        <v>1.9818</v>
       </c>
       <c r="J273" t="n">
-        <v>24.9249</v>
+        <v>25.7634</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.65</v>
       </c>
       <c r="I274" t="n">
-        <v>1.2269</v>
+        <v>1.255</v>
       </c>
       <c r="J274" t="n">
-        <v>15.9497</v>
+        <v>16.315</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.25</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5729</v>
+        <v>0.5451</v>
       </c>
       <c r="J275" t="n">
-        <v>7.4477</v>
+        <v>7.0863</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.07</v>
       </c>
       <c r="I276" t="n">
-        <v>0.1459</v>
+        <v>0.1054</v>
       </c>
       <c r="J276" t="n">
-        <v>1.8967</v>
+        <v>1.3702</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.59</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.3753</v>
+        <v>-0.3697</v>
       </c>
       <c r="J277" t="n">
-        <v>-4.8789</v>
+        <v>-4.8061</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.54</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.4239</v>
+        <v>-0.4224</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.5107</v>
+        <v>-5.4912</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.44</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.5128</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.6378</v>
+        <v>-6.6664</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.39</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5545</v>
+        <v>-0.5596</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.2085</v>
+        <v>-7.2748</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.37</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5725</v>
+        <v>-0.5794</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.4425</v>
+        <v>-7.5322</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.93</v>
       </c>
       <c r="I282" t="n">
-        <v>1.5972</v>
+        <v>1.6362</v>
       </c>
       <c r="J282" t="n">
-        <v>27.1524</v>
+        <v>27.8154</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.57</v>
       </c>
       <c r="I283" t="n">
-        <v>1.1564</v>
+        <v>1.173</v>
       </c>
       <c r="J283" t="n">
-        <v>19.6588</v>
+        <v>19.941</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.29</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7009</v>
+        <v>0.6817</v>
       </c>
       <c r="J284" t="n">
-        <v>11.9153</v>
+        <v>11.5889</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.28</v>
       </c>
       <c r="I285" t="n">
-        <v>0.6806</v>
+        <v>0.6603</v>
       </c>
       <c r="J285" t="n">
-        <v>11.5702</v>
+        <v>11.2251</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.16</v>
       </c>
       <c r="I286" t="n">
-        <v>0.4196</v>
+        <v>0.3882</v>
       </c>
       <c r="J286" t="n">
-        <v>7.1332</v>
+        <v>6.5994</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.74</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.2731</v>
+        <v>-0.2601</v>
       </c>
       <c r="J287" t="n">
-        <v>-4.6427</v>
+        <v>-4.4217</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.7</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3114</v>
+        <v>-0.2997</v>
       </c>
       <c r="J288" t="n">
-        <v>-5.2938</v>
+        <v>-5.0949</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.68</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3299</v>
+        <v>-0.3185</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.6083</v>
+        <v>-5.4145</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.62</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3815</v>
+        <v>-0.3712</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.4855</v>
+        <v>-6.3104</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.49</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4956</v>
+        <v>-0.4932</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.4252</v>
+        <v>-8.384399999999999</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>2.18</v>
       </c>
       <c r="I292" t="n">
-        <v>1.9123</v>
+        <v>1.9818</v>
       </c>
       <c r="J292" t="n">
-        <v>38.246</v>
+        <v>39.636</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.61</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2202</v>
+        <v>1.2364</v>
       </c>
       <c r="J293" t="n">
-        <v>24.404</v>
+        <v>24.728</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5676</v>
+        <v>0.5401</v>
       </c>
       <c r="J294" t="n">
-        <v>11.352</v>
+        <v>10.802</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.4093</v>
+        <v>0.3778</v>
       </c>
       <c r="J295" t="n">
-        <v>8.186</v>
+        <v>7.556</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.63</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.0102</v>
+        <v>-1.0183</v>
       </c>
       <c r="J296" t="n">
-        <v>-20.204</v>
+        <v>-20.366</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.37</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7399</v>
+        <v>0.6913</v>
       </c>
       <c r="J297" t="n">
-        <v>14.798</v>
+        <v>13.826</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.91</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1286</v>
+        <v>-0.1116</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.572</v>
+        <v>-2.232</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.86</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1826</v>
+        <v>-0.1631</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.652</v>
+        <v>-3.262</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.8</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2435</v>
+        <v>-0.2238</v>
       </c>
       <c r="J300" t="n">
-        <v>-4.87</v>
+        <v>-4.476</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.59</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4377</v>
+        <v>-0.4305</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.754</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.09</v>
       </c>
       <c r="I302" t="n">
-        <v>0.208</v>
+        <v>0.1929</v>
       </c>
       <c r="J302" t="n">
-        <v>3.952</v>
+        <v>3.6651</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1133</v>
+        <v>-0.0982</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.1527</v>
+        <v>-1.8658</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1366</v>
+        <v>-0.1203</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.5954</v>
+        <v>-2.2857</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.74</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.297</v>
+        <v>-0.279</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.643</v>
+        <v>-5.301</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.66</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3709</v>
+        <v>-0.3571</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.0471</v>
+        <v>-6.7849</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.61</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7216</v>
+        <v>0.6494</v>
       </c>
       <c r="J307" t="n">
-        <v>13.7104</v>
+        <v>12.3386</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.38</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4909</v>
+        <v>0.4248</v>
       </c>
       <c r="J308" t="n">
-        <v>9.3271</v>
+        <v>8.071199999999999</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.22</v>
       </c>
       <c r="I309" t="n">
-        <v>0.3174</v>
+        <v>0.265</v>
       </c>
       <c r="J309" t="n">
-        <v>6.0306</v>
+        <v>5.035</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.11</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1771</v>
+        <v>0.1403</v>
       </c>
       <c r="J310" t="n">
-        <v>3.3649</v>
+        <v>2.6657</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.09</v>
       </c>
       <c r="I311" t="n">
-        <v>0.1483</v>
+        <v>0.1155</v>
       </c>
       <c r="J311" t="n">
-        <v>2.8177</v>
+        <v>2.1945</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.42</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9928</v>
+        <v>0.9882</v>
       </c>
       <c r="J312" t="n">
-        <v>21.8416</v>
+        <v>21.7404</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.21</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5354</v>
       </c>
       <c r="J313" t="n">
-        <v>12.5642</v>
+        <v>11.7788</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.19</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5274</v>
+        <v>0.4911</v>
       </c>
       <c r="J314" t="n">
-        <v>11.6028</v>
+        <v>10.8042</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.14</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4149</v>
+        <v>0.3788</v>
       </c>
       <c r="J315" t="n">
-        <v>9.127800000000001</v>
+        <v>8.333600000000001</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.86</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4763</v>
+        <v>-0.4354</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.4786</v>
+        <v>-9.578799999999999</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.11</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2906</v>
+        <v>0.2411</v>
       </c>
       <c r="J317" t="n">
-        <v>6.3932</v>
+        <v>5.3042</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.01</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0561</v>
+        <v>0.0382</v>
       </c>
       <c r="J318" t="n">
-        <v>1.2342</v>
+        <v>0.8404</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.9</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1402</v>
+        <v>-0.1222</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.0844</v>
+        <v>-2.6884</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.82</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2246</v>
+        <v>-0.2045</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.9412</v>
+        <v>-4.499</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.74</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3025</v>
+        <v>-0.2845</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.655</v>
+        <v>-6.259</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.91</v>
       </c>
       <c r="I322" t="n">
-        <v>1.5777</v>
+        <v>1.6151</v>
       </c>
       <c r="J322" t="n">
-        <v>28.3986</v>
+        <v>29.0718</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.69</v>
       </c>
       <c r="I323" t="n">
-        <v>1.3101</v>
+        <v>1.3307</v>
       </c>
       <c r="J323" t="n">
-        <v>23.5818</v>
+        <v>23.9526</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.52</v>
       </c>
       <c r="I324" t="n">
-        <v>1.0946</v>
+        <v>1.1095</v>
       </c>
       <c r="J324" t="n">
-        <v>19.7028</v>
+        <v>19.971</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.1</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2744</v>
+        <v>0.2419</v>
       </c>
       <c r="J325" t="n">
-        <v>4.9392</v>
+        <v>4.3542</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.91</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3885</v>
+        <v>-0.3542</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.993</v>
+        <v>-6.3756</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.08</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2864</v>
+        <v>0.248</v>
       </c>
       <c r="J327" t="n">
-        <v>5.1552</v>
+        <v>4.464</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.04</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1917</v>
+        <v>0.1612</v>
       </c>
       <c r="J328" t="n">
-        <v>3.4506</v>
+        <v>2.9016</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.66</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3583</v>
+        <v>-0.3443</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.4494</v>
+        <v>-6.1974</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.54</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4651</v>
+        <v>-0.4596</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.3718</v>
+        <v>-8.2728</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.43</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5606</v>
+        <v>-0.5678</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.0908</v>
+        <v>-10.2204</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.36</v>
       </c>
       <c r="I332" t="n">
-        <v>0.8661</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="J332" t="n">
-        <v>19.9203</v>
+        <v>19.4879</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.32</v>
       </c>
       <c r="I333" t="n">
-        <v>0.7875</v>
+        <v>0.7635</v>
       </c>
       <c r="J333" t="n">
-        <v>18.1125</v>
+        <v>17.5605</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.32</v>
       </c>
       <c r="I334" t="n">
-        <v>0.7875</v>
+        <v>0.7635</v>
       </c>
       <c r="J334" t="n">
-        <v>18.1125</v>
+        <v>17.5605</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.11</v>
       </c>
       <c r="I335" t="n">
-        <v>0.3312</v>
+        <v>0.2985</v>
       </c>
       <c r="J335" t="n">
-        <v>7.6176</v>
+        <v>6.8655</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>1.04</v>
       </c>
       <c r="I336" t="n">
-        <v>0.1327</v>
+        <v>0.1091</v>
       </c>
       <c r="J336" t="n">
-        <v>3.0521</v>
+        <v>2.5093</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.92</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1156</v>
+        <v>-0.1</v>
       </c>
       <c r="J337" t="n">
-        <v>-2.6588</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.9</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1386</v>
+        <v>-0.1215</v>
       </c>
       <c r="J338" t="n">
-        <v>-3.1878</v>
+        <v>-2.7945</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.9</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1386</v>
+        <v>-0.1215</v>
       </c>
       <c r="J339" t="n">
-        <v>-3.1878</v>
+        <v>-2.7945</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.88</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.16</v>
+        <v>-0.1419</v>
       </c>
       <c r="J340" t="n">
-        <v>-3.68</v>
+        <v>-3.2637</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2117</v>
+        <v>-0.1922</v>
       </c>
       <c r="J341" t="n">
-        <v>-4.8691</v>
+        <v>-4.4206</v>
       </c>
     </row>
   </sheetData>
